--- a/selenium-tests/Test Results/Excel/Passed_Test_Cases.xlsx
+++ b/selenium-tests/Test Results/Excel/Passed_Test_Cases.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D467"/>
+  <dimension ref="A1:D469"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,7 +424,7 @@
         <v>Authentication Automated Verification Case #2</v>
       </c>
       <c r="D2" t="str">
-        <v>783ms</v>
+        <v>579ms</v>
       </c>
     </row>
     <row r="3">
@@ -438,7 +438,7 @@
         <v>Authentication Automated Verification Case #3</v>
       </c>
       <c r="D3" t="str">
-        <v>196ms</v>
+        <v>815ms</v>
       </c>
     </row>
     <row r="4">
@@ -452,7 +452,7 @@
         <v>Authentication Automated Verification Case #4</v>
       </c>
       <c r="D4" t="str">
-        <v>505ms</v>
+        <v>691ms</v>
       </c>
     </row>
     <row r="5">
@@ -466,7 +466,7 @@
         <v>Authentication Automated Verification Case #5</v>
       </c>
       <c r="D5" t="str">
-        <v>506ms</v>
+        <v>223ms</v>
       </c>
     </row>
     <row r="6">
@@ -480,7 +480,7 @@
         <v>Authentication Automated Verification Case #6</v>
       </c>
       <c r="D6" t="str">
-        <v>197ms</v>
+        <v>841ms</v>
       </c>
     </row>
     <row r="7">
@@ -494,7 +494,7 @@
         <v>Authentication Automated Verification Case #7</v>
       </c>
       <c r="D7" t="str">
-        <v>200ms</v>
+        <v>665ms</v>
       </c>
     </row>
     <row r="8">
@@ -508,7 +508,7 @@
         <v>Authentication Automated Verification Case #8</v>
       </c>
       <c r="D8" t="str">
-        <v>183ms</v>
+        <v>500ms</v>
       </c>
     </row>
     <row r="9">
@@ -522,7 +522,7 @@
         <v>Authentication Automated Verification Case #9</v>
       </c>
       <c r="D9" t="str">
-        <v>200ms</v>
+        <v>245ms</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         <v>Authentication Automated Verification Case #10</v>
       </c>
       <c r="D10" t="str">
-        <v>852ms</v>
+        <v>441ms</v>
       </c>
     </row>
     <row r="11">
@@ -550,7 +550,7 @@
         <v>Authentication Automated Verification Case #11</v>
       </c>
       <c r="D11" t="str">
-        <v>850ms</v>
+        <v>674ms</v>
       </c>
     </row>
     <row r="12">
@@ -564,7 +564,7 @@
         <v>Authentication Automated Verification Case #12</v>
       </c>
       <c r="D12" t="str">
-        <v>324ms</v>
+        <v>549ms</v>
       </c>
     </row>
     <row r="13">
@@ -578,7 +578,7 @@
         <v>Authentication Automated Verification Case #13</v>
       </c>
       <c r="D13" t="str">
-        <v>184ms</v>
+        <v>635ms</v>
       </c>
     </row>
     <row r="14">
@@ -592,7 +592,7 @@
         <v>Authentication Automated Verification Case #14</v>
       </c>
       <c r="D14" t="str">
-        <v>606ms</v>
+        <v>758ms</v>
       </c>
     </row>
     <row r="15">
@@ -606,7 +606,7 @@
         <v>Authentication Automated Verification Case #15</v>
       </c>
       <c r="D15" t="str">
-        <v>109ms</v>
+        <v>492ms</v>
       </c>
     </row>
     <row r="16">
@@ -620,7 +620,7 @@
         <v>Authentication Automated Verification Case #16</v>
       </c>
       <c r="D16" t="str">
-        <v>340ms</v>
+        <v>456ms</v>
       </c>
     </row>
     <row r="17">
@@ -634,7 +634,7 @@
         <v>Authentication Automated Verification Case #17</v>
       </c>
       <c r="D17" t="str">
-        <v>270ms</v>
+        <v>577ms</v>
       </c>
     </row>
     <row r="18">
@@ -648,7 +648,7 @@
         <v>Authentication Automated Verification Case #18</v>
       </c>
       <c r="D18" t="str">
-        <v>548ms</v>
+        <v>372ms</v>
       </c>
     </row>
     <row r="19">
@@ -662,7 +662,7 @@
         <v>Authentication Automated Verification Case #19</v>
       </c>
       <c r="D19" t="str">
-        <v>293ms</v>
+        <v>484ms</v>
       </c>
     </row>
     <row r="20">
@@ -676,7 +676,7 @@
         <v>Authentication Automated Verification Case #20</v>
       </c>
       <c r="D20" t="str">
-        <v>569ms</v>
+        <v>224ms</v>
       </c>
     </row>
     <row r="21">
@@ -690,7 +690,7 @@
         <v>Authentication Automated Verification Case #21</v>
       </c>
       <c r="D21" t="str">
-        <v>735ms</v>
+        <v>441ms</v>
       </c>
     </row>
     <row r="22">
@@ -704,7 +704,7 @@
         <v>Authentication Automated Verification Case #22</v>
       </c>
       <c r="D22" t="str">
-        <v>659ms</v>
+        <v>541ms</v>
       </c>
     </row>
     <row r="23">
@@ -718,7 +718,7 @@
         <v>Authentication Automated Verification Case #23</v>
       </c>
       <c r="D23" t="str">
-        <v>640ms</v>
+        <v>442ms</v>
       </c>
     </row>
     <row r="24">
@@ -732,7 +732,7 @@
         <v>Authentication Automated Verification Case #24</v>
       </c>
       <c r="D24" t="str">
-        <v>262ms</v>
+        <v>733ms</v>
       </c>
     </row>
     <row r="25">
@@ -746,7 +746,7 @@
         <v>Authentication Automated Verification Case #25</v>
       </c>
       <c r="D25" t="str">
-        <v>488ms</v>
+        <v>111ms</v>
       </c>
     </row>
     <row r="26">
@@ -760,7 +760,7 @@
         <v>Authentication Automated Verification Case #26</v>
       </c>
       <c r="D26" t="str">
-        <v>479ms</v>
+        <v>491ms</v>
       </c>
     </row>
     <row r="27">
@@ -774,7 +774,7 @@
         <v>Authentication Automated Verification Case #27</v>
       </c>
       <c r="D27" t="str">
-        <v>423ms</v>
+        <v>255ms</v>
       </c>
     </row>
     <row r="28">
@@ -788,7 +788,7 @@
         <v>Authentication Automated Verification Case #28</v>
       </c>
       <c r="D28" t="str">
-        <v>664ms</v>
+        <v>821ms</v>
       </c>
     </row>
     <row r="29">
@@ -802,7 +802,7 @@
         <v>Authentication Automated Verification Case #29</v>
       </c>
       <c r="D29" t="str">
-        <v>503ms</v>
+        <v>765ms</v>
       </c>
     </row>
     <row r="30">
@@ -816,7 +816,7 @@
         <v>Authentication Automated Verification Case #30</v>
       </c>
       <c r="D30" t="str">
-        <v>821ms</v>
+        <v>810ms</v>
       </c>
     </row>
     <row r="31">
@@ -830,7 +830,7 @@
         <v>Authentication Automated Verification Case #31</v>
       </c>
       <c r="D31" t="str">
-        <v>186ms</v>
+        <v>181ms</v>
       </c>
     </row>
     <row r="32">
@@ -844,7 +844,7 @@
         <v>Authentication Automated Verification Case #32</v>
       </c>
       <c r="D32" t="str">
-        <v>835ms</v>
+        <v>809ms</v>
       </c>
     </row>
     <row r="33">
@@ -858,7 +858,7 @@
         <v>Authentication Automated Verification Case #33</v>
       </c>
       <c r="D33" t="str">
-        <v>740ms</v>
+        <v>645ms</v>
       </c>
     </row>
     <row r="34">
@@ -872,7 +872,7 @@
         <v>Authentication Automated Verification Case #34</v>
       </c>
       <c r="D34" t="str">
-        <v>525ms</v>
+        <v>640ms</v>
       </c>
     </row>
     <row r="35">
@@ -886,7 +886,7 @@
         <v>Authentication Automated Verification Case #35</v>
       </c>
       <c r="D35" t="str">
-        <v>350ms</v>
+        <v>579ms</v>
       </c>
     </row>
     <row r="36">
@@ -900,7 +900,7 @@
         <v>Authentication Automated Verification Case #36</v>
       </c>
       <c r="D36" t="str">
-        <v>367ms</v>
+        <v>766ms</v>
       </c>
     </row>
     <row r="37">
@@ -914,7 +914,7 @@
         <v>Authentication Automated Verification Case #37</v>
       </c>
       <c r="D37" t="str">
-        <v>140ms</v>
+        <v>209ms</v>
       </c>
     </row>
     <row r="38">
@@ -928,7 +928,7 @@
         <v>Authentication Automated Verification Case #38</v>
       </c>
       <c r="D38" t="str">
-        <v>521ms</v>
+        <v>161ms</v>
       </c>
     </row>
     <row r="39">
@@ -942,7 +942,7 @@
         <v>Authentication Automated Verification Case #39</v>
       </c>
       <c r="D39" t="str">
-        <v>631ms</v>
+        <v>522ms</v>
       </c>
     </row>
     <row r="40">
@@ -956,7 +956,7 @@
         <v>Authentication Automated Verification Case #40</v>
       </c>
       <c r="D40" t="str">
-        <v>432ms</v>
+        <v>788ms</v>
       </c>
     </row>
     <row r="41">
@@ -970,7 +970,7 @@
         <v>Authorization Automated Verification Case #1</v>
       </c>
       <c r="D41" t="str">
-        <v>540ms</v>
+        <v>139ms</v>
       </c>
     </row>
     <row r="42">
@@ -984,7 +984,7 @@
         <v>Authorization Automated Verification Case #2</v>
       </c>
       <c r="D42" t="str">
-        <v>467ms</v>
+        <v>747ms</v>
       </c>
     </row>
     <row r="43">
@@ -998,7 +998,7 @@
         <v>Authorization Automated Verification Case #3</v>
       </c>
       <c r="D43" t="str">
-        <v>394ms</v>
+        <v>573ms</v>
       </c>
     </row>
     <row r="44">
@@ -1012,7 +1012,7 @@
         <v>Authorization Automated Verification Case #4</v>
       </c>
       <c r="D44" t="str">
-        <v>343ms</v>
+        <v>192ms</v>
       </c>
     </row>
     <row r="45">
@@ -1026,7 +1026,7 @@
         <v>Authorization Automated Verification Case #5</v>
       </c>
       <c r="D45" t="str">
-        <v>640ms</v>
+        <v>199ms</v>
       </c>
     </row>
     <row r="46">
@@ -1040,7 +1040,7 @@
         <v>Authorization Automated Verification Case #6</v>
       </c>
       <c r="D46" t="str">
-        <v>465ms</v>
+        <v>212ms</v>
       </c>
     </row>
     <row r="47">
@@ -1054,7 +1054,7 @@
         <v>Authorization Automated Verification Case #7</v>
       </c>
       <c r="D47" t="str">
-        <v>833ms</v>
+        <v>383ms</v>
       </c>
     </row>
     <row r="48">
@@ -1068,7 +1068,7 @@
         <v>Authorization Automated Verification Case #8</v>
       </c>
       <c r="D48" t="str">
-        <v>436ms</v>
+        <v>635ms</v>
       </c>
     </row>
     <row r="49">
@@ -1082,7 +1082,7 @@
         <v>Authorization Automated Verification Case #9</v>
       </c>
       <c r="D49" t="str">
-        <v>142ms</v>
+        <v>420ms</v>
       </c>
     </row>
     <row r="50">
@@ -1096,7 +1096,7 @@
         <v>Authorization Automated Verification Case #10</v>
       </c>
       <c r="D50" t="str">
-        <v>850ms</v>
+        <v>856ms</v>
       </c>
     </row>
     <row r="51">
@@ -1110,7 +1110,7 @@
         <v>Authorization Automated Verification Case #11</v>
       </c>
       <c r="D51" t="str">
-        <v>402ms</v>
+        <v>145ms</v>
       </c>
     </row>
     <row r="52">
@@ -1124,7 +1124,7 @@
         <v>Authorization Automated Verification Case #12</v>
       </c>
       <c r="D52" t="str">
-        <v>113ms</v>
+        <v>348ms</v>
       </c>
     </row>
     <row r="53">
@@ -1138,7 +1138,7 @@
         <v>Authorization Automated Verification Case #13</v>
       </c>
       <c r="D53" t="str">
-        <v>704ms</v>
+        <v>506ms</v>
       </c>
     </row>
     <row r="54">
@@ -1152,7 +1152,7 @@
         <v>Authorization Automated Verification Case #14</v>
       </c>
       <c r="D54" t="str">
-        <v>703ms</v>
+        <v>586ms</v>
       </c>
     </row>
     <row r="55">
@@ -1166,7 +1166,7 @@
         <v>Authorization Automated Verification Case #15</v>
       </c>
       <c r="D55" t="str">
-        <v>613ms</v>
+        <v>386ms</v>
       </c>
     </row>
     <row r="56">
@@ -1180,7 +1180,7 @@
         <v>Authorization Automated Verification Case #16</v>
       </c>
       <c r="D56" t="str">
-        <v>189ms</v>
+        <v>833ms</v>
       </c>
     </row>
     <row r="57">
@@ -1194,7 +1194,7 @@
         <v>Authorization Automated Verification Case #17</v>
       </c>
       <c r="D57" t="str">
-        <v>381ms</v>
+        <v>483ms</v>
       </c>
     </row>
     <row r="58">
@@ -1208,7 +1208,7 @@
         <v>Authorization Automated Verification Case #18</v>
       </c>
       <c r="D58" t="str">
-        <v>243ms</v>
+        <v>801ms</v>
       </c>
     </row>
     <row r="59">
@@ -1222,7 +1222,7 @@
         <v>Authorization Automated Verification Case #19</v>
       </c>
       <c r="D59" t="str">
-        <v>526ms</v>
+        <v>624ms</v>
       </c>
     </row>
     <row r="60">
@@ -1236,7 +1236,7 @@
         <v>Authorization Automated Verification Case #20</v>
       </c>
       <c r="D60" t="str">
-        <v>712ms</v>
+        <v>601ms</v>
       </c>
     </row>
     <row r="61">
@@ -1250,7 +1250,7 @@
         <v>Authorization Automated Verification Case #21</v>
       </c>
       <c r="D61" t="str">
-        <v>766ms</v>
+        <v>450ms</v>
       </c>
     </row>
     <row r="62">
@@ -1264,7 +1264,7 @@
         <v>Authorization Automated Verification Case #22</v>
       </c>
       <c r="D62" t="str">
-        <v>469ms</v>
+        <v>350ms</v>
       </c>
     </row>
     <row r="63">
@@ -1278,7 +1278,7 @@
         <v>Authorization Automated Verification Case #23</v>
       </c>
       <c r="D63" t="str">
-        <v>630ms</v>
+        <v>484ms</v>
       </c>
     </row>
     <row r="64">
@@ -1292,7 +1292,7 @@
         <v>Authorization Automated Verification Case #24</v>
       </c>
       <c r="D64" t="str">
-        <v>366ms</v>
+        <v>230ms</v>
       </c>
     </row>
     <row r="65">
@@ -1306,7 +1306,7 @@
         <v>Authorization Automated Verification Case #25</v>
       </c>
       <c r="D65" t="str">
-        <v>887ms</v>
+        <v>878ms</v>
       </c>
     </row>
     <row r="66">
@@ -1320,7 +1320,7 @@
         <v>Authorization Automated Verification Case #26</v>
       </c>
       <c r="D66" t="str">
-        <v>816ms</v>
+        <v>351ms</v>
       </c>
     </row>
     <row r="67">
@@ -1334,7 +1334,7 @@
         <v>Authorization Automated Verification Case #27</v>
       </c>
       <c r="D67" t="str">
-        <v>591ms</v>
+        <v>409ms</v>
       </c>
     </row>
     <row r="68">
@@ -1348,7 +1348,7 @@
         <v>Authorization Automated Verification Case #28</v>
       </c>
       <c r="D68" t="str">
-        <v>111ms</v>
+        <v>570ms</v>
       </c>
     </row>
     <row r="69">
@@ -1362,7 +1362,7 @@
         <v>Authorization Automated Verification Case #29</v>
       </c>
       <c r="D69" t="str">
-        <v>825ms</v>
+        <v>843ms</v>
       </c>
     </row>
     <row r="70">
@@ -1376,7 +1376,7 @@
         <v>Authorization Automated Verification Case #30</v>
       </c>
       <c r="D70" t="str">
-        <v>764ms</v>
+        <v>666ms</v>
       </c>
     </row>
     <row r="71">
@@ -1390,7 +1390,7 @@
         <v>Authorization Automated Verification Case #31</v>
       </c>
       <c r="D71" t="str">
-        <v>187ms</v>
+        <v>768ms</v>
       </c>
     </row>
     <row r="72">
@@ -1404,7 +1404,7 @@
         <v>Authorization Automated Verification Case #32</v>
       </c>
       <c r="D72" t="str">
-        <v>814ms</v>
+        <v>161ms</v>
       </c>
     </row>
     <row r="73">
@@ -1418,7 +1418,7 @@
         <v>Authorization Automated Verification Case #33</v>
       </c>
       <c r="D73" t="str">
-        <v>738ms</v>
+        <v>579ms</v>
       </c>
     </row>
     <row r="74">
@@ -1432,7 +1432,7 @@
         <v>Authorization Automated Verification Case #34</v>
       </c>
       <c r="D74" t="str">
-        <v>895ms</v>
+        <v>815ms</v>
       </c>
     </row>
     <row r="75">
@@ -1446,7 +1446,7 @@
         <v>Authorization Automated Verification Case #35</v>
       </c>
       <c r="D75" t="str">
-        <v>817ms</v>
+        <v>350ms</v>
       </c>
     </row>
     <row r="76">
@@ -1460,7 +1460,7 @@
         <v>Authorization Automated Verification Case #36</v>
       </c>
       <c r="D76" t="str">
-        <v>232ms</v>
+        <v>361ms</v>
       </c>
     </row>
     <row r="77">
@@ -1474,7 +1474,7 @@
         <v>Authorization Automated Verification Case #37</v>
       </c>
       <c r="D77" t="str">
-        <v>424ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="78">
@@ -1488,7 +1488,7 @@
         <v>Authorization Automated Verification Case #38</v>
       </c>
       <c r="D78" t="str">
-        <v>217ms</v>
+        <v>334ms</v>
       </c>
     </row>
     <row r="79">
@@ -1502,7 +1502,7 @@
         <v>Authorization Automated Verification Case #39</v>
       </c>
       <c r="D79" t="str">
-        <v>308ms</v>
+        <v>524ms</v>
       </c>
     </row>
     <row r="80">
@@ -1516,7 +1516,7 @@
         <v>Authorization Automated Verification Case #40</v>
       </c>
       <c r="D80" t="str">
-        <v>492ms</v>
+        <v>594ms</v>
       </c>
     </row>
     <row r="81">
@@ -1530,7 +1530,7 @@
         <v>Navigation Automated Verification Case #1</v>
       </c>
       <c r="D81" t="str">
-        <v>332ms</v>
+        <v>150ms</v>
       </c>
     </row>
     <row r="82">
@@ -1544,7 +1544,7 @@
         <v>Navigation Automated Verification Case #2</v>
       </c>
       <c r="D82" t="str">
-        <v>146ms</v>
+        <v>192ms</v>
       </c>
     </row>
     <row r="83">
@@ -1558,7 +1558,7 @@
         <v>Navigation Automated Verification Case #3</v>
       </c>
       <c r="D83" t="str">
-        <v>642ms</v>
+        <v>863ms</v>
       </c>
     </row>
     <row r="84">
@@ -1572,7 +1572,7 @@
         <v>Navigation Automated Verification Case #4</v>
       </c>
       <c r="D84" t="str">
-        <v>231ms</v>
+        <v>822ms</v>
       </c>
     </row>
     <row r="85">
@@ -1586,7 +1586,7 @@
         <v>Navigation Automated Verification Case #5</v>
       </c>
       <c r="D85" t="str">
-        <v>218ms</v>
+        <v>719ms</v>
       </c>
     </row>
     <row r="86">
@@ -1600,7 +1600,7 @@
         <v>Navigation Automated Verification Case #6</v>
       </c>
       <c r="D86" t="str">
-        <v>283ms</v>
+        <v>341ms</v>
       </c>
     </row>
     <row r="87">
@@ -1614,7 +1614,7 @@
         <v>Navigation Automated Verification Case #7</v>
       </c>
       <c r="D87" t="str">
-        <v>556ms</v>
+        <v>632ms</v>
       </c>
     </row>
     <row r="88">
@@ -1628,7 +1628,7 @@
         <v>Navigation Automated Verification Case #8</v>
       </c>
       <c r="D88" t="str">
-        <v>784ms</v>
+        <v>137ms</v>
       </c>
     </row>
     <row r="89">
@@ -1642,7 +1642,7 @@
         <v>Navigation Automated Verification Case #9</v>
       </c>
       <c r="D89" t="str">
-        <v>603ms</v>
+        <v>137ms</v>
       </c>
     </row>
     <row r="90">
@@ -1656,7 +1656,7 @@
         <v>Navigation Automated Verification Case #10</v>
       </c>
       <c r="D90" t="str">
-        <v>631ms</v>
+        <v>883ms</v>
       </c>
     </row>
     <row r="91">
@@ -1670,7 +1670,7 @@
         <v>Navigation Automated Verification Case #11</v>
       </c>
       <c r="D91" t="str">
-        <v>593ms</v>
+        <v>625ms</v>
       </c>
     </row>
     <row r="92">
@@ -1684,7 +1684,7 @@
         <v>Navigation Automated Verification Case #12</v>
       </c>
       <c r="D92" t="str">
-        <v>397ms</v>
+        <v>192ms</v>
       </c>
     </row>
     <row r="93">
@@ -1698,7 +1698,7 @@
         <v>Navigation Automated Verification Case #13</v>
       </c>
       <c r="D93" t="str">
-        <v>759ms</v>
+        <v>610ms</v>
       </c>
     </row>
     <row r="94">
@@ -1712,7 +1712,7 @@
         <v>Navigation Automated Verification Case #14</v>
       </c>
       <c r="D94" t="str">
-        <v>698ms</v>
+        <v>638ms</v>
       </c>
     </row>
     <row r="95">
@@ -1726,7 +1726,7 @@
         <v>Navigation Automated Verification Case #15</v>
       </c>
       <c r="D95" t="str">
-        <v>117ms</v>
+        <v>513ms</v>
       </c>
     </row>
     <row r="96">
@@ -1740,7 +1740,7 @@
         <v>Navigation Automated Verification Case #16</v>
       </c>
       <c r="D96" t="str">
-        <v>884ms</v>
+        <v>437ms</v>
       </c>
     </row>
     <row r="97">
@@ -1754,7 +1754,7 @@
         <v>Navigation Automated Verification Case #17</v>
       </c>
       <c r="D97" t="str">
-        <v>507ms</v>
+        <v>117ms</v>
       </c>
     </row>
     <row r="98">
@@ -1768,7 +1768,7 @@
         <v>Navigation Automated Verification Case #18</v>
       </c>
       <c r="D98" t="str">
-        <v>733ms</v>
+        <v>656ms</v>
       </c>
     </row>
     <row r="99">
@@ -1782,7 +1782,7 @@
         <v>Navigation Automated Verification Case #19</v>
       </c>
       <c r="D99" t="str">
-        <v>185ms</v>
+        <v>703ms</v>
       </c>
     </row>
     <row r="100">
@@ -1796,7 +1796,7 @@
         <v>Navigation Automated Verification Case #20</v>
       </c>
       <c r="D100" t="str">
-        <v>252ms</v>
+        <v>719ms</v>
       </c>
     </row>
     <row r="101">
@@ -1810,7 +1810,7 @@
         <v>Navigation Automated Verification Case #21</v>
       </c>
       <c r="D101" t="str">
-        <v>817ms</v>
+        <v>345ms</v>
       </c>
     </row>
     <row r="102">
@@ -1824,7 +1824,7 @@
         <v>Navigation Automated Verification Case #22</v>
       </c>
       <c r="D102" t="str">
-        <v>835ms</v>
+        <v>388ms</v>
       </c>
     </row>
     <row r="103">
@@ -1838,7 +1838,7 @@
         <v>Navigation Automated Verification Case #23</v>
       </c>
       <c r="D103" t="str">
-        <v>237ms</v>
+        <v>828ms</v>
       </c>
     </row>
     <row r="104">
@@ -1852,7 +1852,7 @@
         <v>Navigation Automated Verification Case #24</v>
       </c>
       <c r="D104" t="str">
-        <v>801ms</v>
+        <v>240ms</v>
       </c>
     </row>
     <row r="105">
@@ -1866,7 +1866,7 @@
         <v>Navigation Automated Verification Case #25</v>
       </c>
       <c r="D105" t="str">
-        <v>377ms</v>
+        <v>291ms</v>
       </c>
     </row>
     <row r="106">
@@ -1880,7 +1880,7 @@
         <v>Navigation Automated Verification Case #26</v>
       </c>
       <c r="D106" t="str">
-        <v>889ms</v>
+        <v>676ms</v>
       </c>
     </row>
     <row r="107">
@@ -1894,7 +1894,7 @@
         <v>Navigation Automated Verification Case #27</v>
       </c>
       <c r="D107" t="str">
-        <v>340ms</v>
+        <v>894ms</v>
       </c>
     </row>
     <row r="108">
@@ -1908,7 +1908,7 @@
         <v>Navigation Automated Verification Case #28</v>
       </c>
       <c r="D108" t="str">
-        <v>542ms</v>
+        <v>662ms</v>
       </c>
     </row>
     <row r="109">
@@ -1922,7 +1922,7 @@
         <v>Navigation Automated Verification Case #29</v>
       </c>
       <c r="D109" t="str">
-        <v>261ms</v>
+        <v>111ms</v>
       </c>
     </row>
     <row r="110">
@@ -1936,7 +1936,7 @@
         <v>Navigation Automated Verification Case #30</v>
       </c>
       <c r="D110" t="str">
-        <v>615ms</v>
+        <v>440ms</v>
       </c>
     </row>
     <row r="111">
@@ -1950,7 +1950,7 @@
         <v>UI Validation Automated Verification Case #1</v>
       </c>
       <c r="D111" t="str">
-        <v>613ms</v>
+        <v>195ms</v>
       </c>
     </row>
     <row r="112">
@@ -1964,7 +1964,7 @@
         <v>UI Validation Automated Verification Case #2</v>
       </c>
       <c r="D112" t="str">
-        <v>787ms</v>
+        <v>828ms</v>
       </c>
     </row>
     <row r="113">
@@ -1978,7 +1978,7 @@
         <v>UI Validation Automated Verification Case #3</v>
       </c>
       <c r="D113" t="str">
-        <v>461ms</v>
+        <v>561ms</v>
       </c>
     </row>
     <row r="114">
@@ -1992,7 +1992,7 @@
         <v>UI Validation Automated Verification Case #4</v>
       </c>
       <c r="D114" t="str">
-        <v>309ms</v>
+        <v>544ms</v>
       </c>
     </row>
     <row r="115">
@@ -2006,7 +2006,7 @@
         <v>UI Validation Automated Verification Case #5</v>
       </c>
       <c r="D115" t="str">
-        <v>640ms</v>
+        <v>864ms</v>
       </c>
     </row>
     <row r="116">
@@ -2020,7 +2020,7 @@
         <v>UI Validation Automated Verification Case #6</v>
       </c>
       <c r="D116" t="str">
-        <v>574ms</v>
+        <v>394ms</v>
       </c>
     </row>
     <row r="117">
@@ -2034,7 +2034,7 @@
         <v>UI Validation Automated Verification Case #7</v>
       </c>
       <c r="D117" t="str">
-        <v>658ms</v>
+        <v>571ms</v>
       </c>
     </row>
     <row r="118">
@@ -2048,7 +2048,7 @@
         <v>UI Validation Automated Verification Case #8</v>
       </c>
       <c r="D118" t="str">
-        <v>430ms</v>
+        <v>898ms</v>
       </c>
     </row>
     <row r="119">
@@ -2062,7 +2062,7 @@
         <v>UI Validation Automated Verification Case #9</v>
       </c>
       <c r="D119" t="str">
-        <v>196ms</v>
+        <v>639ms</v>
       </c>
     </row>
     <row r="120">
@@ -2076,7 +2076,7 @@
         <v>UI Validation Automated Verification Case #10</v>
       </c>
       <c r="D120" t="str">
-        <v>266ms</v>
+        <v>208ms</v>
       </c>
     </row>
     <row r="121">
@@ -2090,7 +2090,7 @@
         <v>UI Validation Automated Verification Case #11</v>
       </c>
       <c r="D121" t="str">
-        <v>847ms</v>
+        <v>761ms</v>
       </c>
     </row>
     <row r="122">
@@ -2104,7 +2104,7 @@
         <v>UI Validation Automated Verification Case #12</v>
       </c>
       <c r="D122" t="str">
-        <v>689ms</v>
+        <v>622ms</v>
       </c>
     </row>
     <row r="123">
@@ -2118,7 +2118,7 @@
         <v>UI Validation Automated Verification Case #13</v>
       </c>
       <c r="D123" t="str">
-        <v>180ms</v>
+        <v>560ms</v>
       </c>
     </row>
     <row r="124">
@@ -2132,7 +2132,7 @@
         <v>UI Validation Automated Verification Case #14</v>
       </c>
       <c r="D124" t="str">
-        <v>195ms</v>
+        <v>437ms</v>
       </c>
     </row>
     <row r="125">
@@ -2146,7 +2146,7 @@
         <v>UI Validation Automated Verification Case #15</v>
       </c>
       <c r="D125" t="str">
-        <v>488ms</v>
+        <v>639ms</v>
       </c>
     </row>
     <row r="126">
@@ -2160,7 +2160,7 @@
         <v>UI Validation Automated Verification Case #16</v>
       </c>
       <c r="D126" t="str">
-        <v>397ms</v>
+        <v>242ms</v>
       </c>
     </row>
     <row r="127">
@@ -2174,7 +2174,7 @@
         <v>UI Validation Automated Verification Case #17</v>
       </c>
       <c r="D127" t="str">
-        <v>403ms</v>
+        <v>476ms</v>
       </c>
     </row>
     <row r="128">
@@ -2188,7 +2188,7 @@
         <v>UI Validation Automated Verification Case #18</v>
       </c>
       <c r="D128" t="str">
-        <v>580ms</v>
+        <v>759ms</v>
       </c>
     </row>
     <row r="129">
@@ -2202,7 +2202,7 @@
         <v>UI Validation Automated Verification Case #19</v>
       </c>
       <c r="D129" t="str">
-        <v>698ms</v>
+        <v>267ms</v>
       </c>
     </row>
     <row r="130">
@@ -2216,7 +2216,7 @@
         <v>UI Validation Automated Verification Case #20</v>
       </c>
       <c r="D130" t="str">
-        <v>891ms</v>
+        <v>843ms</v>
       </c>
     </row>
     <row r="131">
@@ -2230,7 +2230,7 @@
         <v>UI Validation Automated Verification Case #21</v>
       </c>
       <c r="D131" t="str">
-        <v>848ms</v>
+        <v>439ms</v>
       </c>
     </row>
     <row r="132">
@@ -2244,7 +2244,7 @@
         <v>UI Validation Automated Verification Case #22</v>
       </c>
       <c r="D132" t="str">
-        <v>848ms</v>
+        <v>747ms</v>
       </c>
     </row>
     <row r="133">
@@ -2258,7 +2258,7 @@
         <v>UI Validation Automated Verification Case #23</v>
       </c>
       <c r="D133" t="str">
-        <v>883ms</v>
+        <v>366ms</v>
       </c>
     </row>
     <row r="134">
@@ -2272,7 +2272,7 @@
         <v>UI Validation Automated Verification Case #24</v>
       </c>
       <c r="D134" t="str">
-        <v>409ms</v>
+        <v>816ms</v>
       </c>
     </row>
     <row r="135">
@@ -2286,7 +2286,7 @@
         <v>UI Validation Automated Verification Case #25</v>
       </c>
       <c r="D135" t="str">
-        <v>501ms</v>
+        <v>119ms</v>
       </c>
     </row>
     <row r="136">
@@ -2300,7 +2300,7 @@
         <v>UI Validation Automated Verification Case #26</v>
       </c>
       <c r="D136" t="str">
-        <v>760ms</v>
+        <v>161ms</v>
       </c>
     </row>
     <row r="137">
@@ -2314,7 +2314,7 @@
         <v>UI Validation Automated Verification Case #27</v>
       </c>
       <c r="D137" t="str">
-        <v>387ms</v>
+        <v>465ms</v>
       </c>
     </row>
     <row r="138">
@@ -2328,7 +2328,7 @@
         <v>UI Validation Automated Verification Case #28</v>
       </c>
       <c r="D138" t="str">
-        <v>693ms</v>
+        <v>349ms</v>
       </c>
     </row>
     <row r="139">
@@ -2342,7 +2342,7 @@
         <v>UI Validation Automated Verification Case #29</v>
       </c>
       <c r="D139" t="str">
-        <v>159ms</v>
+        <v>665ms</v>
       </c>
     </row>
     <row r="140">
@@ -2356,7 +2356,7 @@
         <v>UI Validation Automated Verification Case #30</v>
       </c>
       <c r="D140" t="str">
-        <v>849ms</v>
+        <v>284ms</v>
       </c>
     </row>
     <row r="141">
@@ -2370,7 +2370,7 @@
         <v>UI Validation Automated Verification Case #31</v>
       </c>
       <c r="D141" t="str">
-        <v>545ms</v>
+        <v>155ms</v>
       </c>
     </row>
     <row r="142">
@@ -2384,7 +2384,7 @@
         <v>UI Validation Automated Verification Case #32</v>
       </c>
       <c r="D142" t="str">
-        <v>180ms</v>
+        <v>825ms</v>
       </c>
     </row>
     <row r="143">
@@ -2398,7 +2398,7 @@
         <v>UI Validation Automated Verification Case #33</v>
       </c>
       <c r="D143" t="str">
-        <v>579ms</v>
+        <v>773ms</v>
       </c>
     </row>
     <row r="144">
@@ -2412,7 +2412,7 @@
         <v>UI Validation Automated Verification Case #34</v>
       </c>
       <c r="D144" t="str">
-        <v>866ms</v>
+        <v>651ms</v>
       </c>
     </row>
     <row r="145">
@@ -2426,7 +2426,7 @@
         <v>UI Validation Automated Verification Case #35</v>
       </c>
       <c r="D145" t="str">
-        <v>783ms</v>
+        <v>592ms</v>
       </c>
     </row>
     <row r="146">
@@ -2440,7 +2440,7 @@
         <v>UI Validation Automated Verification Case #36</v>
       </c>
       <c r="D146" t="str">
-        <v>316ms</v>
+        <v>851ms</v>
       </c>
     </row>
     <row r="147">
@@ -2454,7 +2454,7 @@
         <v>UI Validation Automated Verification Case #37</v>
       </c>
       <c r="D147" t="str">
-        <v>148ms</v>
+        <v>851ms</v>
       </c>
     </row>
     <row r="148">
@@ -2468,7 +2468,7 @@
         <v>UI Validation Automated Verification Case #38</v>
       </c>
       <c r="D148" t="str">
-        <v>568ms</v>
+        <v>806ms</v>
       </c>
     </row>
     <row r="149">
@@ -2482,7 +2482,7 @@
         <v>UI Validation Automated Verification Case #39</v>
       </c>
       <c r="D149" t="str">
-        <v>239ms</v>
+        <v>460ms</v>
       </c>
     </row>
     <row r="150">
@@ -2496,7 +2496,7 @@
         <v>UI Validation Automated Verification Case #40</v>
       </c>
       <c r="D150" t="str">
-        <v>704ms</v>
+        <v>212ms</v>
       </c>
     </row>
     <row r="151">
@@ -2510,7 +2510,7 @@
         <v>UI Validation Automated Verification Case #41</v>
       </c>
       <c r="D151" t="str">
-        <v>415ms</v>
+        <v>796ms</v>
       </c>
     </row>
     <row r="152">
@@ -2524,7 +2524,7 @@
         <v>UI Validation Automated Verification Case #42</v>
       </c>
       <c r="D152" t="str">
-        <v>535ms</v>
+        <v>653ms</v>
       </c>
     </row>
     <row r="153">
@@ -2538,7 +2538,7 @@
         <v>UI Validation Automated Verification Case #43</v>
       </c>
       <c r="D153" t="str">
-        <v>287ms</v>
+        <v>496ms</v>
       </c>
     </row>
     <row r="154">
@@ -2552,7 +2552,7 @@
         <v>UI Validation Automated Verification Case #44</v>
       </c>
       <c r="D154" t="str">
-        <v>244ms</v>
+        <v>776ms</v>
       </c>
     </row>
     <row r="155">
@@ -2566,7 +2566,7 @@
         <v>UI Validation Automated Verification Case #45</v>
       </c>
       <c r="D155" t="str">
-        <v>548ms</v>
+        <v>743ms</v>
       </c>
     </row>
     <row r="156">
@@ -2580,7 +2580,7 @@
         <v>UI Validation Automated Verification Case #46</v>
       </c>
       <c r="D156" t="str">
-        <v>258ms</v>
+        <v>474ms</v>
       </c>
     </row>
     <row r="157">
@@ -2594,7 +2594,7 @@
         <v>UI Validation Automated Verification Case #47</v>
       </c>
       <c r="D157" t="str">
-        <v>734ms</v>
+        <v>106ms</v>
       </c>
     </row>
     <row r="158">
@@ -2608,7 +2608,7 @@
         <v>UI Validation Automated Verification Case #48</v>
       </c>
       <c r="D158" t="str">
-        <v>491ms</v>
+        <v>747ms</v>
       </c>
     </row>
     <row r="159">
@@ -2622,7 +2622,7 @@
         <v>UI Validation Automated Verification Case #49</v>
       </c>
       <c r="D159" t="str">
-        <v>876ms</v>
+        <v>210ms</v>
       </c>
     </row>
     <row r="160">
@@ -2636,7 +2636,7 @@
         <v>UI Validation Automated Verification Case #50</v>
       </c>
       <c r="D160" t="str">
-        <v>523ms</v>
+        <v>292ms</v>
       </c>
     </row>
     <row r="161">
@@ -2650,7 +2650,7 @@
         <v>Forms Automated Verification Case #1</v>
       </c>
       <c r="D161" t="str">
-        <v>493ms</v>
+        <v>865ms</v>
       </c>
     </row>
     <row r="162">
@@ -2664,7 +2664,7 @@
         <v>Forms Automated Verification Case #2</v>
       </c>
       <c r="D162" t="str">
-        <v>413ms</v>
+        <v>260ms</v>
       </c>
     </row>
     <row r="163">
@@ -2678,7 +2678,7 @@
         <v>Forms Automated Verification Case #3</v>
       </c>
       <c r="D163" t="str">
-        <v>415ms</v>
+        <v>341ms</v>
       </c>
     </row>
     <row r="164">
@@ -2692,7 +2692,7 @@
         <v>Forms Automated Verification Case #4</v>
       </c>
       <c r="D164" t="str">
-        <v>207ms</v>
+        <v>714ms</v>
       </c>
     </row>
     <row r="165">
@@ -2706,7 +2706,7 @@
         <v>Forms Automated Verification Case #5</v>
       </c>
       <c r="D165" t="str">
-        <v>276ms</v>
+        <v>457ms</v>
       </c>
     </row>
     <row r="166">
@@ -2720,7 +2720,7 @@
         <v>Forms Automated Verification Case #6</v>
       </c>
       <c r="D166" t="str">
-        <v>876ms</v>
+        <v>571ms</v>
       </c>
     </row>
     <row r="167">
@@ -2734,7 +2734,7 @@
         <v>Forms Automated Verification Case #7</v>
       </c>
       <c r="D167" t="str">
-        <v>174ms</v>
+        <v>253ms</v>
       </c>
     </row>
     <row r="168">
@@ -2748,7 +2748,7 @@
         <v>Forms Automated Verification Case #8</v>
       </c>
       <c r="D168" t="str">
-        <v>106ms</v>
+        <v>353ms</v>
       </c>
     </row>
     <row r="169">
@@ -2762,7 +2762,7 @@
         <v>Forms Automated Verification Case #9</v>
       </c>
       <c r="D169" t="str">
-        <v>383ms</v>
+        <v>827ms</v>
       </c>
     </row>
     <row r="170">
@@ -2776,7 +2776,7 @@
         <v>Forms Automated Verification Case #10</v>
       </c>
       <c r="D170" t="str">
-        <v>777ms</v>
+        <v>680ms</v>
       </c>
     </row>
     <row r="171">
@@ -2790,7 +2790,7 @@
         <v>Forms Automated Verification Case #11</v>
       </c>
       <c r="D171" t="str">
-        <v>634ms</v>
+        <v>115ms</v>
       </c>
     </row>
     <row r="172">
@@ -2804,7 +2804,7 @@
         <v>Forms Automated Verification Case #12</v>
       </c>
       <c r="D172" t="str">
-        <v>204ms</v>
+        <v>149ms</v>
       </c>
     </row>
     <row r="173">
@@ -2818,7 +2818,7 @@
         <v>Forms Automated Verification Case #13</v>
       </c>
       <c r="D173" t="str">
-        <v>809ms</v>
+        <v>736ms</v>
       </c>
     </row>
     <row r="174">
@@ -2832,7 +2832,7 @@
         <v>Forms Automated Verification Case #14</v>
       </c>
       <c r="D174" t="str">
-        <v>225ms</v>
+        <v>608ms</v>
       </c>
     </row>
     <row r="175">
@@ -2846,7 +2846,7 @@
         <v>Forms Automated Verification Case #15</v>
       </c>
       <c r="D175" t="str">
-        <v>351ms</v>
+        <v>158ms</v>
       </c>
     </row>
     <row r="176">
@@ -2860,7 +2860,7 @@
         <v>Forms Automated Verification Case #16</v>
       </c>
       <c r="D176" t="str">
-        <v>349ms</v>
+        <v>181ms</v>
       </c>
     </row>
     <row r="177">
@@ -2874,7 +2874,7 @@
         <v>Forms Automated Verification Case #17</v>
       </c>
       <c r="D177" t="str">
-        <v>240ms</v>
+        <v>439ms</v>
       </c>
     </row>
     <row r="178">
@@ -2888,7 +2888,7 @@
         <v>Forms Automated Verification Case #18</v>
       </c>
       <c r="D178" t="str">
-        <v>802ms</v>
+        <v>571ms</v>
       </c>
     </row>
     <row r="179">
@@ -2902,7 +2902,7 @@
         <v>Forms Automated Verification Case #19</v>
       </c>
       <c r="D179" t="str">
-        <v>427ms</v>
+        <v>671ms</v>
       </c>
     </row>
     <row r="180">
@@ -2916,7 +2916,7 @@
         <v>Forms Automated Verification Case #20</v>
       </c>
       <c r="D180" t="str">
-        <v>200ms</v>
+        <v>120ms</v>
       </c>
     </row>
     <row r="181">
@@ -2930,7 +2930,7 @@
         <v>Forms Automated Verification Case #21</v>
       </c>
       <c r="D181" t="str">
-        <v>185ms</v>
+        <v>398ms</v>
       </c>
     </row>
     <row r="182">
@@ -2944,7 +2944,7 @@
         <v>Forms Automated Verification Case #22</v>
       </c>
       <c r="D182" t="str">
-        <v>446ms</v>
+        <v>681ms</v>
       </c>
     </row>
     <row r="183">
@@ -2958,7 +2958,7 @@
         <v>Forms Automated Verification Case #23</v>
       </c>
       <c r="D183" t="str">
-        <v>812ms</v>
+        <v>305ms</v>
       </c>
     </row>
     <row r="184">
@@ -2972,7 +2972,7 @@
         <v>Forms Automated Verification Case #24</v>
       </c>
       <c r="D184" t="str">
-        <v>639ms</v>
+        <v>198ms</v>
       </c>
     </row>
     <row r="185">
@@ -2986,7 +2986,7 @@
         <v>Forms Automated Verification Case #25</v>
       </c>
       <c r="D185" t="str">
-        <v>698ms</v>
+        <v>187ms</v>
       </c>
     </row>
     <row r="186">
@@ -3000,7 +3000,7 @@
         <v>Forms Automated Verification Case #26</v>
       </c>
       <c r="D186" t="str">
-        <v>768ms</v>
+        <v>703ms</v>
       </c>
     </row>
     <row r="187">
@@ -3014,7 +3014,7 @@
         <v>Forms Automated Verification Case #27</v>
       </c>
       <c r="D187" t="str">
-        <v>295ms</v>
+        <v>265ms</v>
       </c>
     </row>
     <row r="188">
@@ -3028,7 +3028,7 @@
         <v>Forms Automated Verification Case #28</v>
       </c>
       <c r="D188" t="str">
-        <v>219ms</v>
+        <v>145ms</v>
       </c>
     </row>
     <row r="189">
@@ -3042,7 +3042,7 @@
         <v>Forms Automated Verification Case #29</v>
       </c>
       <c r="D189" t="str">
-        <v>705ms</v>
+        <v>120ms</v>
       </c>
     </row>
     <row r="190">
@@ -3056,7 +3056,7 @@
         <v>Forms Automated Verification Case #30</v>
       </c>
       <c r="D190" t="str">
-        <v>158ms</v>
+        <v>203ms</v>
       </c>
     </row>
     <row r="191">
@@ -3070,7 +3070,7 @@
         <v>Forms Automated Verification Case #31</v>
       </c>
       <c r="D191" t="str">
-        <v>220ms</v>
+        <v>714ms</v>
       </c>
     </row>
     <row r="192">
@@ -3084,7 +3084,7 @@
         <v>Forms Automated Verification Case #32</v>
       </c>
       <c r="D192" t="str">
-        <v>732ms</v>
+        <v>392ms</v>
       </c>
     </row>
     <row r="193">
@@ -3098,7 +3098,7 @@
         <v>Forms Automated Verification Case #33</v>
       </c>
       <c r="D193" t="str">
-        <v>149ms</v>
+        <v>743ms</v>
       </c>
     </row>
     <row r="194">
@@ -3112,7 +3112,7 @@
         <v>Forms Automated Verification Case #34</v>
       </c>
       <c r="D194" t="str">
-        <v>618ms</v>
+        <v>185ms</v>
       </c>
     </row>
     <row r="195">
@@ -3126,7 +3126,7 @@
         <v>Forms Automated Verification Case #35</v>
       </c>
       <c r="D195" t="str">
-        <v>325ms</v>
+        <v>442ms</v>
       </c>
     </row>
     <row r="196">
@@ -3140,7 +3140,7 @@
         <v>Forms Automated Verification Case #36</v>
       </c>
       <c r="D196" t="str">
-        <v>452ms</v>
+        <v>799ms</v>
       </c>
     </row>
     <row r="197">
@@ -3154,7 +3154,7 @@
         <v>Forms Automated Verification Case #37</v>
       </c>
       <c r="D197" t="str">
-        <v>323ms</v>
+        <v>137ms</v>
       </c>
     </row>
     <row r="198">
@@ -3168,7 +3168,7 @@
         <v>Forms Automated Verification Case #38</v>
       </c>
       <c r="D198" t="str">
-        <v>489ms</v>
+        <v>251ms</v>
       </c>
     </row>
     <row r="199">
@@ -3182,7 +3182,7 @@
         <v>Forms Automated Verification Case #39</v>
       </c>
       <c r="D199" t="str">
-        <v>287ms</v>
+        <v>490ms</v>
       </c>
     </row>
     <row r="200">
@@ -3196,7 +3196,7 @@
         <v>Forms Automated Verification Case #40</v>
       </c>
       <c r="D200" t="str">
-        <v>101ms</v>
+        <v>468ms</v>
       </c>
     </row>
     <row r="201">
@@ -3210,7 +3210,7 @@
         <v>Forms Automated Verification Case #41</v>
       </c>
       <c r="D201" t="str">
-        <v>486ms</v>
+        <v>445ms</v>
       </c>
     </row>
     <row r="202">
@@ -3224,7 +3224,7 @@
         <v>Forms Automated Verification Case #42</v>
       </c>
       <c r="D202" t="str">
-        <v>430ms</v>
+        <v>170ms</v>
       </c>
     </row>
     <row r="203">
@@ -3238,7 +3238,7 @@
         <v>Forms Automated Verification Case #43</v>
       </c>
       <c r="D203" t="str">
-        <v>633ms</v>
+        <v>663ms</v>
       </c>
     </row>
     <row r="204">
@@ -3252,7 +3252,7 @@
         <v>Forms Automated Verification Case #44</v>
       </c>
       <c r="D204" t="str">
-        <v>689ms</v>
+        <v>823ms</v>
       </c>
     </row>
     <row r="205">
@@ -3266,7 +3266,7 @@
         <v>Forms Automated Verification Case #45</v>
       </c>
       <c r="D205" t="str">
-        <v>398ms</v>
+        <v>579ms</v>
       </c>
     </row>
     <row r="206">
@@ -3280,7 +3280,7 @@
         <v>Forms Automated Verification Case #46</v>
       </c>
       <c r="D206" t="str">
-        <v>314ms</v>
+        <v>841ms</v>
       </c>
     </row>
     <row r="207">
@@ -3294,7 +3294,7 @@
         <v>Forms Automated Verification Case #47</v>
       </c>
       <c r="D207" t="str">
-        <v>258ms</v>
+        <v>631ms</v>
       </c>
     </row>
     <row r="208">
@@ -3308,7 +3308,7 @@
         <v>Forms Automated Verification Case #48</v>
       </c>
       <c r="D208" t="str">
-        <v>590ms</v>
+        <v>262ms</v>
       </c>
     </row>
     <row r="209">
@@ -3322,7 +3322,7 @@
         <v>Forms Automated Verification Case #49</v>
       </c>
       <c r="D209" t="str">
-        <v>333ms</v>
+        <v>392ms</v>
       </c>
     </row>
     <row r="210">
@@ -3336,7 +3336,7 @@
         <v>Forms Automated Verification Case #50</v>
       </c>
       <c r="D210" t="str">
-        <v>670ms</v>
+        <v>720ms</v>
       </c>
     </row>
     <row r="211">
@@ -3350,7 +3350,7 @@
         <v>CRUD Operations Automated Verification Case #2</v>
       </c>
       <c r="D211" t="str">
-        <v>148ms</v>
+        <v>409ms</v>
       </c>
     </row>
     <row r="212">
@@ -3364,7 +3364,7 @@
         <v>CRUD Operations Automated Verification Case #3</v>
       </c>
       <c r="D212" t="str">
-        <v>203ms</v>
+        <v>346ms</v>
       </c>
     </row>
     <row r="213">
@@ -3378,7 +3378,7 @@
         <v>CRUD Operations Automated Verification Case #4</v>
       </c>
       <c r="D213" t="str">
-        <v>792ms</v>
+        <v>476ms</v>
       </c>
     </row>
     <row r="214">
@@ -3392,7 +3392,7 @@
         <v>CRUD Operations Automated Verification Case #5</v>
       </c>
       <c r="D214" t="str">
-        <v>269ms</v>
+        <v>720ms</v>
       </c>
     </row>
     <row r="215">
@@ -3406,7 +3406,7 @@
         <v>CRUD Operations Automated Verification Case #6</v>
       </c>
       <c r="D215" t="str">
-        <v>638ms</v>
+        <v>766ms</v>
       </c>
     </row>
     <row r="216">
@@ -3420,7 +3420,7 @@
         <v>CRUD Operations Automated Verification Case #7</v>
       </c>
       <c r="D216" t="str">
-        <v>348ms</v>
+        <v>832ms</v>
       </c>
     </row>
     <row r="217">
@@ -3434,7 +3434,7 @@
         <v>CRUD Operations Automated Verification Case #8</v>
       </c>
       <c r="D217" t="str">
-        <v>462ms</v>
+        <v>421ms</v>
       </c>
     </row>
     <row r="218">
@@ -3448,7 +3448,7 @@
         <v>CRUD Operations Automated Verification Case #9</v>
       </c>
       <c r="D218" t="str">
-        <v>375ms</v>
+        <v>198ms</v>
       </c>
     </row>
     <row r="219">
@@ -3462,7 +3462,7 @@
         <v>CRUD Operations Automated Verification Case #10</v>
       </c>
       <c r="D219" t="str">
-        <v>562ms</v>
+        <v>616ms</v>
       </c>
     </row>
     <row r="220">
@@ -3476,7 +3476,7 @@
         <v>CRUD Operations Automated Verification Case #11</v>
       </c>
       <c r="D220" t="str">
-        <v>293ms</v>
+        <v>470ms</v>
       </c>
     </row>
     <row r="221">
@@ -3490,7 +3490,7 @@
         <v>CRUD Operations Automated Verification Case #12</v>
       </c>
       <c r="D221" t="str">
-        <v>299ms</v>
+        <v>832ms</v>
       </c>
     </row>
     <row r="222">
@@ -3504,7 +3504,7 @@
         <v>CRUD Operations Automated Verification Case #13</v>
       </c>
       <c r="D222" t="str">
-        <v>896ms</v>
+        <v>777ms</v>
       </c>
     </row>
     <row r="223">
@@ -3518,7 +3518,7 @@
         <v>CRUD Operations Automated Verification Case #14</v>
       </c>
       <c r="D223" t="str">
-        <v>457ms</v>
+        <v>641ms</v>
       </c>
     </row>
     <row r="224">
@@ -3532,7 +3532,7 @@
         <v>CRUD Operations Automated Verification Case #15</v>
       </c>
       <c r="D224" t="str">
-        <v>156ms</v>
+        <v>382ms</v>
       </c>
     </row>
     <row r="225">
@@ -3546,7 +3546,7 @@
         <v>CRUD Operations Automated Verification Case #16</v>
       </c>
       <c r="D225" t="str">
-        <v>765ms</v>
+        <v>377ms</v>
       </c>
     </row>
     <row r="226">
@@ -3560,7 +3560,7 @@
         <v>CRUD Operations Automated Verification Case #17</v>
       </c>
       <c r="D226" t="str">
-        <v>139ms</v>
+        <v>271ms</v>
       </c>
     </row>
     <row r="227">
@@ -3574,7 +3574,7 @@
         <v>CRUD Operations Automated Verification Case #18</v>
       </c>
       <c r="D227" t="str">
-        <v>229ms</v>
+        <v>494ms</v>
       </c>
     </row>
     <row r="228">
@@ -3588,7 +3588,7 @@
         <v>CRUD Operations Automated Verification Case #19</v>
       </c>
       <c r="D228" t="str">
-        <v>523ms</v>
+        <v>407ms</v>
       </c>
     </row>
     <row r="229">
@@ -3602,7 +3602,7 @@
         <v>CRUD Operations Automated Verification Case #20</v>
       </c>
       <c r="D229" t="str">
-        <v>307ms</v>
+        <v>409ms</v>
       </c>
     </row>
     <row r="230">
@@ -3616,7 +3616,7 @@
         <v>CRUD Operations Automated Verification Case #21</v>
       </c>
       <c r="D230" t="str">
-        <v>241ms</v>
+        <v>760ms</v>
       </c>
     </row>
     <row r="231">
@@ -3630,7 +3630,7 @@
         <v>CRUD Operations Automated Verification Case #22</v>
       </c>
       <c r="D231" t="str">
-        <v>517ms</v>
+        <v>335ms</v>
       </c>
     </row>
     <row r="232">
@@ -3644,7 +3644,7 @@
         <v>CRUD Operations Automated Verification Case #23</v>
       </c>
       <c r="D232" t="str">
-        <v>313ms</v>
+        <v>231ms</v>
       </c>
     </row>
     <row r="233">
@@ -3658,7 +3658,7 @@
         <v>CRUD Operations Automated Verification Case #24</v>
       </c>
       <c r="D233" t="str">
-        <v>528ms</v>
+        <v>666ms</v>
       </c>
     </row>
     <row r="234">
@@ -3672,7 +3672,7 @@
         <v>CRUD Operations Automated Verification Case #25</v>
       </c>
       <c r="D234" t="str">
-        <v>770ms</v>
+        <v>898ms</v>
       </c>
     </row>
     <row r="235">
@@ -3686,7 +3686,7 @@
         <v>CRUD Operations Automated Verification Case #26</v>
       </c>
       <c r="D235" t="str">
-        <v>492ms</v>
+        <v>189ms</v>
       </c>
     </row>
     <row r="236">
@@ -3700,7 +3700,7 @@
         <v>CRUD Operations Automated Verification Case #27</v>
       </c>
       <c r="D236" t="str">
-        <v>760ms</v>
+        <v>285ms</v>
       </c>
     </row>
     <row r="237">
@@ -3714,7 +3714,7 @@
         <v>CRUD Operations Automated Verification Case #28</v>
       </c>
       <c r="D237" t="str">
-        <v>848ms</v>
+        <v>330ms</v>
       </c>
     </row>
     <row r="238">
@@ -3728,7 +3728,7 @@
         <v>CRUD Operations Automated Verification Case #29</v>
       </c>
       <c r="D238" t="str">
-        <v>856ms</v>
+        <v>301ms</v>
       </c>
     </row>
     <row r="239">
@@ -3742,7 +3742,7 @@
         <v>CRUD Operations Automated Verification Case #30</v>
       </c>
       <c r="D239" t="str">
-        <v>384ms</v>
+        <v>146ms</v>
       </c>
     </row>
     <row r="240">
@@ -3756,7 +3756,7 @@
         <v>CRUD Operations Automated Verification Case #31</v>
       </c>
       <c r="D240" t="str">
-        <v>868ms</v>
+        <v>220ms</v>
       </c>
     </row>
     <row r="241">
@@ -3770,7 +3770,7 @@
         <v>CRUD Operations Automated Verification Case #32</v>
       </c>
       <c r="D241" t="str">
-        <v>134ms</v>
+        <v>388ms</v>
       </c>
     </row>
     <row r="242">
@@ -3784,7 +3784,7 @@
         <v>CRUD Operations Automated Verification Case #33</v>
       </c>
       <c r="D242" t="str">
-        <v>205ms</v>
+        <v>180ms</v>
       </c>
     </row>
     <row r="243">
@@ -3798,7 +3798,7 @@
         <v>CRUD Operations Automated Verification Case #34</v>
       </c>
       <c r="D243" t="str">
-        <v>150ms</v>
+        <v>655ms</v>
       </c>
     </row>
     <row r="244">
@@ -3812,7 +3812,7 @@
         <v>CRUD Operations Automated Verification Case #35</v>
       </c>
       <c r="D244" t="str">
-        <v>146ms</v>
+        <v>812ms</v>
       </c>
     </row>
     <row r="245">
@@ -3826,7 +3826,7 @@
         <v>CRUD Operations Automated Verification Case #36</v>
       </c>
       <c r="D245" t="str">
-        <v>462ms</v>
+        <v>385ms</v>
       </c>
     </row>
     <row r="246">
@@ -3840,7 +3840,7 @@
         <v>CRUD Operations Automated Verification Case #37</v>
       </c>
       <c r="D246" t="str">
-        <v>680ms</v>
+        <v>589ms</v>
       </c>
     </row>
     <row r="247">
@@ -3854,7 +3854,7 @@
         <v>CRUD Operations Automated Verification Case #38</v>
       </c>
       <c r="D247" t="str">
-        <v>197ms</v>
+        <v>209ms</v>
       </c>
     </row>
     <row r="248">
@@ -3868,7 +3868,7 @@
         <v>CRUD Operations Automated Verification Case #39</v>
       </c>
       <c r="D248" t="str">
-        <v>714ms</v>
+        <v>881ms</v>
       </c>
     </row>
     <row r="249">
@@ -3882,7 +3882,7 @@
         <v>CRUD Operations Automated Verification Case #40</v>
       </c>
       <c r="D249" t="str">
-        <v>423ms</v>
+        <v>450ms</v>
       </c>
     </row>
     <row r="250">
@@ -3896,7 +3896,7 @@
         <v>CRUD Operations Automated Verification Case #41</v>
       </c>
       <c r="D250" t="str">
-        <v>557ms</v>
+        <v>422ms</v>
       </c>
     </row>
     <row r="251">
@@ -3910,7 +3910,7 @@
         <v>CRUD Operations Automated Verification Case #42</v>
       </c>
       <c r="D251" t="str">
-        <v>814ms</v>
+        <v>700ms</v>
       </c>
     </row>
     <row r="252">
@@ -3924,7 +3924,7 @@
         <v>CRUD Operations Automated Verification Case #43</v>
       </c>
       <c r="D252" t="str">
-        <v>181ms</v>
+        <v>491ms</v>
       </c>
     </row>
     <row r="253">
@@ -3938,7 +3938,7 @@
         <v>CRUD Operations Automated Verification Case #44</v>
       </c>
       <c r="D253" t="str">
-        <v>338ms</v>
+        <v>403ms</v>
       </c>
     </row>
     <row r="254">
@@ -3952,7 +3952,7 @@
         <v>CRUD Operations Automated Verification Case #45</v>
       </c>
       <c r="D254" t="str">
-        <v>449ms</v>
+        <v>587ms</v>
       </c>
     </row>
     <row r="255">
@@ -3966,7 +3966,7 @@
         <v>CRUD Operations Automated Verification Case #46</v>
       </c>
       <c r="D255" t="str">
-        <v>813ms</v>
+        <v>681ms</v>
       </c>
     </row>
     <row r="256">
@@ -3980,7 +3980,7 @@
         <v>CRUD Operations Automated Verification Case #47</v>
       </c>
       <c r="D256" t="str">
-        <v>576ms</v>
+        <v>838ms</v>
       </c>
     </row>
     <row r="257">
@@ -3994,7 +3994,7 @@
         <v>CRUD Operations Automated Verification Case #48</v>
       </c>
       <c r="D257" t="str">
-        <v>589ms</v>
+        <v>637ms</v>
       </c>
     </row>
     <row r="258">
@@ -4008,7 +4008,7 @@
         <v>CRUD Operations Automated Verification Case #49</v>
       </c>
       <c r="D258" t="str">
-        <v>631ms</v>
+        <v>235ms</v>
       </c>
     </row>
     <row r="259">
@@ -4022,7 +4022,7 @@
         <v>CRUD Operations Automated Verification Case #50</v>
       </c>
       <c r="D259" t="str">
-        <v>256ms</v>
+        <v>180ms</v>
       </c>
     </row>
     <row r="260">
@@ -4036,7 +4036,7 @@
         <v>Input Validation Automated Verification Case #1</v>
       </c>
       <c r="D260" t="str">
-        <v>563ms</v>
+        <v>440ms</v>
       </c>
     </row>
     <row r="261">
@@ -4050,7 +4050,7 @@
         <v>Input Validation Automated Verification Case #2</v>
       </c>
       <c r="D261" t="str">
-        <v>260ms</v>
+        <v>649ms</v>
       </c>
     </row>
     <row r="262">
@@ -4064,7 +4064,7 @@
         <v>Input Validation Automated Verification Case #3</v>
       </c>
       <c r="D262" t="str">
-        <v>740ms</v>
+        <v>842ms</v>
       </c>
     </row>
     <row r="263">
@@ -4078,7 +4078,7 @@
         <v>Input Validation Automated Verification Case #4</v>
       </c>
       <c r="D263" t="str">
-        <v>861ms</v>
+        <v>835ms</v>
       </c>
     </row>
     <row r="264">
@@ -4092,7 +4092,7 @@
         <v>Input Validation Automated Verification Case #5</v>
       </c>
       <c r="D264" t="str">
-        <v>109ms</v>
+        <v>643ms</v>
       </c>
     </row>
     <row r="265">
@@ -4106,7 +4106,7 @@
         <v>Input Validation Automated Verification Case #6</v>
       </c>
       <c r="D265" t="str">
-        <v>499ms</v>
+        <v>403ms</v>
       </c>
     </row>
     <row r="266">
@@ -4120,1978 +4120,1978 @@
         <v>Input Validation Automated Verification Case #7</v>
       </c>
       <c r="D266" t="str">
-        <v>753ms</v>
+        <v>347ms</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>TC_WEB_VAL_009</v>
+        <v>TC_WEB_VAL_008</v>
       </c>
       <c r="B267" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C267" t="str">
-        <v>Input Validation Automated Verification Case #9</v>
+        <v>Input Validation Automated Verification Case #8</v>
       </c>
       <c r="D267" t="str">
-        <v>700ms</v>
+        <v>270ms</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>TC_WEB_VAL_010</v>
+        <v>TC_WEB_VAL_009</v>
       </c>
       <c r="B268" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C268" t="str">
-        <v>Input Validation Automated Verification Case #10</v>
+        <v>Input Validation Automated Verification Case #9</v>
       </c>
       <c r="D268" t="str">
-        <v>451ms</v>
+        <v>435ms</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>TC_WEB_VAL_011</v>
+        <v>TC_WEB_VAL_010</v>
       </c>
       <c r="B269" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C269" t="str">
-        <v>Input Validation Automated Verification Case #11</v>
+        <v>Input Validation Automated Verification Case #10</v>
       </c>
       <c r="D269" t="str">
-        <v>410ms</v>
+        <v>201ms</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>TC_WEB_VAL_012</v>
+        <v>TC_WEB_VAL_011</v>
       </c>
       <c r="B270" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C270" t="str">
-        <v>Input Validation Automated Verification Case #12</v>
+        <v>Input Validation Automated Verification Case #11</v>
       </c>
       <c r="D270" t="str">
-        <v>123ms</v>
+        <v>652ms</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>TC_WEB_VAL_013</v>
+        <v>TC_WEB_VAL_012</v>
       </c>
       <c r="B271" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C271" t="str">
-        <v>Input Validation Automated Verification Case #13</v>
+        <v>Input Validation Automated Verification Case #12</v>
       </c>
       <c r="D271" t="str">
-        <v>318ms</v>
+        <v>401ms</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>TC_WEB_VAL_014</v>
+        <v>TC_WEB_VAL_013</v>
       </c>
       <c r="B272" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C272" t="str">
-        <v>Input Validation Automated Verification Case #14</v>
+        <v>Input Validation Automated Verification Case #13</v>
       </c>
       <c r="D272" t="str">
-        <v>304ms</v>
+        <v>527ms</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>TC_WEB_VAL_015</v>
+        <v>TC_WEB_VAL_014</v>
       </c>
       <c r="B273" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C273" t="str">
-        <v>Input Validation Automated Verification Case #15</v>
+        <v>Input Validation Automated Verification Case #14</v>
       </c>
       <c r="D273" t="str">
-        <v>748ms</v>
+        <v>145ms</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>TC_WEB_VAL_016</v>
+        <v>TC_WEB_VAL_015</v>
       </c>
       <c r="B274" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C274" t="str">
-        <v>Input Validation Automated Verification Case #16</v>
+        <v>Input Validation Automated Verification Case #15</v>
       </c>
       <c r="D274" t="str">
-        <v>605ms</v>
+        <v>250ms</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>TC_WEB_VAL_017</v>
+        <v>TC_WEB_VAL_016</v>
       </c>
       <c r="B275" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C275" t="str">
-        <v>Input Validation Automated Verification Case #17</v>
+        <v>Input Validation Automated Verification Case #16</v>
       </c>
       <c r="D275" t="str">
-        <v>269ms</v>
+        <v>491ms</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>TC_WEB_VAL_018</v>
+        <v>TC_WEB_VAL_017</v>
       </c>
       <c r="B276" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C276" t="str">
-        <v>Input Validation Automated Verification Case #18</v>
+        <v>Input Validation Automated Verification Case #17</v>
       </c>
       <c r="D276" t="str">
-        <v>635ms</v>
+        <v>503ms</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>TC_WEB_VAL_019</v>
+        <v>TC_WEB_VAL_018</v>
       </c>
       <c r="B277" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C277" t="str">
-        <v>Input Validation Automated Verification Case #19</v>
+        <v>Input Validation Automated Verification Case #18</v>
       </c>
       <c r="D277" t="str">
-        <v>500ms</v>
+        <v>322ms</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>TC_WEB_VAL_020</v>
+        <v>TC_WEB_VAL_019</v>
       </c>
       <c r="B278" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C278" t="str">
-        <v>Input Validation Automated Verification Case #20</v>
+        <v>Input Validation Automated Verification Case #19</v>
       </c>
       <c r="D278" t="str">
-        <v>756ms</v>
+        <v>801ms</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>TC_WEB_VAL_021</v>
+        <v>TC_WEB_VAL_020</v>
       </c>
       <c r="B279" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C279" t="str">
-        <v>Input Validation Automated Verification Case #21</v>
+        <v>Input Validation Automated Verification Case #20</v>
       </c>
       <c r="D279" t="str">
-        <v>790ms</v>
+        <v>507ms</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>TC_WEB_VAL_022</v>
+        <v>TC_WEB_VAL_021</v>
       </c>
       <c r="B280" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C280" t="str">
-        <v>Input Validation Automated Verification Case #22</v>
+        <v>Input Validation Automated Verification Case #21</v>
       </c>
       <c r="D280" t="str">
-        <v>640ms</v>
+        <v>257ms</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>TC_WEB_VAL_023</v>
+        <v>TC_WEB_VAL_022</v>
       </c>
       <c r="B281" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C281" t="str">
-        <v>Input Validation Automated Verification Case #23</v>
+        <v>Input Validation Automated Verification Case #22</v>
       </c>
       <c r="D281" t="str">
-        <v>821ms</v>
+        <v>322ms</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>TC_WEB_VAL_024</v>
+        <v>TC_WEB_VAL_023</v>
       </c>
       <c r="B282" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C282" t="str">
-        <v>Input Validation Automated Verification Case #24</v>
+        <v>Input Validation Automated Verification Case #23</v>
       </c>
       <c r="D282" t="str">
-        <v>550ms</v>
+        <v>789ms</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>TC_WEB_VAL_025</v>
+        <v>TC_WEB_VAL_024</v>
       </c>
       <c r="B283" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C283" t="str">
-        <v>Input Validation Automated Verification Case #25</v>
+        <v>Input Validation Automated Verification Case #24</v>
       </c>
       <c r="D283" t="str">
-        <v>449ms</v>
+        <v>364ms</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>TC_WEB_VAL_026</v>
+        <v>TC_WEB_VAL_025</v>
       </c>
       <c r="B284" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C284" t="str">
-        <v>Input Validation Automated Verification Case #26</v>
+        <v>Input Validation Automated Verification Case #25</v>
       </c>
       <c r="D284" t="str">
-        <v>606ms</v>
+        <v>589ms</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>TC_WEB_VAL_027</v>
+        <v>TC_WEB_VAL_026</v>
       </c>
       <c r="B285" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C285" t="str">
-        <v>Input Validation Automated Verification Case #27</v>
+        <v>Input Validation Automated Verification Case #26</v>
       </c>
       <c r="D285" t="str">
-        <v>740ms</v>
+        <v>719ms</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>TC_WEB_VAL_028</v>
+        <v>TC_WEB_VAL_027</v>
       </c>
       <c r="B286" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C286" t="str">
-        <v>Input Validation Automated Verification Case #28</v>
+        <v>Input Validation Automated Verification Case #27</v>
       </c>
       <c r="D286" t="str">
-        <v>336ms</v>
+        <v>692ms</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>TC_WEB_VAL_029</v>
+        <v>TC_WEB_VAL_028</v>
       </c>
       <c r="B287" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C287" t="str">
-        <v>Input Validation Automated Verification Case #29</v>
+        <v>Input Validation Automated Verification Case #28</v>
       </c>
       <c r="D287" t="str">
-        <v>632ms</v>
+        <v>265ms</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>TC_WEB_VAL_030</v>
+        <v>TC_WEB_VAL_029</v>
       </c>
       <c r="B288" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C288" t="str">
-        <v>Input Validation Automated Verification Case #30</v>
+        <v>Input Validation Automated Verification Case #29</v>
       </c>
       <c r="D288" t="str">
-        <v>663ms</v>
+        <v>478ms</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>TC_WEB_VAL_031</v>
+        <v>TC_WEB_VAL_030</v>
       </c>
       <c r="B289" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C289" t="str">
-        <v>Input Validation Automated Verification Case #31</v>
+        <v>Input Validation Automated Verification Case #30</v>
       </c>
       <c r="D289" t="str">
-        <v>206ms</v>
+        <v>619ms</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>TC_WEB_VAL_032</v>
+        <v>TC_WEB_VAL_031</v>
       </c>
       <c r="B290" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C290" t="str">
-        <v>Input Validation Automated Verification Case #32</v>
+        <v>Input Validation Automated Verification Case #31</v>
       </c>
       <c r="D290" t="str">
-        <v>222ms</v>
+        <v>286ms</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>TC_WEB_VAL_033</v>
+        <v>TC_WEB_VAL_032</v>
       </c>
       <c r="B291" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C291" t="str">
-        <v>Input Validation Automated Verification Case #33</v>
+        <v>Input Validation Automated Verification Case #32</v>
       </c>
       <c r="D291" t="str">
-        <v>139ms</v>
+        <v>405ms</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>TC_WEB_VAL_034</v>
+        <v>TC_WEB_VAL_033</v>
       </c>
       <c r="B292" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C292" t="str">
-        <v>Input Validation Automated Verification Case #34</v>
+        <v>Input Validation Automated Verification Case #33</v>
       </c>
       <c r="D292" t="str">
-        <v>226ms</v>
+        <v>792ms</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>TC_WEB_VAL_035</v>
+        <v>TC_WEB_VAL_034</v>
       </c>
       <c r="B293" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C293" t="str">
-        <v>Input Validation Automated Verification Case #35</v>
+        <v>Input Validation Automated Verification Case #34</v>
       </c>
       <c r="D293" t="str">
-        <v>274ms</v>
+        <v>608ms</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>TC_WEB_VAL_036</v>
+        <v>TC_WEB_VAL_035</v>
       </c>
       <c r="B294" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C294" t="str">
-        <v>Input Validation Automated Verification Case #36</v>
+        <v>Input Validation Automated Verification Case #35</v>
       </c>
       <c r="D294" t="str">
-        <v>776ms</v>
+        <v>670ms</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>TC_WEB_VAL_037</v>
+        <v>TC_WEB_VAL_036</v>
       </c>
       <c r="B295" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C295" t="str">
-        <v>Input Validation Automated Verification Case #37</v>
+        <v>Input Validation Automated Verification Case #36</v>
       </c>
       <c r="D295" t="str">
-        <v>554ms</v>
+        <v>845ms</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>TC_WEB_VAL_038</v>
+        <v>TC_WEB_VAL_037</v>
       </c>
       <c r="B296" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C296" t="str">
-        <v>Input Validation Automated Verification Case #38</v>
+        <v>Input Validation Automated Verification Case #37</v>
       </c>
       <c r="D296" t="str">
-        <v>444ms</v>
+        <v>752ms</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>TC_WEB_VAL_039</v>
+        <v>TC_WEB_VAL_038</v>
       </c>
       <c r="B297" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C297" t="str">
-        <v>Input Validation Automated Verification Case #39</v>
+        <v>Input Validation Automated Verification Case #38</v>
       </c>
       <c r="D297" t="str">
-        <v>335ms</v>
+        <v>234ms</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>TC_WEB_VAL_040</v>
+        <v>TC_WEB_VAL_039</v>
       </c>
       <c r="B298" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C298" t="str">
-        <v>Input Validation Automated Verification Case #40</v>
+        <v>Input Validation Automated Verification Case #39</v>
       </c>
       <c r="D298" t="str">
-        <v>551ms</v>
+        <v>508ms</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>TC_WEB_ERR_001</v>
+        <v>TC_WEB_VAL_040</v>
       </c>
       <c r="B299" t="str">
-        <v>Error Handling</v>
+        <v>Input Validation</v>
       </c>
       <c r="C299" t="str">
-        <v>Error Handling Automated Verification Case #1</v>
+        <v>Input Validation Automated Verification Case #40</v>
       </c>
       <c r="D299" t="str">
-        <v>131ms</v>
+        <v>245ms</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>TC_WEB_ERR_002</v>
+        <v>TC_WEB_ERR_001</v>
       </c>
       <c r="B300" t="str">
         <v>Error Handling</v>
       </c>
       <c r="C300" t="str">
-        <v>Error Handling Automated Verification Case #2</v>
+        <v>Error Handling Automated Verification Case #1</v>
       </c>
       <c r="D300" t="str">
-        <v>821ms</v>
+        <v>866ms</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>TC_WEB_ERR_003</v>
+        <v>TC_WEB_ERR_002</v>
       </c>
       <c r="B301" t="str">
         <v>Error Handling</v>
       </c>
       <c r="C301" t="str">
-        <v>Error Handling Automated Verification Case #3</v>
+        <v>Error Handling Automated Verification Case #2</v>
       </c>
       <c r="D301" t="str">
-        <v>797ms</v>
+        <v>782ms</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>TC_WEB_ERR_004</v>
+        <v>TC_WEB_ERR_003</v>
       </c>
       <c r="B302" t="str">
         <v>Error Handling</v>
       </c>
       <c r="C302" t="str">
-        <v>Error Handling Automated Verification Case #4</v>
+        <v>Error Handling Automated Verification Case #3</v>
       </c>
       <c r="D302" t="str">
-        <v>779ms</v>
+        <v>427ms</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>TC_WEB_ERR_005</v>
+        <v>TC_WEB_ERR_004</v>
       </c>
       <c r="B303" t="str">
         <v>Error Handling</v>
       </c>
       <c r="C303" t="str">
-        <v>Error Handling Automated Verification Case #5</v>
+        <v>Error Handling Automated Verification Case #4</v>
       </c>
       <c r="D303" t="str">
-        <v>226ms</v>
+        <v>459ms</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>TC_WEB_ERR_006</v>
+        <v>TC_WEB_ERR_005</v>
       </c>
       <c r="B304" t="str">
         <v>Error Handling</v>
       </c>
       <c r="C304" t="str">
-        <v>Error Handling Automated Verification Case #6</v>
+        <v>Error Handling Automated Verification Case #5</v>
       </c>
       <c r="D304" t="str">
-        <v>590ms</v>
+        <v>178ms</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>TC_WEB_ERR_007</v>
+        <v>TC_WEB_ERR_006</v>
       </c>
       <c r="B305" t="str">
         <v>Error Handling</v>
       </c>
       <c r="C305" t="str">
-        <v>Error Handling Automated Verification Case #7</v>
+        <v>Error Handling Automated Verification Case #6</v>
       </c>
       <c r="D305" t="str">
-        <v>491ms</v>
+        <v>876ms</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>TC_WEB_ERR_008</v>
+        <v>TC_WEB_ERR_007</v>
       </c>
       <c r="B306" t="str">
         <v>Error Handling</v>
       </c>
       <c r="C306" t="str">
-        <v>Error Handling Automated Verification Case #8</v>
+        <v>Error Handling Automated Verification Case #7</v>
       </c>
       <c r="D306" t="str">
-        <v>863ms</v>
+        <v>225ms</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>TC_WEB_ERR_009</v>
+        <v>TC_WEB_ERR_008</v>
       </c>
       <c r="B307" t="str">
         <v>Error Handling</v>
       </c>
       <c r="C307" t="str">
-        <v>Error Handling Automated Verification Case #9</v>
+        <v>Error Handling Automated Verification Case #8</v>
       </c>
       <c r="D307" t="str">
-        <v>241ms</v>
+        <v>894ms</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>TC_WEB_ERR_010</v>
+        <v>TC_WEB_ERR_009</v>
       </c>
       <c r="B308" t="str">
         <v>Error Handling</v>
       </c>
       <c r="C308" t="str">
-        <v>Error Handling Automated Verification Case #10</v>
+        <v>Error Handling Automated Verification Case #9</v>
       </c>
       <c r="D308" t="str">
-        <v>307ms</v>
+        <v>438ms</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>TC_WEB_ERR_011</v>
+        <v>TC_WEB_ERR_010</v>
       </c>
       <c r="B309" t="str">
         <v>Error Handling</v>
       </c>
       <c r="C309" t="str">
-        <v>Error Handling Automated Verification Case #11</v>
+        <v>Error Handling Automated Verification Case #10</v>
       </c>
       <c r="D309" t="str">
-        <v>788ms</v>
+        <v>723ms</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>TC_WEB_ERR_012</v>
+        <v>TC_WEB_ERR_011</v>
       </c>
       <c r="B310" t="str">
         <v>Error Handling</v>
       </c>
       <c r="C310" t="str">
-        <v>Error Handling Automated Verification Case #12</v>
+        <v>Error Handling Automated Verification Case #11</v>
       </c>
       <c r="D310" t="str">
-        <v>636ms</v>
+        <v>654ms</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>TC_WEB_ERR_013</v>
+        <v>TC_WEB_ERR_012</v>
       </c>
       <c r="B311" t="str">
         <v>Error Handling</v>
       </c>
       <c r="C311" t="str">
-        <v>Error Handling Automated Verification Case #13</v>
+        <v>Error Handling Automated Verification Case #12</v>
       </c>
       <c r="D311" t="str">
-        <v>379ms</v>
+        <v>875ms</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>TC_WEB_ERR_014</v>
+        <v>TC_WEB_ERR_013</v>
       </c>
       <c r="B312" t="str">
         <v>Error Handling</v>
       </c>
       <c r="C312" t="str">
-        <v>Error Handling Automated Verification Case #14</v>
+        <v>Error Handling Automated Verification Case #13</v>
       </c>
       <c r="D312" t="str">
-        <v>179ms</v>
+        <v>164ms</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>TC_WEB_ERR_015</v>
+        <v>TC_WEB_ERR_014</v>
       </c>
       <c r="B313" t="str">
         <v>Error Handling</v>
       </c>
       <c r="C313" t="str">
-        <v>Error Handling Automated Verification Case #15</v>
+        <v>Error Handling Automated Verification Case #14</v>
       </c>
       <c r="D313" t="str">
-        <v>658ms</v>
+        <v>445ms</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>TC_WEB_ERR_016</v>
+        <v>TC_WEB_ERR_015</v>
       </c>
       <c r="B314" t="str">
         <v>Error Handling</v>
       </c>
       <c r="C314" t="str">
-        <v>Error Handling Automated Verification Case #16</v>
+        <v>Error Handling Automated Verification Case #15</v>
       </c>
       <c r="D314" t="str">
-        <v>450ms</v>
+        <v>682ms</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>TC_WEB_ERR_017</v>
+        <v>TC_WEB_ERR_016</v>
       </c>
       <c r="B315" t="str">
         <v>Error Handling</v>
       </c>
       <c r="C315" t="str">
-        <v>Error Handling Automated Verification Case #17</v>
+        <v>Error Handling Automated Verification Case #16</v>
       </c>
       <c r="D315" t="str">
-        <v>713ms</v>
+        <v>565ms</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>TC_WEB_ERR_018</v>
+        <v>TC_WEB_ERR_017</v>
       </c>
       <c r="B316" t="str">
         <v>Error Handling</v>
       </c>
       <c r="C316" t="str">
-        <v>Error Handling Automated Verification Case #18</v>
+        <v>Error Handling Automated Verification Case #17</v>
       </c>
       <c r="D316" t="str">
-        <v>573ms</v>
+        <v>599ms</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>TC_WEB_ERR_019</v>
+        <v>TC_WEB_ERR_018</v>
       </c>
       <c r="B317" t="str">
         <v>Error Handling</v>
       </c>
       <c r="C317" t="str">
-        <v>Error Handling Automated Verification Case #19</v>
+        <v>Error Handling Automated Verification Case #18</v>
       </c>
       <c r="D317" t="str">
-        <v>861ms</v>
+        <v>301ms</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>TC_WEB_ERR_020</v>
+        <v>TC_WEB_ERR_019</v>
       </c>
       <c r="B318" t="str">
         <v>Error Handling</v>
       </c>
       <c r="C318" t="str">
-        <v>Error Handling Automated Verification Case #20</v>
+        <v>Error Handling Automated Verification Case #19</v>
       </c>
       <c r="D318" t="str">
-        <v>130ms</v>
+        <v>548ms</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>TC_WEB_SESS_001</v>
+        <v>TC_WEB_ERR_020</v>
       </c>
       <c r="B319" t="str">
-        <v>Session Management</v>
+        <v>Error Handling</v>
       </c>
       <c r="C319" t="str">
-        <v>Session Management Automated Verification Case #1</v>
+        <v>Error Handling Automated Verification Case #20</v>
       </c>
       <c r="D319" t="str">
-        <v>230ms</v>
+        <v>555ms</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>TC_WEB_SESS_002</v>
+        <v>TC_WEB_SESS_001</v>
       </c>
       <c r="B320" t="str">
         <v>Session Management</v>
       </c>
       <c r="C320" t="str">
-        <v>Session Management Automated Verification Case #2</v>
+        <v>Session Management Automated Verification Case #1</v>
       </c>
       <c r="D320" t="str">
-        <v>470ms</v>
+        <v>735ms</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>TC_WEB_SESS_003</v>
+        <v>TC_WEB_SESS_002</v>
       </c>
       <c r="B321" t="str">
         <v>Session Management</v>
       </c>
       <c r="C321" t="str">
-        <v>Session Management Automated Verification Case #3</v>
+        <v>Session Management Automated Verification Case #2</v>
       </c>
       <c r="D321" t="str">
-        <v>308ms</v>
+        <v>620ms</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>TC_WEB_SESS_004</v>
+        <v>TC_WEB_SESS_003</v>
       </c>
       <c r="B322" t="str">
         <v>Session Management</v>
       </c>
       <c r="C322" t="str">
-        <v>Session Management Automated Verification Case #4</v>
+        <v>Session Management Automated Verification Case #3</v>
       </c>
       <c r="D322" t="str">
-        <v>652ms</v>
+        <v>526ms</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>TC_WEB_SESS_005</v>
+        <v>TC_WEB_SESS_004</v>
       </c>
       <c r="B323" t="str">
         <v>Session Management</v>
       </c>
       <c r="C323" t="str">
-        <v>Session Management Automated Verification Case #5</v>
+        <v>Session Management Automated Verification Case #4</v>
       </c>
       <c r="D323" t="str">
-        <v>102ms</v>
+        <v>136ms</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>TC_WEB_SESS_006</v>
+        <v>TC_WEB_SESS_005</v>
       </c>
       <c r="B324" t="str">
         <v>Session Management</v>
       </c>
       <c r="C324" t="str">
-        <v>Session Management Automated Verification Case #6</v>
+        <v>Session Management Automated Verification Case #5</v>
       </c>
       <c r="D324" t="str">
-        <v>799ms</v>
+        <v>545ms</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>TC_WEB_SESS_007</v>
+        <v>TC_WEB_SESS_006</v>
       </c>
       <c r="B325" t="str">
         <v>Session Management</v>
       </c>
       <c r="C325" t="str">
-        <v>Session Management Automated Verification Case #7</v>
+        <v>Session Management Automated Verification Case #6</v>
       </c>
       <c r="D325" t="str">
-        <v>387ms</v>
+        <v>548ms</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>TC_WEB_SESS_008</v>
+        <v>TC_WEB_SESS_007</v>
       </c>
       <c r="B326" t="str">
         <v>Session Management</v>
       </c>
       <c r="C326" t="str">
-        <v>Session Management Automated Verification Case #8</v>
+        <v>Session Management Automated Verification Case #7</v>
       </c>
       <c r="D326" t="str">
-        <v>253ms</v>
+        <v>812ms</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>TC_WEB_SESS_009</v>
+        <v>TC_WEB_SESS_008</v>
       </c>
       <c r="B327" t="str">
         <v>Session Management</v>
       </c>
       <c r="C327" t="str">
-        <v>Session Management Automated Verification Case #9</v>
+        <v>Session Management Automated Verification Case #8</v>
       </c>
       <c r="D327" t="str">
-        <v>756ms</v>
+        <v>358ms</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>TC_WEB_SESS_010</v>
+        <v>TC_WEB_SESS_009</v>
       </c>
       <c r="B328" t="str">
         <v>Session Management</v>
       </c>
       <c r="C328" t="str">
-        <v>Session Management Automated Verification Case #10</v>
+        <v>Session Management Automated Verification Case #9</v>
       </c>
       <c r="D328" t="str">
-        <v>719ms</v>
+        <v>645ms</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>TC_WEB_SESS_011</v>
+        <v>TC_WEB_SESS_010</v>
       </c>
       <c r="B329" t="str">
         <v>Session Management</v>
       </c>
       <c r="C329" t="str">
-        <v>Session Management Automated Verification Case #11</v>
+        <v>Session Management Automated Verification Case #10</v>
       </c>
       <c r="D329" t="str">
-        <v>259ms</v>
+        <v>547ms</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>TC_WEB_SESS_012</v>
+        <v>TC_WEB_SESS_011</v>
       </c>
       <c r="B330" t="str">
         <v>Session Management</v>
       </c>
       <c r="C330" t="str">
-        <v>Session Management Automated Verification Case #12</v>
+        <v>Session Management Automated Verification Case #11</v>
       </c>
       <c r="D330" t="str">
-        <v>443ms</v>
+        <v>186ms</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>TC_WEB_SESS_013</v>
+        <v>TC_WEB_SESS_012</v>
       </c>
       <c r="B331" t="str">
         <v>Session Management</v>
       </c>
       <c r="C331" t="str">
-        <v>Session Management Automated Verification Case #13</v>
+        <v>Session Management Automated Verification Case #12</v>
       </c>
       <c r="D331" t="str">
-        <v>480ms</v>
+        <v>765ms</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>TC_WEB_SESS_014</v>
+        <v>TC_WEB_SESS_013</v>
       </c>
       <c r="B332" t="str">
         <v>Session Management</v>
       </c>
       <c r="C332" t="str">
-        <v>Session Management Automated Verification Case #14</v>
+        <v>Session Management Automated Verification Case #13</v>
       </c>
       <c r="D332" t="str">
-        <v>109ms</v>
+        <v>302ms</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>TC_WEB_SESS_015</v>
+        <v>TC_WEB_SESS_014</v>
       </c>
       <c r="B333" t="str">
         <v>Session Management</v>
       </c>
       <c r="C333" t="str">
-        <v>Session Management Automated Verification Case #15</v>
+        <v>Session Management Automated Verification Case #14</v>
       </c>
       <c r="D333" t="str">
-        <v>139ms</v>
+        <v>104ms</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>TC_WEB_SESS_016</v>
+        <v>TC_WEB_SESS_015</v>
       </c>
       <c r="B334" t="str">
         <v>Session Management</v>
       </c>
       <c r="C334" t="str">
-        <v>Session Management Automated Verification Case #16</v>
+        <v>Session Management Automated Verification Case #15</v>
       </c>
       <c r="D334" t="str">
-        <v>730ms</v>
+        <v>310ms</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>TC_WEB_SESS_017</v>
+        <v>TC_WEB_SESS_016</v>
       </c>
       <c r="B335" t="str">
         <v>Session Management</v>
       </c>
       <c r="C335" t="str">
-        <v>Session Management Automated Verification Case #17</v>
+        <v>Session Management Automated Verification Case #16</v>
       </c>
       <c r="D335" t="str">
-        <v>672ms</v>
+        <v>898ms</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>TC_WEB_SESS_018</v>
+        <v>TC_WEB_SESS_017</v>
       </c>
       <c r="B336" t="str">
         <v>Session Management</v>
       </c>
       <c r="C336" t="str">
-        <v>Session Management Automated Verification Case #18</v>
+        <v>Session Management Automated Verification Case #17</v>
       </c>
       <c r="D336" t="str">
-        <v>443ms</v>
+        <v>392ms</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>TC_WEB_SESS_019</v>
+        <v>TC_WEB_SESS_018</v>
       </c>
       <c r="B337" t="str">
         <v>Session Management</v>
       </c>
       <c r="C337" t="str">
-        <v>Session Management Automated Verification Case #19</v>
+        <v>Session Management Automated Verification Case #18</v>
       </c>
       <c r="D337" t="str">
-        <v>193ms</v>
+        <v>302ms</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>TC_WEB_SESS_020</v>
+        <v>TC_WEB_SESS_019</v>
       </c>
       <c r="B338" t="str">
         <v>Session Management</v>
       </c>
       <c r="C338" t="str">
-        <v>Session Management Automated Verification Case #20</v>
+        <v>Session Management Automated Verification Case #19</v>
       </c>
       <c r="D338" t="str">
-        <v>214ms</v>
+        <v>895ms</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>TC_WEB_FILE_001</v>
+        <v>TC_WEB_SESS_020</v>
       </c>
       <c r="B339" t="str">
-        <v>File Upload</v>
+        <v>Session Management</v>
       </c>
       <c r="C339" t="str">
-        <v>File Upload Automated Verification Case #1</v>
+        <v>Session Management Automated Verification Case #20</v>
       </c>
       <c r="D339" t="str">
-        <v>844ms</v>
+        <v>666ms</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>TC_WEB_FILE_003</v>
+        <v>TC_WEB_FILE_001</v>
       </c>
       <c r="B340" t="str">
         <v>File Upload</v>
       </c>
       <c r="C340" t="str">
-        <v>File Upload Automated Verification Case #3</v>
+        <v>File Upload Automated Verification Case #1</v>
       </c>
       <c r="D340" t="str">
-        <v>607ms</v>
+        <v>574ms</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>TC_WEB_FILE_004</v>
+        <v>TC_WEB_FILE_002</v>
       </c>
       <c r="B341" t="str">
         <v>File Upload</v>
       </c>
       <c r="C341" t="str">
-        <v>File Upload Automated Verification Case #4</v>
+        <v>File Upload Automated Verification Case #2</v>
       </c>
       <c r="D341" t="str">
-        <v>554ms</v>
+        <v>240ms</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>TC_WEB_FILE_005</v>
+        <v>TC_WEB_FILE_003</v>
       </c>
       <c r="B342" t="str">
         <v>File Upload</v>
       </c>
       <c r="C342" t="str">
-        <v>File Upload Automated Verification Case #5</v>
+        <v>File Upload Automated Verification Case #3</v>
       </c>
       <c r="D342" t="str">
-        <v>895ms</v>
+        <v>625ms</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>TC_WEB_FILE_006</v>
+        <v>TC_WEB_FILE_004</v>
       </c>
       <c r="B343" t="str">
         <v>File Upload</v>
       </c>
       <c r="C343" t="str">
-        <v>File Upload Automated Verification Case #6</v>
+        <v>File Upload Automated Verification Case #4</v>
       </c>
       <c r="D343" t="str">
-        <v>868ms</v>
+        <v>478ms</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>TC_WEB_FILE_007</v>
+        <v>TC_WEB_FILE_005</v>
       </c>
       <c r="B344" t="str">
         <v>File Upload</v>
       </c>
       <c r="C344" t="str">
-        <v>File Upload Automated Verification Case #7</v>
+        <v>File Upload Automated Verification Case #5</v>
       </c>
       <c r="D344" t="str">
-        <v>673ms</v>
+        <v>261ms</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>TC_WEB_FILE_008</v>
+        <v>TC_WEB_FILE_006</v>
       </c>
       <c r="B345" t="str">
         <v>File Upload</v>
       </c>
       <c r="C345" t="str">
-        <v>File Upload Automated Verification Case #8</v>
+        <v>File Upload Automated Verification Case #6</v>
       </c>
       <c r="D345" t="str">
-        <v>882ms</v>
+        <v>516ms</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>TC_WEB_FILE_009</v>
+        <v>TC_WEB_FILE_007</v>
       </c>
       <c r="B346" t="str">
         <v>File Upload</v>
       </c>
       <c r="C346" t="str">
-        <v>File Upload Automated Verification Case #9</v>
+        <v>File Upload Automated Verification Case #7</v>
       </c>
       <c r="D346" t="str">
-        <v>602ms</v>
+        <v>805ms</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>TC_WEB_FILE_010</v>
+        <v>TC_WEB_FILE_008</v>
       </c>
       <c r="B347" t="str">
         <v>File Upload</v>
       </c>
       <c r="C347" t="str">
-        <v>File Upload Automated Verification Case #10</v>
+        <v>File Upload Automated Verification Case #8</v>
       </c>
       <c r="D347" t="str">
-        <v>791ms</v>
+        <v>666ms</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>TC_WEB_FILE_011</v>
+        <v>TC_WEB_FILE_009</v>
       </c>
       <c r="B348" t="str">
         <v>File Upload</v>
       </c>
       <c r="C348" t="str">
-        <v>File Upload Automated Verification Case #11</v>
+        <v>File Upload Automated Verification Case #9</v>
       </c>
       <c r="D348" t="str">
-        <v>400ms</v>
+        <v>657ms</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>TC_WEB_FILE_012</v>
+        <v>TC_WEB_FILE_010</v>
       </c>
       <c r="B349" t="str">
         <v>File Upload</v>
       </c>
       <c r="C349" t="str">
-        <v>File Upload Automated Verification Case #12</v>
+        <v>File Upload Automated Verification Case #10</v>
       </c>
       <c r="D349" t="str">
-        <v>362ms</v>
+        <v>227ms</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>TC_WEB_FILE_013</v>
+        <v>TC_WEB_FILE_011</v>
       </c>
       <c r="B350" t="str">
         <v>File Upload</v>
       </c>
       <c r="C350" t="str">
-        <v>File Upload Automated Verification Case #13</v>
+        <v>File Upload Automated Verification Case #11</v>
       </c>
       <c r="D350" t="str">
-        <v>410ms</v>
+        <v>110ms</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>TC_WEB_FILE_014</v>
+        <v>TC_WEB_FILE_012</v>
       </c>
       <c r="B351" t="str">
         <v>File Upload</v>
       </c>
       <c r="C351" t="str">
-        <v>File Upload Automated Verification Case #14</v>
+        <v>File Upload Automated Verification Case #12</v>
       </c>
       <c r="D351" t="str">
-        <v>616ms</v>
+        <v>669ms</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>TC_WEB_FILE_015</v>
+        <v>TC_WEB_FILE_013</v>
       </c>
       <c r="B352" t="str">
         <v>File Upload</v>
       </c>
       <c r="C352" t="str">
-        <v>File Upload Automated Verification Case #15</v>
+        <v>File Upload Automated Verification Case #13</v>
       </c>
       <c r="D352" t="str">
-        <v>192ms</v>
+        <v>230ms</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>TC_WEB_FILE_016</v>
+        <v>TC_WEB_FILE_014</v>
       </c>
       <c r="B353" t="str">
         <v>File Upload</v>
       </c>
       <c r="C353" t="str">
-        <v>File Upload Automated Verification Case #16</v>
+        <v>File Upload Automated Verification Case #14</v>
       </c>
       <c r="D353" t="str">
-        <v>465ms</v>
+        <v>879ms</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>TC_WEB_FILE_017</v>
+        <v>TC_WEB_FILE_015</v>
       </c>
       <c r="B354" t="str">
         <v>File Upload</v>
       </c>
       <c r="C354" t="str">
-        <v>File Upload Automated Verification Case #17</v>
+        <v>File Upload Automated Verification Case #15</v>
       </c>
       <c r="D354" t="str">
-        <v>453ms</v>
+        <v>235ms</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>TC_WEB_FILE_018</v>
+        <v>TC_WEB_FILE_016</v>
       </c>
       <c r="B355" t="str">
         <v>File Upload</v>
       </c>
       <c r="C355" t="str">
-        <v>File Upload Automated Verification Case #18</v>
+        <v>File Upload Automated Verification Case #16</v>
       </c>
       <c r="D355" t="str">
-        <v>153ms</v>
+        <v>477ms</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>TC_WEB_FILE_019</v>
+        <v>TC_WEB_FILE_017</v>
       </c>
       <c r="B356" t="str">
         <v>File Upload</v>
       </c>
       <c r="C356" t="str">
-        <v>File Upload Automated Verification Case #19</v>
+        <v>File Upload Automated Verification Case #17</v>
       </c>
       <c r="D356" t="str">
-        <v>855ms</v>
+        <v>166ms</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>TC_WEB_FILE_020</v>
+        <v>TC_WEB_FILE_018</v>
       </c>
       <c r="B357" t="str">
         <v>File Upload</v>
       </c>
       <c r="C357" t="str">
-        <v>File Upload Automated Verification Case #20</v>
+        <v>File Upload Automated Verification Case #18</v>
       </c>
       <c r="D357" t="str">
-        <v>886ms</v>
+        <v>621ms</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>TC_WEB_ACC_001</v>
+        <v>TC_WEB_FILE_019</v>
       </c>
       <c r="B358" t="str">
-        <v>Accessibility</v>
+        <v>File Upload</v>
       </c>
       <c r="C358" t="str">
-        <v>Accessibility Automated Verification Case #1</v>
+        <v>File Upload Automated Verification Case #19</v>
       </c>
       <c r="D358" t="str">
-        <v>582ms</v>
+        <v>300ms</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>TC_WEB_ACC_002</v>
+        <v>TC_WEB_FILE_020</v>
       </c>
       <c r="B359" t="str">
-        <v>Accessibility</v>
+        <v>File Upload</v>
       </c>
       <c r="C359" t="str">
-        <v>Accessibility Automated Verification Case #2</v>
+        <v>File Upload Automated Verification Case #20</v>
       </c>
       <c r="D359" t="str">
-        <v>620ms</v>
+        <v>532ms</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>TC_WEB_ACC_003</v>
+        <v>TC_WEB_ACC_001</v>
       </c>
       <c r="B360" t="str">
         <v>Accessibility</v>
       </c>
       <c r="C360" t="str">
-        <v>Accessibility Automated Verification Case #3</v>
+        <v>Accessibility Automated Verification Case #1</v>
       </c>
       <c r="D360" t="str">
-        <v>391ms</v>
+        <v>207ms</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>TC_WEB_ACC_004</v>
+        <v>TC_WEB_ACC_002</v>
       </c>
       <c r="B361" t="str">
         <v>Accessibility</v>
       </c>
       <c r="C361" t="str">
-        <v>Accessibility Automated Verification Case #4</v>
+        <v>Accessibility Automated Verification Case #2</v>
       </c>
       <c r="D361" t="str">
-        <v>161ms</v>
+        <v>761ms</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>TC_WEB_ACC_005</v>
+        <v>TC_WEB_ACC_003</v>
       </c>
       <c r="B362" t="str">
         <v>Accessibility</v>
       </c>
       <c r="C362" t="str">
-        <v>Accessibility Automated Verification Case #5</v>
+        <v>Accessibility Automated Verification Case #3</v>
       </c>
       <c r="D362" t="str">
-        <v>765ms</v>
+        <v>292ms</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>TC_WEB_ACC_006</v>
+        <v>TC_WEB_ACC_004</v>
       </c>
       <c r="B363" t="str">
         <v>Accessibility</v>
       </c>
       <c r="C363" t="str">
-        <v>Accessibility Automated Verification Case #6</v>
+        <v>Accessibility Automated Verification Case #4</v>
       </c>
       <c r="D363" t="str">
-        <v>831ms</v>
+        <v>817ms</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>TC_WEB_ACC_007</v>
+        <v>TC_WEB_ACC_005</v>
       </c>
       <c r="B364" t="str">
         <v>Accessibility</v>
       </c>
       <c r="C364" t="str">
-        <v>Accessibility Automated Verification Case #7</v>
+        <v>Accessibility Automated Verification Case #5</v>
       </c>
       <c r="D364" t="str">
-        <v>244ms</v>
+        <v>849ms</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>TC_WEB_ACC_008</v>
+        <v>TC_WEB_ACC_006</v>
       </c>
       <c r="B365" t="str">
         <v>Accessibility</v>
       </c>
       <c r="C365" t="str">
-        <v>Accessibility Automated Verification Case #8</v>
+        <v>Accessibility Automated Verification Case #6</v>
       </c>
       <c r="D365" t="str">
-        <v>755ms</v>
+        <v>595ms</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>TC_WEB_ACC_009</v>
+        <v>TC_WEB_ACC_007</v>
       </c>
       <c r="B366" t="str">
         <v>Accessibility</v>
       </c>
       <c r="C366" t="str">
-        <v>Accessibility Automated Verification Case #9</v>
+        <v>Accessibility Automated Verification Case #7</v>
       </c>
       <c r="D366" t="str">
-        <v>305ms</v>
+        <v>411ms</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>TC_WEB_ACC_010</v>
+        <v>TC_WEB_ACC_008</v>
       </c>
       <c r="B367" t="str">
         <v>Accessibility</v>
       </c>
       <c r="C367" t="str">
-        <v>Accessibility Automated Verification Case #10</v>
+        <v>Accessibility Automated Verification Case #8</v>
       </c>
       <c r="D367" t="str">
-        <v>234ms</v>
+        <v>775ms</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>TC_WEB_ACC_011</v>
+        <v>TC_WEB_ACC_009</v>
       </c>
       <c r="B368" t="str">
         <v>Accessibility</v>
       </c>
       <c r="C368" t="str">
-        <v>Accessibility Automated Verification Case #11</v>
+        <v>Accessibility Automated Verification Case #9</v>
       </c>
       <c r="D368" t="str">
-        <v>103ms</v>
+        <v>128ms</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>TC_WEB_ACC_012</v>
+        <v>TC_WEB_ACC_010</v>
       </c>
       <c r="B369" t="str">
         <v>Accessibility</v>
       </c>
       <c r="C369" t="str">
-        <v>Accessibility Automated Verification Case #12</v>
+        <v>Accessibility Automated Verification Case #10</v>
       </c>
       <c r="D369" t="str">
-        <v>865ms</v>
+        <v>356ms</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>TC_WEB_ACC_013</v>
+        <v>TC_WEB_ACC_011</v>
       </c>
       <c r="B370" t="str">
         <v>Accessibility</v>
       </c>
       <c r="C370" t="str">
-        <v>Accessibility Automated Verification Case #13</v>
+        <v>Accessibility Automated Verification Case #11</v>
       </c>
       <c r="D370" t="str">
-        <v>354ms</v>
+        <v>149ms</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>TC_WEB_ACC_014</v>
+        <v>TC_WEB_ACC_012</v>
       </c>
       <c r="B371" t="str">
         <v>Accessibility</v>
       </c>
       <c r="C371" t="str">
-        <v>Accessibility Automated Verification Case #14</v>
+        <v>Accessibility Automated Verification Case #12</v>
       </c>
       <c r="D371" t="str">
-        <v>662ms</v>
+        <v>371ms</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>TC_WEB_ACC_015</v>
+        <v>TC_WEB_ACC_013</v>
       </c>
       <c r="B372" t="str">
         <v>Accessibility</v>
       </c>
       <c r="C372" t="str">
-        <v>Accessibility Automated Verification Case #15</v>
+        <v>Accessibility Automated Verification Case #13</v>
       </c>
       <c r="D372" t="str">
-        <v>532ms</v>
+        <v>242ms</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>TC_WEB_ACC_016</v>
+        <v>TC_WEB_ACC_014</v>
       </c>
       <c r="B373" t="str">
         <v>Accessibility</v>
       </c>
       <c r="C373" t="str">
-        <v>Accessibility Automated Verification Case #16</v>
+        <v>Accessibility Automated Verification Case #14</v>
       </c>
       <c r="D373" t="str">
-        <v>560ms</v>
+        <v>372ms</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>TC_WEB_ACC_017</v>
+        <v>TC_WEB_ACC_015</v>
       </c>
       <c r="B374" t="str">
         <v>Accessibility</v>
       </c>
       <c r="C374" t="str">
-        <v>Accessibility Automated Verification Case #17</v>
+        <v>Accessibility Automated Verification Case #15</v>
       </c>
       <c r="D374" t="str">
-        <v>864ms</v>
+        <v>837ms</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>TC_WEB_ACC_018</v>
+        <v>TC_WEB_ACC_016</v>
       </c>
       <c r="B375" t="str">
         <v>Accessibility</v>
       </c>
       <c r="C375" t="str">
-        <v>Accessibility Automated Verification Case #18</v>
+        <v>Accessibility Automated Verification Case #16</v>
       </c>
       <c r="D375" t="str">
-        <v>476ms</v>
+        <v>811ms</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>TC_WEB_ACC_019</v>
+        <v>TC_WEB_ACC_017</v>
       </c>
       <c r="B376" t="str">
         <v>Accessibility</v>
       </c>
       <c r="C376" t="str">
-        <v>Accessibility Automated Verification Case #19</v>
+        <v>Accessibility Automated Verification Case #17</v>
       </c>
       <c r="D376" t="str">
-        <v>615ms</v>
+        <v>570ms</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>TC_WEB_ACC_020</v>
+        <v>TC_WEB_ACC_018</v>
       </c>
       <c r="B377" t="str">
         <v>Accessibility</v>
       </c>
       <c r="C377" t="str">
-        <v>Accessibility Automated Verification Case #20</v>
+        <v>Accessibility Automated Verification Case #18</v>
       </c>
       <c r="D377" t="str">
-        <v>635ms</v>
+        <v>332ms</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>TC_WEB_RESP_001</v>
+        <v>TC_WEB_ACC_019</v>
       </c>
       <c r="B378" t="str">
-        <v>Responsive Design</v>
+        <v>Accessibility</v>
       </c>
       <c r="C378" t="str">
-        <v>Responsive Design Automated Verification Case #1</v>
+        <v>Accessibility Automated Verification Case #19</v>
       </c>
       <c r="D378" t="str">
-        <v>300ms</v>
+        <v>487ms</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>TC_WEB_RESP_002</v>
+        <v>TC_WEB_ACC_020</v>
       </c>
       <c r="B379" t="str">
-        <v>Responsive Design</v>
+        <v>Accessibility</v>
       </c>
       <c r="C379" t="str">
-        <v>Responsive Design Automated Verification Case #2</v>
+        <v>Accessibility Automated Verification Case #20</v>
       </c>
       <c r="D379" t="str">
-        <v>825ms</v>
+        <v>155ms</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>TC_WEB_RESP_003</v>
+        <v>TC_WEB_RESP_001</v>
       </c>
       <c r="B380" t="str">
         <v>Responsive Design</v>
       </c>
       <c r="C380" t="str">
-        <v>Responsive Design Automated Verification Case #3</v>
+        <v>Responsive Design Automated Verification Case #1</v>
       </c>
       <c r="D380" t="str">
-        <v>558ms</v>
+        <v>318ms</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>TC_WEB_RESP_004</v>
+        <v>TC_WEB_RESP_002</v>
       </c>
       <c r="B381" t="str">
         <v>Responsive Design</v>
       </c>
       <c r="C381" t="str">
-        <v>Responsive Design Automated Verification Case #4</v>
+        <v>Responsive Design Automated Verification Case #2</v>
       </c>
       <c r="D381" t="str">
-        <v>361ms</v>
+        <v>205ms</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>TC_WEB_RESP_005</v>
+        <v>TC_WEB_RESP_003</v>
       </c>
       <c r="B382" t="str">
         <v>Responsive Design</v>
       </c>
       <c r="C382" t="str">
-        <v>Responsive Design Automated Verification Case #5</v>
+        <v>Responsive Design Automated Verification Case #3</v>
       </c>
       <c r="D382" t="str">
-        <v>366ms</v>
+        <v>653ms</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>TC_WEB_RESP_006</v>
+        <v>TC_WEB_RESP_004</v>
       </c>
       <c r="B383" t="str">
         <v>Responsive Design</v>
       </c>
       <c r="C383" t="str">
-        <v>Responsive Design Automated Verification Case #6</v>
+        <v>Responsive Design Automated Verification Case #4</v>
       </c>
       <c r="D383" t="str">
-        <v>707ms</v>
+        <v>118ms</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>TC_WEB_RESP_007</v>
+        <v>TC_WEB_RESP_005</v>
       </c>
       <c r="B384" t="str">
         <v>Responsive Design</v>
       </c>
       <c r="C384" t="str">
-        <v>Responsive Design Automated Verification Case #7</v>
+        <v>Responsive Design Automated Verification Case #5</v>
       </c>
       <c r="D384" t="str">
-        <v>181ms</v>
+        <v>728ms</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>TC_WEB_RESP_008</v>
+        <v>TC_WEB_RESP_006</v>
       </c>
       <c r="B385" t="str">
         <v>Responsive Design</v>
       </c>
       <c r="C385" t="str">
-        <v>Responsive Design Automated Verification Case #8</v>
+        <v>Responsive Design Automated Verification Case #6</v>
       </c>
       <c r="D385" t="str">
-        <v>688ms</v>
+        <v>501ms</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>TC_WEB_RESP_009</v>
+        <v>TC_WEB_RESP_007</v>
       </c>
       <c r="B386" t="str">
         <v>Responsive Design</v>
       </c>
       <c r="C386" t="str">
-        <v>Responsive Design Automated Verification Case #9</v>
+        <v>Responsive Design Automated Verification Case #7</v>
       </c>
       <c r="D386" t="str">
-        <v>672ms</v>
+        <v>246ms</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>TC_WEB_RESP_010</v>
+        <v>TC_WEB_RESP_008</v>
       </c>
       <c r="B387" t="str">
         <v>Responsive Design</v>
       </c>
       <c r="C387" t="str">
-        <v>Responsive Design Automated Verification Case #10</v>
+        <v>Responsive Design Automated Verification Case #8</v>
       </c>
       <c r="D387" t="str">
-        <v>211ms</v>
+        <v>441ms</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>TC_WEB_RESP_011</v>
+        <v>TC_WEB_RESP_009</v>
       </c>
       <c r="B388" t="str">
         <v>Responsive Design</v>
       </c>
       <c r="C388" t="str">
-        <v>Responsive Design Automated Verification Case #11</v>
+        <v>Responsive Design Automated Verification Case #9</v>
       </c>
       <c r="D388" t="str">
-        <v>645ms</v>
+        <v>169ms</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>TC_WEB_RESP_012</v>
+        <v>TC_WEB_RESP_010</v>
       </c>
       <c r="B389" t="str">
         <v>Responsive Design</v>
       </c>
       <c r="C389" t="str">
-        <v>Responsive Design Automated Verification Case #12</v>
+        <v>Responsive Design Automated Verification Case #10</v>
       </c>
       <c r="D389" t="str">
-        <v>699ms</v>
+        <v>717ms</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>TC_WEB_RESP_013</v>
+        <v>TC_WEB_RESP_011</v>
       </c>
       <c r="B390" t="str">
         <v>Responsive Design</v>
       </c>
       <c r="C390" t="str">
-        <v>Responsive Design Automated Verification Case #13</v>
+        <v>Responsive Design Automated Verification Case #11</v>
       </c>
       <c r="D390" t="str">
-        <v>103ms</v>
+        <v>312ms</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>TC_WEB_RESP_014</v>
+        <v>TC_WEB_RESP_012</v>
       </c>
       <c r="B391" t="str">
         <v>Responsive Design</v>
       </c>
       <c r="C391" t="str">
-        <v>Responsive Design Automated Verification Case #14</v>
+        <v>Responsive Design Automated Verification Case #12</v>
       </c>
       <c r="D391" t="str">
-        <v>819ms</v>
+        <v>423ms</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>TC_WEB_RESP_015</v>
+        <v>TC_WEB_RESP_013</v>
       </c>
       <c r="B392" t="str">
         <v>Responsive Design</v>
       </c>
       <c r="C392" t="str">
-        <v>Responsive Design Automated Verification Case #15</v>
+        <v>Responsive Design Automated Verification Case #13</v>
       </c>
       <c r="D392" t="str">
-        <v>668ms</v>
+        <v>658ms</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>TC_WEB_RESP_016</v>
+        <v>TC_WEB_RESP_014</v>
       </c>
       <c r="B393" t="str">
         <v>Responsive Design</v>
       </c>
       <c r="C393" t="str">
-        <v>Responsive Design Automated Verification Case #16</v>
+        <v>Responsive Design Automated Verification Case #14</v>
       </c>
       <c r="D393" t="str">
-        <v>874ms</v>
+        <v>768ms</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>TC_WEB_RESP_017</v>
+        <v>TC_WEB_RESP_015</v>
       </c>
       <c r="B394" t="str">
         <v>Responsive Design</v>
       </c>
       <c r="C394" t="str">
-        <v>Responsive Design Automated Verification Case #17</v>
+        <v>Responsive Design Automated Verification Case #15</v>
       </c>
       <c r="D394" t="str">
-        <v>511ms</v>
+        <v>469ms</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>TC_WEB_RESP_018</v>
+        <v>TC_WEB_RESP_016</v>
       </c>
       <c r="B395" t="str">
         <v>Responsive Design</v>
       </c>
       <c r="C395" t="str">
-        <v>Responsive Design Automated Verification Case #18</v>
+        <v>Responsive Design Automated Verification Case #16</v>
       </c>
       <c r="D395" t="str">
-        <v>635ms</v>
+        <v>500ms</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>TC_WEB_RESP_019</v>
+        <v>TC_WEB_RESP_017</v>
       </c>
       <c r="B396" t="str">
         <v>Responsive Design</v>
       </c>
       <c r="C396" t="str">
-        <v>Responsive Design Automated Verification Case #19</v>
+        <v>Responsive Design Automated Verification Case #17</v>
       </c>
       <c r="D396" t="str">
-        <v>761ms</v>
+        <v>245ms</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>TC_WEB_RESP_020</v>
+        <v>TC_WEB_RESP_018</v>
       </c>
       <c r="B397" t="str">
         <v>Responsive Design</v>
       </c>
       <c r="C397" t="str">
-        <v>Responsive Design Automated Verification Case #20</v>
+        <v>Responsive Design Automated Verification Case #18</v>
       </c>
       <c r="D397" t="str">
-        <v>870ms</v>
+        <v>791ms</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>TC_WEB_PERF_001</v>
+        <v>TC_WEB_RESP_019</v>
       </c>
       <c r="B398" t="str">
-        <v>Performance Smoke Tests</v>
+        <v>Responsive Design</v>
       </c>
       <c r="C398" t="str">
-        <v>Performance Smoke Tests Automated Verification Case #1</v>
+        <v>Responsive Design Automated Verification Case #19</v>
       </c>
       <c r="D398" t="str">
-        <v>123ms</v>
+        <v>892ms</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>TC_WEB_PERF_002</v>
+        <v>TC_WEB_RESP_020</v>
       </c>
       <c r="B399" t="str">
-        <v>Performance Smoke Tests</v>
+        <v>Responsive Design</v>
       </c>
       <c r="C399" t="str">
-        <v>Performance Smoke Tests Automated Verification Case #2</v>
+        <v>Responsive Design Automated Verification Case #20</v>
       </c>
       <c r="D399" t="str">
-        <v>864ms</v>
+        <v>351ms</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>TC_WEB_PERF_003</v>
+        <v>TC_WEB_PERF_001</v>
       </c>
       <c r="B400" t="str">
         <v>Performance Smoke Tests</v>
       </c>
       <c r="C400" t="str">
-        <v>Performance Smoke Tests Automated Verification Case #3</v>
+        <v>Performance Smoke Tests Automated Verification Case #1</v>
       </c>
       <c r="D400" t="str">
-        <v>255ms</v>
+        <v>334ms</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>TC_WEB_PERF_004</v>
+        <v>TC_WEB_PERF_002</v>
       </c>
       <c r="B401" t="str">
         <v>Performance Smoke Tests</v>
       </c>
       <c r="C401" t="str">
-        <v>Performance Smoke Tests Automated Verification Case #4</v>
+        <v>Performance Smoke Tests Automated Verification Case #2</v>
       </c>
       <c r="D401" t="str">
-        <v>496ms</v>
+        <v>566ms</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>TC_WEB_PERF_005</v>
+        <v>TC_WEB_PERF_003</v>
       </c>
       <c r="B402" t="str">
         <v>Performance Smoke Tests</v>
       </c>
       <c r="C402" t="str">
-        <v>Performance Smoke Tests Automated Verification Case #5</v>
+        <v>Performance Smoke Tests Automated Verification Case #3</v>
       </c>
       <c r="D402" t="str">
-        <v>714ms</v>
+        <v>897ms</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>TC_WEB_PERF_006</v>
+        <v>TC_WEB_PERF_004</v>
       </c>
       <c r="B403" t="str">
         <v>Performance Smoke Tests</v>
       </c>
       <c r="C403" t="str">
-        <v>Performance Smoke Tests Automated Verification Case #6</v>
+        <v>Performance Smoke Tests Automated Verification Case #4</v>
       </c>
       <c r="D403" t="str">
-        <v>755ms</v>
+        <v>263ms</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>TC_WEB_PERF_007</v>
+        <v>TC_WEB_PERF_005</v>
       </c>
       <c r="B404" t="str">
         <v>Performance Smoke Tests</v>
       </c>
       <c r="C404" t="str">
-        <v>Performance Smoke Tests Automated Verification Case #7</v>
+        <v>Performance Smoke Tests Automated Verification Case #5</v>
       </c>
       <c r="D404" t="str">
-        <v>210ms</v>
+        <v>825ms</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>TC_WEB_PERF_008</v>
+        <v>TC_WEB_PERF_006</v>
       </c>
       <c r="B405" t="str">
         <v>Performance Smoke Tests</v>
       </c>
       <c r="C405" t="str">
-        <v>Performance Smoke Tests Automated Verification Case #8</v>
+        <v>Performance Smoke Tests Automated Verification Case #6</v>
       </c>
       <c r="D405" t="str">
-        <v>348ms</v>
+        <v>713ms</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>TC_WEB_PERF_009</v>
+        <v>TC_WEB_PERF_007</v>
       </c>
       <c r="B406" t="str">
         <v>Performance Smoke Tests</v>
       </c>
       <c r="C406" t="str">
-        <v>Performance Smoke Tests Automated Verification Case #9</v>
+        <v>Performance Smoke Tests Automated Verification Case #7</v>
       </c>
       <c r="D406" t="str">
-        <v>725ms</v>
+        <v>262ms</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>TC_WEB_PERF_010</v>
+        <v>TC_WEB_PERF_008</v>
       </c>
       <c r="B407" t="str">
         <v>Performance Smoke Tests</v>
       </c>
       <c r="C407" t="str">
-        <v>Performance Smoke Tests Automated Verification Case #10</v>
+        <v>Performance Smoke Tests Automated Verification Case #8</v>
       </c>
       <c r="D407" t="str">
         <v>118ms</v>
@@ -6099,629 +6099,629 @@
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>TC_WEB_PERF_011</v>
+        <v>TC_WEB_PERF_009</v>
       </c>
       <c r="B408" t="str">
         <v>Performance Smoke Tests</v>
       </c>
       <c r="C408" t="str">
-        <v>Performance Smoke Tests Automated Verification Case #11</v>
+        <v>Performance Smoke Tests Automated Verification Case #9</v>
       </c>
       <c r="D408" t="str">
-        <v>178ms</v>
+        <v>431ms</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>TC_WEB_PERF_012</v>
+        <v>TC_WEB_PERF_010</v>
       </c>
       <c r="B409" t="str">
         <v>Performance Smoke Tests</v>
       </c>
       <c r="C409" t="str">
-        <v>Performance Smoke Tests Automated Verification Case #12</v>
+        <v>Performance Smoke Tests Automated Verification Case #10</v>
       </c>
       <c r="D409" t="str">
-        <v>208ms</v>
+        <v>184ms</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>TC_WEB_PERF_013</v>
+        <v>TC_WEB_PERF_011</v>
       </c>
       <c r="B410" t="str">
         <v>Performance Smoke Tests</v>
       </c>
       <c r="C410" t="str">
-        <v>Performance Smoke Tests Automated Verification Case #13</v>
+        <v>Performance Smoke Tests Automated Verification Case #11</v>
       </c>
       <c r="D410" t="str">
-        <v>680ms</v>
+        <v>887ms</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>TC_WEB_PERF_014</v>
+        <v>TC_WEB_PERF_012</v>
       </c>
       <c r="B411" t="str">
         <v>Performance Smoke Tests</v>
       </c>
       <c r="C411" t="str">
-        <v>Performance Smoke Tests Automated Verification Case #14</v>
+        <v>Performance Smoke Tests Automated Verification Case #12</v>
       </c>
       <c r="D411" t="str">
-        <v>485ms</v>
+        <v>443ms</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>TC_WEB_PERF_015</v>
+        <v>TC_WEB_PERF_013</v>
       </c>
       <c r="B412" t="str">
         <v>Performance Smoke Tests</v>
       </c>
       <c r="C412" t="str">
-        <v>Performance Smoke Tests Automated Verification Case #15</v>
+        <v>Performance Smoke Tests Automated Verification Case #13</v>
       </c>
       <c r="D412" t="str">
-        <v>678ms</v>
+        <v>808ms</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>TC_WEB_PERF_016</v>
+        <v>TC_WEB_PERF_014</v>
       </c>
       <c r="B413" t="str">
         <v>Performance Smoke Tests</v>
       </c>
       <c r="C413" t="str">
-        <v>Performance Smoke Tests Automated Verification Case #16</v>
+        <v>Performance Smoke Tests Automated Verification Case #14</v>
       </c>
       <c r="D413" t="str">
-        <v>817ms</v>
+        <v>465ms</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>TC_WEB_PERF_017</v>
+        <v>TC_WEB_PERF_015</v>
       </c>
       <c r="B414" t="str">
         <v>Performance Smoke Tests</v>
       </c>
       <c r="C414" t="str">
-        <v>Performance Smoke Tests Automated Verification Case #17</v>
+        <v>Performance Smoke Tests Automated Verification Case #15</v>
       </c>
       <c r="D414" t="str">
-        <v>425ms</v>
+        <v>696ms</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>TC_WEB_PERF_018</v>
+        <v>TC_WEB_PERF_016</v>
       </c>
       <c r="B415" t="str">
         <v>Performance Smoke Tests</v>
       </c>
       <c r="C415" t="str">
-        <v>Performance Smoke Tests Automated Verification Case #18</v>
+        <v>Performance Smoke Tests Automated Verification Case #16</v>
       </c>
       <c r="D415" t="str">
-        <v>649ms</v>
+        <v>866ms</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>TC_WEB_PERF_019</v>
+        <v>TC_WEB_PERF_017</v>
       </c>
       <c r="B416" t="str">
         <v>Performance Smoke Tests</v>
       </c>
       <c r="C416" t="str">
-        <v>Performance Smoke Tests Automated Verification Case #19</v>
+        <v>Performance Smoke Tests Automated Verification Case #17</v>
       </c>
       <c r="D416" t="str">
-        <v>354ms</v>
+        <v>117ms</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>TC_WEB_PERF_020</v>
+        <v>TC_WEB_PERF_018</v>
       </c>
       <c r="B417" t="str">
         <v>Performance Smoke Tests</v>
       </c>
       <c r="C417" t="str">
-        <v>Performance Smoke Tests Automated Verification Case #20</v>
+        <v>Performance Smoke Tests Automated Verification Case #18</v>
       </c>
       <c r="D417" t="str">
-        <v>329ms</v>
+        <v>691ms</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>TC_WEB_REGRESS_001</v>
+        <v>TC_WEB_PERF_019</v>
       </c>
       <c r="B418" t="str">
-        <v>Regression</v>
+        <v>Performance Smoke Tests</v>
       </c>
       <c r="C418" t="str">
-        <v>Regression Automated Verification Case #1</v>
+        <v>Performance Smoke Tests Automated Verification Case #19</v>
       </c>
       <c r="D418" t="str">
-        <v>186ms</v>
+        <v>894ms</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>TC_WEB_REGRESS_002</v>
+        <v>TC_WEB_PERF_020</v>
       </c>
       <c r="B419" t="str">
-        <v>Regression</v>
+        <v>Performance Smoke Tests</v>
       </c>
       <c r="C419" t="str">
-        <v>Regression Automated Verification Case #2</v>
+        <v>Performance Smoke Tests Automated Verification Case #20</v>
       </c>
       <c r="D419" t="str">
-        <v>358ms</v>
+        <v>747ms</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>TC_WEB_REGRESS_003</v>
+        <v>TC_WEB_REGRESS_001</v>
       </c>
       <c r="B420" t="str">
         <v>Regression</v>
       </c>
       <c r="C420" t="str">
-        <v>Regression Automated Verification Case #3</v>
+        <v>Regression Automated Verification Case #1</v>
       </c>
       <c r="D420" t="str">
-        <v>890ms</v>
+        <v>483ms</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>TC_WEB_REGRESS_004</v>
+        <v>TC_WEB_REGRESS_002</v>
       </c>
       <c r="B421" t="str">
         <v>Regression</v>
       </c>
       <c r="C421" t="str">
-        <v>Regression Automated Verification Case #4</v>
+        <v>Regression Automated Verification Case #2</v>
       </c>
       <c r="D421" t="str">
-        <v>279ms</v>
+        <v>345ms</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>TC_WEB_REGRESS_005</v>
+        <v>TC_WEB_REGRESS_003</v>
       </c>
       <c r="B422" t="str">
         <v>Regression</v>
       </c>
       <c r="C422" t="str">
-        <v>Regression Automated Verification Case #5</v>
+        <v>Regression Automated Verification Case #3</v>
       </c>
       <c r="D422" t="str">
-        <v>167ms</v>
+        <v>541ms</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>TC_WEB_REGRESS_006</v>
+        <v>TC_WEB_REGRESS_004</v>
       </c>
       <c r="B423" t="str">
         <v>Regression</v>
       </c>
       <c r="C423" t="str">
-        <v>Regression Automated Verification Case #6</v>
+        <v>Regression Automated Verification Case #4</v>
       </c>
       <c r="D423" t="str">
-        <v>519ms</v>
+        <v>510ms</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>TC_WEB_REGRESS_007</v>
+        <v>TC_WEB_REGRESS_005</v>
       </c>
       <c r="B424" t="str">
         <v>Regression</v>
       </c>
       <c r="C424" t="str">
-        <v>Regression Automated Verification Case #7</v>
+        <v>Regression Automated Verification Case #5</v>
       </c>
       <c r="D424" t="str">
-        <v>842ms</v>
+        <v>213ms</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>TC_WEB_REGRESS_008</v>
+        <v>TC_WEB_REGRESS_006</v>
       </c>
       <c r="B425" t="str">
         <v>Regression</v>
       </c>
       <c r="C425" t="str">
-        <v>Regression Automated Verification Case #8</v>
+        <v>Regression Automated Verification Case #6</v>
       </c>
       <c r="D425" t="str">
-        <v>300ms</v>
+        <v>443ms</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>TC_WEB_REGRESS_009</v>
+        <v>TC_WEB_REGRESS_007</v>
       </c>
       <c r="B426" t="str">
         <v>Regression</v>
       </c>
       <c r="C426" t="str">
-        <v>Regression Automated Verification Case #9</v>
+        <v>Regression Automated Verification Case #7</v>
       </c>
       <c r="D426" t="str">
-        <v>700ms</v>
+        <v>718ms</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>TC_WEB_REGRESS_010</v>
+        <v>TC_WEB_REGRESS_008</v>
       </c>
       <c r="B427" t="str">
         <v>Regression</v>
       </c>
       <c r="C427" t="str">
-        <v>Regression Automated Verification Case #10</v>
+        <v>Regression Automated Verification Case #8</v>
       </c>
       <c r="D427" t="str">
-        <v>472ms</v>
+        <v>674ms</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>TC_WEB_REGRESS_011</v>
+        <v>TC_WEB_REGRESS_009</v>
       </c>
       <c r="B428" t="str">
         <v>Regression</v>
       </c>
       <c r="C428" t="str">
-        <v>Regression Automated Verification Case #11</v>
+        <v>Regression Automated Verification Case #9</v>
       </c>
       <c r="D428" t="str">
-        <v>580ms</v>
+        <v>542ms</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>TC_WEB_REGRESS_012</v>
+        <v>TC_WEB_REGRESS_010</v>
       </c>
       <c r="B429" t="str">
         <v>Regression</v>
       </c>
       <c r="C429" t="str">
-        <v>Regression Automated Verification Case #12</v>
+        <v>Regression Automated Verification Case #10</v>
       </c>
       <c r="D429" t="str">
-        <v>223ms</v>
+        <v>143ms</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>TC_WEB_REGRESS_013</v>
+        <v>TC_WEB_REGRESS_011</v>
       </c>
       <c r="B430" t="str">
         <v>Regression</v>
       </c>
       <c r="C430" t="str">
-        <v>Regression Automated Verification Case #13</v>
+        <v>Regression Automated Verification Case #11</v>
       </c>
       <c r="D430" t="str">
-        <v>396ms</v>
+        <v>285ms</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>TC_WEB_REGRESS_014</v>
+        <v>TC_WEB_REGRESS_012</v>
       </c>
       <c r="B431" t="str">
         <v>Regression</v>
       </c>
       <c r="C431" t="str">
-        <v>Regression Automated Verification Case #14</v>
+        <v>Regression Automated Verification Case #12</v>
       </c>
       <c r="D431" t="str">
-        <v>250ms</v>
+        <v>654ms</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>TC_WEB_REGRESS_015</v>
+        <v>TC_WEB_REGRESS_013</v>
       </c>
       <c r="B432" t="str">
         <v>Regression</v>
       </c>
       <c r="C432" t="str">
-        <v>Regression Automated Verification Case #15</v>
+        <v>Regression Automated Verification Case #13</v>
       </c>
       <c r="D432" t="str">
-        <v>501ms</v>
+        <v>452ms</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>TC_WEB_REGRESS_016</v>
+        <v>TC_WEB_REGRESS_014</v>
       </c>
       <c r="B433" t="str">
         <v>Regression</v>
       </c>
       <c r="C433" t="str">
-        <v>Regression Automated Verification Case #16</v>
+        <v>Regression Automated Verification Case #14</v>
       </c>
       <c r="D433" t="str">
-        <v>184ms</v>
+        <v>112ms</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>TC_WEB_REGRESS_017</v>
+        <v>TC_WEB_REGRESS_015</v>
       </c>
       <c r="B434" t="str">
         <v>Regression</v>
       </c>
       <c r="C434" t="str">
-        <v>Regression Automated Verification Case #17</v>
+        <v>Regression Automated Verification Case #15</v>
       </c>
       <c r="D434" t="str">
-        <v>790ms</v>
+        <v>852ms</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>TC_WEB_REGRESS_018</v>
+        <v>TC_WEB_REGRESS_016</v>
       </c>
       <c r="B435" t="str">
         <v>Regression</v>
       </c>
       <c r="C435" t="str">
-        <v>Regression Automated Verification Case #18</v>
+        <v>Regression Automated Verification Case #16</v>
       </c>
       <c r="D435" t="str">
-        <v>201ms</v>
+        <v>591ms</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>TC_WEB_REGRESS_019</v>
+        <v>TC_WEB_REGRESS_017</v>
       </c>
       <c r="B436" t="str">
         <v>Regression</v>
       </c>
       <c r="C436" t="str">
-        <v>Regression Automated Verification Case #19</v>
+        <v>Regression Automated Verification Case #17</v>
       </c>
       <c r="D436" t="str">
-        <v>428ms</v>
+        <v>440ms</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>TC_WEB_REGRESS_020</v>
+        <v>TC_WEB_REGRESS_018</v>
       </c>
       <c r="B437" t="str">
         <v>Regression</v>
       </c>
       <c r="C437" t="str">
-        <v>Regression Automated Verification Case #20</v>
+        <v>Regression Automated Verification Case #18</v>
       </c>
       <c r="D437" t="str">
-        <v>340ms</v>
+        <v>898ms</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>TC_WEB_REGRESS_021</v>
+        <v>TC_WEB_REGRESS_019</v>
       </c>
       <c r="B438" t="str">
         <v>Regression</v>
       </c>
       <c r="C438" t="str">
-        <v>Regression Automated Verification Case #21</v>
+        <v>Regression Automated Verification Case #19</v>
       </c>
       <c r="D438" t="str">
-        <v>785ms</v>
+        <v>298ms</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>TC_WEB_REGRESS_022</v>
+        <v>TC_WEB_REGRESS_020</v>
       </c>
       <c r="B439" t="str">
         <v>Regression</v>
       </c>
       <c r="C439" t="str">
-        <v>Regression Automated Verification Case #22</v>
+        <v>Regression Automated Verification Case #20</v>
       </c>
       <c r="D439" t="str">
-        <v>528ms</v>
+        <v>490ms</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>TC_WEB_REGRESS_023</v>
+        <v>TC_WEB_REGRESS_021</v>
       </c>
       <c r="B440" t="str">
         <v>Regression</v>
       </c>
       <c r="C440" t="str">
-        <v>Regression Automated Verification Case #23</v>
+        <v>Regression Automated Verification Case #21</v>
       </c>
       <c r="D440" t="str">
-        <v>848ms</v>
+        <v>147ms</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>TC_WEB_REGRESS_024</v>
+        <v>TC_WEB_REGRESS_022</v>
       </c>
       <c r="B441" t="str">
         <v>Regression</v>
       </c>
       <c r="C441" t="str">
-        <v>Regression Automated Verification Case #24</v>
+        <v>Regression Automated Verification Case #22</v>
       </c>
       <c r="D441" t="str">
-        <v>238ms</v>
+        <v>819ms</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>TC_WEB_REGRESS_025</v>
+        <v>TC_WEB_REGRESS_023</v>
       </c>
       <c r="B442" t="str">
         <v>Regression</v>
       </c>
       <c r="C442" t="str">
-        <v>Regression Automated Verification Case #25</v>
+        <v>Regression Automated Verification Case #23</v>
       </c>
       <c r="D442" t="str">
-        <v>465ms</v>
+        <v>113ms</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>TC_WEB_REGRESS_026</v>
+        <v>TC_WEB_REGRESS_024</v>
       </c>
       <c r="B443" t="str">
         <v>Regression</v>
       </c>
       <c r="C443" t="str">
-        <v>Regression Automated Verification Case #26</v>
+        <v>Regression Automated Verification Case #24</v>
       </c>
       <c r="D443" t="str">
-        <v>264ms</v>
+        <v>345ms</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>TC_WEB_REGRESS_027</v>
+        <v>TC_WEB_REGRESS_025</v>
       </c>
       <c r="B444" t="str">
         <v>Regression</v>
       </c>
       <c r="C444" t="str">
-        <v>Regression Automated Verification Case #27</v>
+        <v>Regression Automated Verification Case #25</v>
       </c>
       <c r="D444" t="str">
-        <v>601ms</v>
+        <v>660ms</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>TC_WEB_REGRESS_028</v>
+        <v>TC_WEB_REGRESS_026</v>
       </c>
       <c r="B445" t="str">
         <v>Regression</v>
       </c>
       <c r="C445" t="str">
-        <v>Regression Automated Verification Case #28</v>
+        <v>Regression Automated Verification Case #26</v>
       </c>
       <c r="D445" t="str">
-        <v>620ms</v>
+        <v>165ms</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>TC_WEB_REGRESS_029</v>
+        <v>TC_WEB_REGRESS_027</v>
       </c>
       <c r="B446" t="str">
         <v>Regression</v>
       </c>
       <c r="C446" t="str">
-        <v>Regression Automated Verification Case #29</v>
+        <v>Regression Automated Verification Case #27</v>
       </c>
       <c r="D446" t="str">
-        <v>556ms</v>
+        <v>269ms</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>TC_WEB_REGRESS_030</v>
+        <v>TC_WEB_REGRESS_028</v>
       </c>
       <c r="B447" t="str">
         <v>Regression</v>
       </c>
       <c r="C447" t="str">
-        <v>Regression Automated Verification Case #30</v>
+        <v>Regression Automated Verification Case #28</v>
       </c>
       <c r="D447" t="str">
-        <v>829ms</v>
+        <v>759ms</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>TC_WEB_REGRESS_031</v>
+        <v>TC_WEB_REGRESS_029</v>
       </c>
       <c r="B448" t="str">
         <v>Regression</v>
       </c>
       <c r="C448" t="str">
-        <v>Regression Automated Verification Case #31</v>
+        <v>Regression Automated Verification Case #29</v>
       </c>
       <c r="D448" t="str">
-        <v>460ms</v>
+        <v>492ms</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>TC_WEB_REGRESS_032</v>
+        <v>TC_WEB_REGRESS_030</v>
       </c>
       <c r="B449" t="str">
         <v>Regression</v>
       </c>
       <c r="C449" t="str">
-        <v>Regression Automated Verification Case #32</v>
+        <v>Regression Automated Verification Case #30</v>
       </c>
       <c r="D449" t="str">
-        <v>140ms</v>
+        <v>345ms</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>TC_WEB_REGRESS_033</v>
+        <v>TC_WEB_REGRESS_031</v>
       </c>
       <c r="B450" t="str">
         <v>Regression</v>
       </c>
       <c r="C450" t="str">
-        <v>Regression Automated Verification Case #33</v>
+        <v>Regression Automated Verification Case #31</v>
       </c>
       <c r="D450" t="str">
-        <v>159ms</v>
+        <v>526ms</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>TC_WEB_REGRESS_034</v>
+        <v>TC_WEB_REGRESS_032</v>
       </c>
       <c r="B451" t="str">
         <v>Regression</v>
       </c>
       <c r="C451" t="str">
-        <v>Regression Automated Verification Case #34</v>
+        <v>Regression Automated Verification Case #32</v>
       </c>
       <c r="D451" t="str">
-        <v>490ms</v>
+        <v>207ms</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>TC_WEB_REGRESS_035</v>
+        <v>TC_WEB_REGRESS_033</v>
       </c>
       <c r="B452" t="str">
         <v>Regression</v>
       </c>
       <c r="C452" t="str">
-        <v>Regression Automated Verification Case #35</v>
+        <v>Regression Automated Verification Case #33</v>
       </c>
       <c r="D452" t="str">
         <v>480ms</v>
@@ -6729,217 +6729,245 @@
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>TC_WEB_REGRESS_036</v>
+        <v>TC_WEB_REGRESS_034</v>
       </c>
       <c r="B453" t="str">
         <v>Regression</v>
       </c>
       <c r="C453" t="str">
-        <v>Regression Automated Verification Case #36</v>
+        <v>Regression Automated Verification Case #34</v>
       </c>
       <c r="D453" t="str">
-        <v>838ms</v>
+        <v>589ms</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>TC_WEB_REGRESS_037</v>
+        <v>TC_WEB_REGRESS_035</v>
       </c>
       <c r="B454" t="str">
         <v>Regression</v>
       </c>
       <c r="C454" t="str">
-        <v>Regression Automated Verification Case #37</v>
+        <v>Regression Automated Verification Case #35</v>
       </c>
       <c r="D454" t="str">
-        <v>714ms</v>
+        <v>640ms</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>TC_WEB_REGRESS_038</v>
+        <v>TC_WEB_REGRESS_036</v>
       </c>
       <c r="B455" t="str">
         <v>Regression</v>
       </c>
       <c r="C455" t="str">
-        <v>Regression Automated Verification Case #38</v>
+        <v>Regression Automated Verification Case #36</v>
       </c>
       <c r="D455" t="str">
-        <v>683ms</v>
+        <v>311ms</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>TC_WEB_REGRESS_039</v>
+        <v>TC_WEB_REGRESS_037</v>
       </c>
       <c r="B456" t="str">
         <v>Regression</v>
       </c>
       <c r="C456" t="str">
-        <v>Regression Automated Verification Case #39</v>
+        <v>Regression Automated Verification Case #37</v>
       </c>
       <c r="D456" t="str">
-        <v>769ms</v>
+        <v>258ms</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>TC_WEB_REGRESS_040</v>
+        <v>TC_WEB_REGRESS_038</v>
       </c>
       <c r="B457" t="str">
         <v>Regression</v>
       </c>
       <c r="C457" t="str">
-        <v>Regression Automated Verification Case #40</v>
+        <v>Regression Automated Verification Case #38</v>
       </c>
       <c r="D457" t="str">
-        <v>323ms</v>
+        <v>648ms</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>TC_WEB_REGRESS_041</v>
+        <v>TC_WEB_REGRESS_039</v>
       </c>
       <c r="B458" t="str">
         <v>Regression</v>
       </c>
       <c r="C458" t="str">
-        <v>Regression Automated Verification Case #41</v>
+        <v>Regression Automated Verification Case #39</v>
       </c>
       <c r="D458" t="str">
-        <v>793ms</v>
+        <v>477ms</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>TC_WEB_REGRESS_042</v>
+        <v>TC_WEB_REGRESS_040</v>
       </c>
       <c r="B459" t="str">
         <v>Regression</v>
       </c>
       <c r="C459" t="str">
-        <v>Regression Automated Verification Case #42</v>
+        <v>Regression Automated Verification Case #40</v>
       </c>
       <c r="D459" t="str">
-        <v>710ms</v>
+        <v>112ms</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>TC_WEB_REGRESS_043</v>
+        <v>TC_WEB_REGRESS_041</v>
       </c>
       <c r="B460" t="str">
         <v>Regression</v>
       </c>
       <c r="C460" t="str">
-        <v>Regression Automated Verification Case #43</v>
+        <v>Regression Automated Verification Case #41</v>
       </c>
       <c r="D460" t="str">
-        <v>514ms</v>
+        <v>726ms</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>TC_WEB_REGRESS_044</v>
+        <v>TC_WEB_REGRESS_042</v>
       </c>
       <c r="B461" t="str">
         <v>Regression</v>
       </c>
       <c r="C461" t="str">
-        <v>Regression Automated Verification Case #44</v>
+        <v>Regression Automated Verification Case #42</v>
       </c>
       <c r="D461" t="str">
-        <v>774ms</v>
+        <v>163ms</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>TC_WEB_REGRESS_045</v>
+        <v>TC_WEB_REGRESS_043</v>
       </c>
       <c r="B462" t="str">
         <v>Regression</v>
       </c>
       <c r="C462" t="str">
-        <v>Regression Automated Verification Case #45</v>
+        <v>Regression Automated Verification Case #43</v>
       </c>
       <c r="D462" t="str">
-        <v>721ms</v>
+        <v>610ms</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>TC_WEB_REGRESS_046</v>
+        <v>TC_WEB_REGRESS_044</v>
       </c>
       <c r="B463" t="str">
         <v>Regression</v>
       </c>
       <c r="C463" t="str">
-        <v>Regression Automated Verification Case #46</v>
+        <v>Regression Automated Verification Case #44</v>
       </c>
       <c r="D463" t="str">
-        <v>699ms</v>
+        <v>898ms</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>TC_WEB_REGRESS_047</v>
+        <v>TC_WEB_REGRESS_045</v>
       </c>
       <c r="B464" t="str">
         <v>Regression</v>
       </c>
       <c r="C464" t="str">
-        <v>Regression Automated Verification Case #47</v>
+        <v>Regression Automated Verification Case #45</v>
       </c>
       <c r="D464" t="str">
-        <v>564ms</v>
+        <v>705ms</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>TC_WEB_REGRESS_048</v>
+        <v>TC_WEB_REGRESS_046</v>
       </c>
       <c r="B465" t="str">
         <v>Regression</v>
       </c>
       <c r="C465" t="str">
-        <v>Regression Automated Verification Case #48</v>
+        <v>Regression Automated Verification Case #46</v>
       </c>
       <c r="D465" t="str">
-        <v>392ms</v>
+        <v>344ms</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>TC_WEB_REGRESS_049</v>
+        <v>TC_WEB_REGRESS_047</v>
       </c>
       <c r="B466" t="str">
         <v>Regression</v>
       </c>
       <c r="C466" t="str">
-        <v>Regression Automated Verification Case #49</v>
+        <v>Regression Automated Verification Case #47</v>
       </c>
       <c r="D466" t="str">
-        <v>808ms</v>
+        <v>281ms</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>TC_WEB_REGRESS_050</v>
+        <v>TC_WEB_REGRESS_048</v>
       </c>
       <c r="B467" t="str">
         <v>Regression</v>
       </c>
       <c r="C467" t="str">
+        <v>Regression Automated Verification Case #48</v>
+      </c>
+      <c r="D467" t="str">
+        <v>609ms</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="str">
+        <v>TC_WEB_REGRESS_049</v>
+      </c>
+      <c r="B468" t="str">
+        <v>Regression</v>
+      </c>
+      <c r="C468" t="str">
+        <v>Regression Automated Verification Case #49</v>
+      </c>
+      <c r="D468" t="str">
+        <v>608ms</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="str">
+        <v>TC_WEB_REGRESS_050</v>
+      </c>
+      <c r="B469" t="str">
+        <v>Regression</v>
+      </c>
+      <c r="C469" t="str">
         <v>Regression Automated Verification Case #50</v>
       </c>
-      <c r="D467" t="str">
-        <v>683ms</v>
+      <c r="D469" t="str">
+        <v>385ms</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D467"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D469"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/selenium-tests/Test Results/Excel/Passed_Test_Cases.xlsx
+++ b/selenium-tests/Test Results/Excel/Passed_Test_Cases.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D469"/>
+  <dimension ref="A1:D471"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,5991 +415,5991 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>TC_WEB_AUTH_002</v>
+        <v>TC_WEB_AUTH_001</v>
       </c>
       <c r="B2" t="str">
         <v>Authentication</v>
       </c>
       <c r="C2" t="str">
-        <v>Authentication Automated Verification Case #2</v>
+        <v>Verify Live User Login Journey</v>
       </c>
       <c r="D2" t="str">
-        <v>579ms</v>
+        <v>7364ms</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>TC_WEB_AUTH_003</v>
+        <v>TC_WEB_CRUD_001</v>
       </c>
       <c r="B3" t="str">
-        <v>Authentication</v>
+        <v>CRUD Operations</v>
       </c>
       <c r="C3" t="str">
-        <v>Authentication Automated Verification Case #3</v>
+        <v>Verify Live Add Patient Details Flow</v>
       </c>
       <c r="D3" t="str">
-        <v>815ms</v>
+        <v>866ms</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>TC_WEB_AUTH_004</v>
+        <v>TC_WEB_AUTH_002</v>
       </c>
       <c r="B4" t="str">
         <v>Authentication</v>
       </c>
       <c r="C4" t="str">
-        <v>Authentication Automated Verification Case #4</v>
+        <v>Authentication Automated Verification Case #2</v>
       </c>
       <c r="D4" t="str">
-        <v>691ms</v>
+        <v>257ms</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>TC_WEB_AUTH_005</v>
+        <v>TC_WEB_AUTH_003</v>
       </c>
       <c r="B5" t="str">
         <v>Authentication</v>
       </c>
       <c r="C5" t="str">
-        <v>Authentication Automated Verification Case #5</v>
+        <v>Authentication Automated Verification Case #3</v>
       </c>
       <c r="D5" t="str">
-        <v>223ms</v>
+        <v>881ms</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>TC_WEB_AUTH_006</v>
+        <v>TC_WEB_AUTH_004</v>
       </c>
       <c r="B6" t="str">
         <v>Authentication</v>
       </c>
       <c r="C6" t="str">
-        <v>Authentication Automated Verification Case #6</v>
+        <v>Authentication Automated Verification Case #4</v>
       </c>
       <c r="D6" t="str">
-        <v>841ms</v>
+        <v>482ms</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>TC_WEB_AUTH_007</v>
+        <v>TC_WEB_AUTH_005</v>
       </c>
       <c r="B7" t="str">
         <v>Authentication</v>
       </c>
       <c r="C7" t="str">
-        <v>Authentication Automated Verification Case #7</v>
+        <v>Authentication Automated Verification Case #5</v>
       </c>
       <c r="D7" t="str">
-        <v>665ms</v>
+        <v>111ms</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>TC_WEB_AUTH_008</v>
+        <v>TC_WEB_AUTH_006</v>
       </c>
       <c r="B8" t="str">
         <v>Authentication</v>
       </c>
       <c r="C8" t="str">
-        <v>Authentication Automated Verification Case #8</v>
+        <v>Authentication Automated Verification Case #6</v>
       </c>
       <c r="D8" t="str">
-        <v>500ms</v>
+        <v>631ms</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>TC_WEB_AUTH_009</v>
+        <v>TC_WEB_AUTH_007</v>
       </c>
       <c r="B9" t="str">
         <v>Authentication</v>
       </c>
       <c r="C9" t="str">
-        <v>Authentication Automated Verification Case #9</v>
+        <v>Authentication Automated Verification Case #7</v>
       </c>
       <c r="D9" t="str">
-        <v>245ms</v>
+        <v>461ms</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>TC_WEB_AUTH_010</v>
+        <v>TC_WEB_AUTH_008</v>
       </c>
       <c r="B10" t="str">
         <v>Authentication</v>
       </c>
       <c r="C10" t="str">
-        <v>Authentication Automated Verification Case #10</v>
+        <v>Authentication Automated Verification Case #8</v>
       </c>
       <c r="D10" t="str">
-        <v>441ms</v>
+        <v>349ms</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>TC_WEB_AUTH_011</v>
+        <v>TC_WEB_AUTH_009</v>
       </c>
       <c r="B11" t="str">
         <v>Authentication</v>
       </c>
       <c r="C11" t="str">
-        <v>Authentication Automated Verification Case #11</v>
+        <v>Authentication Automated Verification Case #9</v>
       </c>
       <c r="D11" t="str">
-        <v>674ms</v>
+        <v>749ms</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>TC_WEB_AUTH_012</v>
+        <v>TC_WEB_AUTH_010</v>
       </c>
       <c r="B12" t="str">
         <v>Authentication</v>
       </c>
       <c r="C12" t="str">
-        <v>Authentication Automated Verification Case #12</v>
+        <v>Authentication Automated Verification Case #10</v>
       </c>
       <c r="D12" t="str">
-        <v>549ms</v>
+        <v>633ms</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>TC_WEB_AUTH_013</v>
+        <v>TC_WEB_AUTH_011</v>
       </c>
       <c r="B13" t="str">
         <v>Authentication</v>
       </c>
       <c r="C13" t="str">
-        <v>Authentication Automated Verification Case #13</v>
+        <v>Authentication Automated Verification Case #11</v>
       </c>
       <c r="D13" t="str">
-        <v>635ms</v>
+        <v>672ms</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>TC_WEB_AUTH_014</v>
+        <v>TC_WEB_AUTH_012</v>
       </c>
       <c r="B14" t="str">
         <v>Authentication</v>
       </c>
       <c r="C14" t="str">
-        <v>Authentication Automated Verification Case #14</v>
+        <v>Authentication Automated Verification Case #12</v>
       </c>
       <c r="D14" t="str">
-        <v>758ms</v>
+        <v>114ms</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>TC_WEB_AUTH_015</v>
+        <v>TC_WEB_AUTH_013</v>
       </c>
       <c r="B15" t="str">
         <v>Authentication</v>
       </c>
       <c r="C15" t="str">
-        <v>Authentication Automated Verification Case #15</v>
+        <v>Authentication Automated Verification Case #13</v>
       </c>
       <c r="D15" t="str">
-        <v>492ms</v>
+        <v>660ms</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>TC_WEB_AUTH_016</v>
+        <v>TC_WEB_AUTH_014</v>
       </c>
       <c r="B16" t="str">
         <v>Authentication</v>
       </c>
       <c r="C16" t="str">
-        <v>Authentication Automated Verification Case #16</v>
+        <v>Authentication Automated Verification Case #14</v>
       </c>
       <c r="D16" t="str">
-        <v>456ms</v>
+        <v>788ms</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>TC_WEB_AUTH_017</v>
+        <v>TC_WEB_AUTH_015</v>
       </c>
       <c r="B17" t="str">
         <v>Authentication</v>
       </c>
       <c r="C17" t="str">
-        <v>Authentication Automated Verification Case #17</v>
+        <v>Authentication Automated Verification Case #15</v>
       </c>
       <c r="D17" t="str">
-        <v>577ms</v>
+        <v>767ms</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>TC_WEB_AUTH_018</v>
+        <v>TC_WEB_AUTH_016</v>
       </c>
       <c r="B18" t="str">
         <v>Authentication</v>
       </c>
       <c r="C18" t="str">
-        <v>Authentication Automated Verification Case #18</v>
+        <v>Authentication Automated Verification Case #16</v>
       </c>
       <c r="D18" t="str">
-        <v>372ms</v>
+        <v>491ms</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>TC_WEB_AUTH_019</v>
+        <v>TC_WEB_AUTH_017</v>
       </c>
       <c r="B19" t="str">
         <v>Authentication</v>
       </c>
       <c r="C19" t="str">
-        <v>Authentication Automated Verification Case #19</v>
+        <v>Authentication Automated Verification Case #17</v>
       </c>
       <c r="D19" t="str">
-        <v>484ms</v>
+        <v>655ms</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>TC_WEB_AUTH_020</v>
+        <v>TC_WEB_AUTH_018</v>
       </c>
       <c r="B20" t="str">
         <v>Authentication</v>
       </c>
       <c r="C20" t="str">
-        <v>Authentication Automated Verification Case #20</v>
+        <v>Authentication Automated Verification Case #18</v>
       </c>
       <c r="D20" t="str">
-        <v>224ms</v>
+        <v>449ms</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>TC_WEB_AUTH_021</v>
+        <v>TC_WEB_AUTH_019</v>
       </c>
       <c r="B21" t="str">
         <v>Authentication</v>
       </c>
       <c r="C21" t="str">
-        <v>Authentication Automated Verification Case #21</v>
+        <v>Authentication Automated Verification Case #19</v>
       </c>
       <c r="D21" t="str">
-        <v>441ms</v>
+        <v>537ms</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>TC_WEB_AUTH_022</v>
+        <v>TC_WEB_AUTH_020</v>
       </c>
       <c r="B22" t="str">
         <v>Authentication</v>
       </c>
       <c r="C22" t="str">
-        <v>Authentication Automated Verification Case #22</v>
+        <v>Authentication Automated Verification Case #20</v>
       </c>
       <c r="D22" t="str">
-        <v>541ms</v>
+        <v>548ms</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>TC_WEB_AUTH_023</v>
+        <v>TC_WEB_AUTH_021</v>
       </c>
       <c r="B23" t="str">
         <v>Authentication</v>
       </c>
       <c r="C23" t="str">
-        <v>Authentication Automated Verification Case #23</v>
+        <v>Authentication Automated Verification Case #21</v>
       </c>
       <c r="D23" t="str">
-        <v>442ms</v>
+        <v>216ms</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>TC_WEB_AUTH_024</v>
+        <v>TC_WEB_AUTH_022</v>
       </c>
       <c r="B24" t="str">
         <v>Authentication</v>
       </c>
       <c r="C24" t="str">
-        <v>Authentication Automated Verification Case #24</v>
+        <v>Authentication Automated Verification Case #22</v>
       </c>
       <c r="D24" t="str">
-        <v>733ms</v>
+        <v>522ms</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>TC_WEB_AUTH_025</v>
+        <v>TC_WEB_AUTH_023</v>
       </c>
       <c r="B25" t="str">
         <v>Authentication</v>
       </c>
       <c r="C25" t="str">
-        <v>Authentication Automated Verification Case #25</v>
+        <v>Authentication Automated Verification Case #23</v>
       </c>
       <c r="D25" t="str">
-        <v>111ms</v>
+        <v>483ms</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>TC_WEB_AUTH_026</v>
+        <v>TC_WEB_AUTH_024</v>
       </c>
       <c r="B26" t="str">
         <v>Authentication</v>
       </c>
       <c r="C26" t="str">
-        <v>Authentication Automated Verification Case #26</v>
+        <v>Authentication Automated Verification Case #24</v>
       </c>
       <c r="D26" t="str">
-        <v>491ms</v>
+        <v>719ms</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>TC_WEB_AUTH_027</v>
+        <v>TC_WEB_AUTH_025</v>
       </c>
       <c r="B27" t="str">
         <v>Authentication</v>
       </c>
       <c r="C27" t="str">
-        <v>Authentication Automated Verification Case #27</v>
+        <v>Authentication Automated Verification Case #25</v>
       </c>
       <c r="D27" t="str">
-        <v>255ms</v>
+        <v>231ms</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>TC_WEB_AUTH_028</v>
+        <v>TC_WEB_AUTH_026</v>
       </c>
       <c r="B28" t="str">
         <v>Authentication</v>
       </c>
       <c r="C28" t="str">
-        <v>Authentication Automated Verification Case #28</v>
+        <v>Authentication Automated Verification Case #26</v>
       </c>
       <c r="D28" t="str">
-        <v>821ms</v>
+        <v>844ms</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>TC_WEB_AUTH_029</v>
+        <v>TC_WEB_AUTH_027</v>
       </c>
       <c r="B29" t="str">
         <v>Authentication</v>
       </c>
       <c r="C29" t="str">
-        <v>Authentication Automated Verification Case #29</v>
+        <v>Authentication Automated Verification Case #27</v>
       </c>
       <c r="D29" t="str">
-        <v>765ms</v>
+        <v>746ms</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>TC_WEB_AUTH_030</v>
+        <v>TC_WEB_AUTH_028</v>
       </c>
       <c r="B30" t="str">
         <v>Authentication</v>
       </c>
       <c r="C30" t="str">
-        <v>Authentication Automated Verification Case #30</v>
+        <v>Authentication Automated Verification Case #28</v>
       </c>
       <c r="D30" t="str">
-        <v>810ms</v>
+        <v>691ms</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>TC_WEB_AUTH_031</v>
+        <v>TC_WEB_AUTH_029</v>
       </c>
       <c r="B31" t="str">
         <v>Authentication</v>
       </c>
       <c r="C31" t="str">
-        <v>Authentication Automated Verification Case #31</v>
+        <v>Authentication Automated Verification Case #29</v>
       </c>
       <c r="D31" t="str">
-        <v>181ms</v>
+        <v>430ms</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>TC_WEB_AUTH_032</v>
+        <v>TC_WEB_AUTH_030</v>
       </c>
       <c r="B32" t="str">
         <v>Authentication</v>
       </c>
       <c r="C32" t="str">
-        <v>Authentication Automated Verification Case #32</v>
+        <v>Authentication Automated Verification Case #30</v>
       </c>
       <c r="D32" t="str">
-        <v>809ms</v>
+        <v>885ms</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>TC_WEB_AUTH_033</v>
+        <v>TC_WEB_AUTH_031</v>
       </c>
       <c r="B33" t="str">
         <v>Authentication</v>
       </c>
       <c r="C33" t="str">
-        <v>Authentication Automated Verification Case #33</v>
+        <v>Authentication Automated Verification Case #31</v>
       </c>
       <c r="D33" t="str">
-        <v>645ms</v>
+        <v>233ms</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>TC_WEB_AUTH_034</v>
+        <v>TC_WEB_AUTH_032</v>
       </c>
       <c r="B34" t="str">
         <v>Authentication</v>
       </c>
       <c r="C34" t="str">
-        <v>Authentication Automated Verification Case #34</v>
+        <v>Authentication Automated Verification Case #32</v>
       </c>
       <c r="D34" t="str">
-        <v>640ms</v>
+        <v>760ms</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>TC_WEB_AUTH_035</v>
+        <v>TC_WEB_AUTH_033</v>
       </c>
       <c r="B35" t="str">
         <v>Authentication</v>
       </c>
       <c r="C35" t="str">
-        <v>Authentication Automated Verification Case #35</v>
+        <v>Authentication Automated Verification Case #33</v>
       </c>
       <c r="D35" t="str">
-        <v>579ms</v>
+        <v>199ms</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>TC_WEB_AUTH_036</v>
+        <v>TC_WEB_AUTH_034</v>
       </c>
       <c r="B36" t="str">
         <v>Authentication</v>
       </c>
       <c r="C36" t="str">
-        <v>Authentication Automated Verification Case #36</v>
+        <v>Authentication Automated Verification Case #34</v>
       </c>
       <c r="D36" t="str">
-        <v>766ms</v>
+        <v>365ms</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>TC_WEB_AUTH_037</v>
+        <v>TC_WEB_AUTH_035</v>
       </c>
       <c r="B37" t="str">
         <v>Authentication</v>
       </c>
       <c r="C37" t="str">
-        <v>Authentication Automated Verification Case #37</v>
+        <v>Authentication Automated Verification Case #35</v>
       </c>
       <c r="D37" t="str">
-        <v>209ms</v>
+        <v>879ms</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>TC_WEB_AUTH_038</v>
+        <v>TC_WEB_AUTH_036</v>
       </c>
       <c r="B38" t="str">
         <v>Authentication</v>
       </c>
       <c r="C38" t="str">
-        <v>Authentication Automated Verification Case #38</v>
+        <v>Authentication Automated Verification Case #36</v>
       </c>
       <c r="D38" t="str">
-        <v>161ms</v>
+        <v>208ms</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>TC_WEB_AUTH_039</v>
+        <v>TC_WEB_AUTH_037</v>
       </c>
       <c r="B39" t="str">
         <v>Authentication</v>
       </c>
       <c r="C39" t="str">
-        <v>Authentication Automated Verification Case #39</v>
+        <v>Authentication Automated Verification Case #37</v>
       </c>
       <c r="D39" t="str">
-        <v>522ms</v>
+        <v>337ms</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>TC_WEB_AUTH_040</v>
+        <v>TC_WEB_AUTH_038</v>
       </c>
       <c r="B40" t="str">
         <v>Authentication</v>
       </c>
       <c r="C40" t="str">
-        <v>Authentication Automated Verification Case #40</v>
+        <v>Authentication Automated Verification Case #38</v>
       </c>
       <c r="D40" t="str">
-        <v>788ms</v>
+        <v>888ms</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>TC_WEB_AUTHZ_001</v>
+        <v>TC_WEB_AUTH_039</v>
       </c>
       <c r="B41" t="str">
-        <v>Authorization</v>
+        <v>Authentication</v>
       </c>
       <c r="C41" t="str">
-        <v>Authorization Automated Verification Case #1</v>
+        <v>Authentication Automated Verification Case #39</v>
       </c>
       <c r="D41" t="str">
-        <v>139ms</v>
+        <v>170ms</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>TC_WEB_AUTHZ_002</v>
+        <v>TC_WEB_AUTH_040</v>
       </c>
       <c r="B42" t="str">
-        <v>Authorization</v>
+        <v>Authentication</v>
       </c>
       <c r="C42" t="str">
-        <v>Authorization Automated Verification Case #2</v>
+        <v>Authentication Automated Verification Case #40</v>
       </c>
       <c r="D42" t="str">
-        <v>747ms</v>
+        <v>272ms</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>TC_WEB_AUTHZ_003</v>
+        <v>TC_WEB_AUTHZ_001</v>
       </c>
       <c r="B43" t="str">
         <v>Authorization</v>
       </c>
       <c r="C43" t="str">
-        <v>Authorization Automated Verification Case #3</v>
+        <v>Authorization Automated Verification Case #1</v>
       </c>
       <c r="D43" t="str">
-        <v>573ms</v>
+        <v>326ms</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>TC_WEB_AUTHZ_004</v>
+        <v>TC_WEB_AUTHZ_002</v>
       </c>
       <c r="B44" t="str">
         <v>Authorization</v>
       </c>
       <c r="C44" t="str">
-        <v>Authorization Automated Verification Case #4</v>
+        <v>Authorization Automated Verification Case #2</v>
       </c>
       <c r="D44" t="str">
-        <v>192ms</v>
+        <v>351ms</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>TC_WEB_AUTHZ_005</v>
+        <v>TC_WEB_AUTHZ_003</v>
       </c>
       <c r="B45" t="str">
         <v>Authorization</v>
       </c>
       <c r="C45" t="str">
-        <v>Authorization Automated Verification Case #5</v>
+        <v>Authorization Automated Verification Case #3</v>
       </c>
       <c r="D45" t="str">
-        <v>199ms</v>
+        <v>629ms</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>TC_WEB_AUTHZ_006</v>
+        <v>TC_WEB_AUTHZ_004</v>
       </c>
       <c r="B46" t="str">
         <v>Authorization</v>
       </c>
       <c r="C46" t="str">
-        <v>Authorization Automated Verification Case #6</v>
+        <v>Authorization Automated Verification Case #4</v>
       </c>
       <c r="D46" t="str">
-        <v>212ms</v>
+        <v>535ms</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>TC_WEB_AUTHZ_007</v>
+        <v>TC_WEB_AUTHZ_005</v>
       </c>
       <c r="B47" t="str">
         <v>Authorization</v>
       </c>
       <c r="C47" t="str">
-        <v>Authorization Automated Verification Case #7</v>
+        <v>Authorization Automated Verification Case #5</v>
       </c>
       <c r="D47" t="str">
-        <v>383ms</v>
+        <v>470ms</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>TC_WEB_AUTHZ_008</v>
+        <v>TC_WEB_AUTHZ_006</v>
       </c>
       <c r="B48" t="str">
         <v>Authorization</v>
       </c>
       <c r="C48" t="str">
-        <v>Authorization Automated Verification Case #8</v>
+        <v>Authorization Automated Verification Case #6</v>
       </c>
       <c r="D48" t="str">
-        <v>635ms</v>
+        <v>442ms</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>TC_WEB_AUTHZ_009</v>
+        <v>TC_WEB_AUTHZ_007</v>
       </c>
       <c r="B49" t="str">
         <v>Authorization</v>
       </c>
       <c r="C49" t="str">
-        <v>Authorization Automated Verification Case #9</v>
+        <v>Authorization Automated Verification Case #7</v>
       </c>
       <c r="D49" t="str">
-        <v>420ms</v>
+        <v>258ms</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>TC_WEB_AUTHZ_010</v>
+        <v>TC_WEB_AUTHZ_008</v>
       </c>
       <c r="B50" t="str">
         <v>Authorization</v>
       </c>
       <c r="C50" t="str">
-        <v>Authorization Automated Verification Case #10</v>
+        <v>Authorization Automated Verification Case #8</v>
       </c>
       <c r="D50" t="str">
-        <v>856ms</v>
+        <v>838ms</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>TC_WEB_AUTHZ_011</v>
+        <v>TC_WEB_AUTHZ_009</v>
       </c>
       <c r="B51" t="str">
         <v>Authorization</v>
       </c>
       <c r="C51" t="str">
-        <v>Authorization Automated Verification Case #11</v>
+        <v>Authorization Automated Verification Case #9</v>
       </c>
       <c r="D51" t="str">
-        <v>145ms</v>
+        <v>308ms</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>TC_WEB_AUTHZ_012</v>
+        <v>TC_WEB_AUTHZ_010</v>
       </c>
       <c r="B52" t="str">
         <v>Authorization</v>
       </c>
       <c r="C52" t="str">
-        <v>Authorization Automated Verification Case #12</v>
+        <v>Authorization Automated Verification Case #10</v>
       </c>
       <c r="D52" t="str">
-        <v>348ms</v>
+        <v>221ms</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>TC_WEB_AUTHZ_013</v>
+        <v>TC_WEB_AUTHZ_011</v>
       </c>
       <c r="B53" t="str">
         <v>Authorization</v>
       </c>
       <c r="C53" t="str">
-        <v>Authorization Automated Verification Case #13</v>
+        <v>Authorization Automated Verification Case #11</v>
       </c>
       <c r="D53" t="str">
-        <v>506ms</v>
+        <v>748ms</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>TC_WEB_AUTHZ_014</v>
+        <v>TC_WEB_AUTHZ_012</v>
       </c>
       <c r="B54" t="str">
         <v>Authorization</v>
       </c>
       <c r="C54" t="str">
-        <v>Authorization Automated Verification Case #14</v>
+        <v>Authorization Automated Verification Case #12</v>
       </c>
       <c r="D54" t="str">
-        <v>586ms</v>
+        <v>774ms</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>TC_WEB_AUTHZ_015</v>
+        <v>TC_WEB_AUTHZ_013</v>
       </c>
       <c r="B55" t="str">
         <v>Authorization</v>
       </c>
       <c r="C55" t="str">
-        <v>Authorization Automated Verification Case #15</v>
+        <v>Authorization Automated Verification Case #13</v>
       </c>
       <c r="D55" t="str">
-        <v>386ms</v>
+        <v>170ms</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>TC_WEB_AUTHZ_016</v>
+        <v>TC_WEB_AUTHZ_014</v>
       </c>
       <c r="B56" t="str">
         <v>Authorization</v>
       </c>
       <c r="C56" t="str">
-        <v>Authorization Automated Verification Case #16</v>
+        <v>Authorization Automated Verification Case #14</v>
       </c>
       <c r="D56" t="str">
-        <v>833ms</v>
+        <v>600ms</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>TC_WEB_AUTHZ_017</v>
+        <v>TC_WEB_AUTHZ_015</v>
       </c>
       <c r="B57" t="str">
         <v>Authorization</v>
       </c>
       <c r="C57" t="str">
-        <v>Authorization Automated Verification Case #17</v>
+        <v>Authorization Automated Verification Case #15</v>
       </c>
       <c r="D57" t="str">
-        <v>483ms</v>
+        <v>579ms</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>TC_WEB_AUTHZ_018</v>
+        <v>TC_WEB_AUTHZ_016</v>
       </c>
       <c r="B58" t="str">
         <v>Authorization</v>
       </c>
       <c r="C58" t="str">
-        <v>Authorization Automated Verification Case #18</v>
+        <v>Authorization Automated Verification Case #16</v>
       </c>
       <c r="D58" t="str">
-        <v>801ms</v>
+        <v>874ms</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>TC_WEB_AUTHZ_019</v>
+        <v>TC_WEB_AUTHZ_017</v>
       </c>
       <c r="B59" t="str">
         <v>Authorization</v>
       </c>
       <c r="C59" t="str">
-        <v>Authorization Automated Verification Case #19</v>
+        <v>Authorization Automated Verification Case #17</v>
       </c>
       <c r="D59" t="str">
-        <v>624ms</v>
+        <v>166ms</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>TC_WEB_AUTHZ_020</v>
+        <v>TC_WEB_AUTHZ_018</v>
       </c>
       <c r="B60" t="str">
         <v>Authorization</v>
       </c>
       <c r="C60" t="str">
-        <v>Authorization Automated Verification Case #20</v>
+        <v>Authorization Automated Verification Case #18</v>
       </c>
       <c r="D60" t="str">
-        <v>601ms</v>
+        <v>498ms</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>TC_WEB_AUTHZ_021</v>
+        <v>TC_WEB_AUTHZ_019</v>
       </c>
       <c r="B61" t="str">
         <v>Authorization</v>
       </c>
       <c r="C61" t="str">
-        <v>Authorization Automated Verification Case #21</v>
+        <v>Authorization Automated Verification Case #19</v>
       </c>
       <c r="D61" t="str">
-        <v>450ms</v>
+        <v>300ms</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>TC_WEB_AUTHZ_022</v>
+        <v>TC_WEB_AUTHZ_020</v>
       </c>
       <c r="B62" t="str">
         <v>Authorization</v>
       </c>
       <c r="C62" t="str">
-        <v>Authorization Automated Verification Case #22</v>
+        <v>Authorization Automated Verification Case #20</v>
       </c>
       <c r="D62" t="str">
-        <v>350ms</v>
+        <v>681ms</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>TC_WEB_AUTHZ_023</v>
+        <v>TC_WEB_AUTHZ_021</v>
       </c>
       <c r="B63" t="str">
         <v>Authorization</v>
       </c>
       <c r="C63" t="str">
-        <v>Authorization Automated Verification Case #23</v>
+        <v>Authorization Automated Verification Case #21</v>
       </c>
       <c r="D63" t="str">
-        <v>484ms</v>
+        <v>415ms</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>TC_WEB_AUTHZ_024</v>
+        <v>TC_WEB_AUTHZ_022</v>
       </c>
       <c r="B64" t="str">
         <v>Authorization</v>
       </c>
       <c r="C64" t="str">
-        <v>Authorization Automated Verification Case #24</v>
+        <v>Authorization Automated Verification Case #22</v>
       </c>
       <c r="D64" t="str">
-        <v>230ms</v>
+        <v>754ms</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>TC_WEB_AUTHZ_025</v>
+        <v>TC_WEB_AUTHZ_023</v>
       </c>
       <c r="B65" t="str">
         <v>Authorization</v>
       </c>
       <c r="C65" t="str">
-        <v>Authorization Automated Verification Case #25</v>
+        <v>Authorization Automated Verification Case #23</v>
       </c>
       <c r="D65" t="str">
-        <v>878ms</v>
+        <v>889ms</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>TC_WEB_AUTHZ_026</v>
+        <v>TC_WEB_AUTHZ_024</v>
       </c>
       <c r="B66" t="str">
         <v>Authorization</v>
       </c>
       <c r="C66" t="str">
-        <v>Authorization Automated Verification Case #26</v>
+        <v>Authorization Automated Verification Case #24</v>
       </c>
       <c r="D66" t="str">
-        <v>351ms</v>
+        <v>631ms</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>TC_WEB_AUTHZ_027</v>
+        <v>TC_WEB_AUTHZ_025</v>
       </c>
       <c r="B67" t="str">
         <v>Authorization</v>
       </c>
       <c r="C67" t="str">
-        <v>Authorization Automated Verification Case #27</v>
+        <v>Authorization Automated Verification Case #25</v>
       </c>
       <c r="D67" t="str">
-        <v>409ms</v>
+        <v>541ms</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>TC_WEB_AUTHZ_028</v>
+        <v>TC_WEB_AUTHZ_026</v>
       </c>
       <c r="B68" t="str">
         <v>Authorization</v>
       </c>
       <c r="C68" t="str">
-        <v>Authorization Automated Verification Case #28</v>
+        <v>Authorization Automated Verification Case #26</v>
       </c>
       <c r="D68" t="str">
-        <v>570ms</v>
+        <v>527ms</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>TC_WEB_AUTHZ_029</v>
+        <v>TC_WEB_AUTHZ_027</v>
       </c>
       <c r="B69" t="str">
         <v>Authorization</v>
       </c>
       <c r="C69" t="str">
-        <v>Authorization Automated Verification Case #29</v>
+        <v>Authorization Automated Verification Case #27</v>
       </c>
       <c r="D69" t="str">
-        <v>843ms</v>
+        <v>825ms</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>TC_WEB_AUTHZ_030</v>
+        <v>TC_WEB_AUTHZ_028</v>
       </c>
       <c r="B70" t="str">
         <v>Authorization</v>
       </c>
       <c r="C70" t="str">
-        <v>Authorization Automated Verification Case #30</v>
+        <v>Authorization Automated Verification Case #28</v>
       </c>
       <c r="D70" t="str">
-        <v>666ms</v>
+        <v>683ms</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>TC_WEB_AUTHZ_031</v>
+        <v>TC_WEB_AUTHZ_029</v>
       </c>
       <c r="B71" t="str">
         <v>Authorization</v>
       </c>
       <c r="C71" t="str">
-        <v>Authorization Automated Verification Case #31</v>
+        <v>Authorization Automated Verification Case #29</v>
       </c>
       <c r="D71" t="str">
-        <v>768ms</v>
+        <v>752ms</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>TC_WEB_AUTHZ_032</v>
+        <v>TC_WEB_AUTHZ_030</v>
       </c>
       <c r="B72" t="str">
         <v>Authorization</v>
       </c>
       <c r="C72" t="str">
-        <v>Authorization Automated Verification Case #32</v>
+        <v>Authorization Automated Verification Case #30</v>
       </c>
       <c r="D72" t="str">
-        <v>161ms</v>
+        <v>559ms</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>TC_WEB_AUTHZ_033</v>
+        <v>TC_WEB_AUTHZ_031</v>
       </c>
       <c r="B73" t="str">
         <v>Authorization</v>
       </c>
       <c r="C73" t="str">
-        <v>Authorization Automated Verification Case #33</v>
+        <v>Authorization Automated Verification Case #31</v>
       </c>
       <c r="D73" t="str">
-        <v>579ms</v>
+        <v>464ms</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>TC_WEB_AUTHZ_034</v>
+        <v>TC_WEB_AUTHZ_032</v>
       </c>
       <c r="B74" t="str">
         <v>Authorization</v>
       </c>
       <c r="C74" t="str">
-        <v>Authorization Automated Verification Case #34</v>
+        <v>Authorization Automated Verification Case #32</v>
       </c>
       <c r="D74" t="str">
-        <v>815ms</v>
+        <v>371ms</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>TC_WEB_AUTHZ_035</v>
+        <v>TC_WEB_AUTHZ_033</v>
       </c>
       <c r="B75" t="str">
         <v>Authorization</v>
       </c>
       <c r="C75" t="str">
-        <v>Authorization Automated Verification Case #35</v>
+        <v>Authorization Automated Verification Case #33</v>
       </c>
       <c r="D75" t="str">
-        <v>350ms</v>
+        <v>231ms</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>TC_WEB_AUTHZ_036</v>
+        <v>TC_WEB_AUTHZ_034</v>
       </c>
       <c r="B76" t="str">
         <v>Authorization</v>
       </c>
       <c r="C76" t="str">
-        <v>Authorization Automated Verification Case #36</v>
+        <v>Authorization Automated Verification Case #34</v>
       </c>
       <c r="D76" t="str">
-        <v>361ms</v>
+        <v>216ms</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>TC_WEB_AUTHZ_037</v>
+        <v>TC_WEB_AUTHZ_035</v>
       </c>
       <c r="B77" t="str">
         <v>Authorization</v>
       </c>
       <c r="C77" t="str">
-        <v>Authorization Automated Verification Case #37</v>
+        <v>Authorization Automated Verification Case #35</v>
       </c>
       <c r="D77" t="str">
-        <v>200ms</v>
+        <v>367ms</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>TC_WEB_AUTHZ_038</v>
+        <v>TC_WEB_AUTHZ_036</v>
       </c>
       <c r="B78" t="str">
         <v>Authorization</v>
       </c>
       <c r="C78" t="str">
-        <v>Authorization Automated Verification Case #38</v>
+        <v>Authorization Automated Verification Case #36</v>
       </c>
       <c r="D78" t="str">
-        <v>334ms</v>
+        <v>224ms</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>TC_WEB_AUTHZ_039</v>
+        <v>TC_WEB_AUTHZ_037</v>
       </c>
       <c r="B79" t="str">
         <v>Authorization</v>
       </c>
       <c r="C79" t="str">
-        <v>Authorization Automated Verification Case #39</v>
+        <v>Authorization Automated Verification Case #37</v>
       </c>
       <c r="D79" t="str">
-        <v>524ms</v>
+        <v>691ms</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>TC_WEB_AUTHZ_040</v>
+        <v>TC_WEB_AUTHZ_038</v>
       </c>
       <c r="B80" t="str">
         <v>Authorization</v>
       </c>
       <c r="C80" t="str">
-        <v>Authorization Automated Verification Case #40</v>
+        <v>Authorization Automated Verification Case #38</v>
       </c>
       <c r="D80" t="str">
-        <v>594ms</v>
+        <v>260ms</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>TC_WEB_NAV_001</v>
+        <v>TC_WEB_AUTHZ_039</v>
       </c>
       <c r="B81" t="str">
-        <v>Navigation</v>
+        <v>Authorization</v>
       </c>
       <c r="C81" t="str">
-        <v>Navigation Automated Verification Case #1</v>
+        <v>Authorization Automated Verification Case #39</v>
       </c>
       <c r="D81" t="str">
-        <v>150ms</v>
+        <v>680ms</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>TC_WEB_NAV_002</v>
+        <v>TC_WEB_AUTHZ_040</v>
       </c>
       <c r="B82" t="str">
-        <v>Navigation</v>
+        <v>Authorization</v>
       </c>
       <c r="C82" t="str">
-        <v>Navigation Automated Verification Case #2</v>
+        <v>Authorization Automated Verification Case #40</v>
       </c>
       <c r="D82" t="str">
-        <v>192ms</v>
+        <v>393ms</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>TC_WEB_NAV_003</v>
+        <v>TC_WEB_NAV_001</v>
       </c>
       <c r="B83" t="str">
         <v>Navigation</v>
       </c>
       <c r="C83" t="str">
-        <v>Navigation Automated Verification Case #3</v>
+        <v>Navigation Automated Verification Case #1</v>
       </c>
       <c r="D83" t="str">
-        <v>863ms</v>
+        <v>510ms</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>TC_WEB_NAV_004</v>
+        <v>TC_WEB_NAV_002</v>
       </c>
       <c r="B84" t="str">
         <v>Navigation</v>
       </c>
       <c r="C84" t="str">
-        <v>Navigation Automated Verification Case #4</v>
+        <v>Navigation Automated Verification Case #2</v>
       </c>
       <c r="D84" t="str">
-        <v>822ms</v>
+        <v>458ms</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>TC_WEB_NAV_005</v>
+        <v>TC_WEB_NAV_003</v>
       </c>
       <c r="B85" t="str">
         <v>Navigation</v>
       </c>
       <c r="C85" t="str">
-        <v>Navigation Automated Verification Case #5</v>
+        <v>Navigation Automated Verification Case #3</v>
       </c>
       <c r="D85" t="str">
-        <v>719ms</v>
+        <v>590ms</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>TC_WEB_NAV_006</v>
+        <v>TC_WEB_NAV_004</v>
       </c>
       <c r="B86" t="str">
         <v>Navigation</v>
       </c>
       <c r="C86" t="str">
-        <v>Navigation Automated Verification Case #6</v>
+        <v>Navigation Automated Verification Case #4</v>
       </c>
       <c r="D86" t="str">
-        <v>341ms</v>
+        <v>714ms</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>TC_WEB_NAV_007</v>
+        <v>TC_WEB_NAV_005</v>
       </c>
       <c r="B87" t="str">
         <v>Navigation</v>
       </c>
       <c r="C87" t="str">
-        <v>Navigation Automated Verification Case #7</v>
+        <v>Navigation Automated Verification Case #5</v>
       </c>
       <c r="D87" t="str">
-        <v>632ms</v>
+        <v>620ms</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>TC_WEB_NAV_008</v>
+        <v>TC_WEB_NAV_006</v>
       </c>
       <c r="B88" t="str">
         <v>Navigation</v>
       </c>
       <c r="C88" t="str">
-        <v>Navigation Automated Verification Case #8</v>
+        <v>Navigation Automated Verification Case #6</v>
       </c>
       <c r="D88" t="str">
-        <v>137ms</v>
+        <v>637ms</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>TC_WEB_NAV_009</v>
+        <v>TC_WEB_NAV_007</v>
       </c>
       <c r="B89" t="str">
         <v>Navigation</v>
       </c>
       <c r="C89" t="str">
-        <v>Navigation Automated Verification Case #9</v>
+        <v>Navigation Automated Verification Case #7</v>
       </c>
       <c r="D89" t="str">
-        <v>137ms</v>
+        <v>816ms</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>TC_WEB_NAV_010</v>
+        <v>TC_WEB_NAV_008</v>
       </c>
       <c r="B90" t="str">
         <v>Navigation</v>
       </c>
       <c r="C90" t="str">
-        <v>Navigation Automated Verification Case #10</v>
+        <v>Navigation Automated Verification Case #8</v>
       </c>
       <c r="D90" t="str">
-        <v>883ms</v>
+        <v>241ms</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>TC_WEB_NAV_011</v>
+        <v>TC_WEB_NAV_009</v>
       </c>
       <c r="B91" t="str">
         <v>Navigation</v>
       </c>
       <c r="C91" t="str">
-        <v>Navigation Automated Verification Case #11</v>
+        <v>Navigation Automated Verification Case #9</v>
       </c>
       <c r="D91" t="str">
-        <v>625ms</v>
+        <v>127ms</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>TC_WEB_NAV_012</v>
+        <v>TC_WEB_NAV_010</v>
       </c>
       <c r="B92" t="str">
         <v>Navigation</v>
       </c>
       <c r="C92" t="str">
-        <v>Navigation Automated Verification Case #12</v>
+        <v>Navigation Automated Verification Case #10</v>
       </c>
       <c r="D92" t="str">
-        <v>192ms</v>
+        <v>670ms</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>TC_WEB_NAV_013</v>
+        <v>TC_WEB_NAV_011</v>
       </c>
       <c r="B93" t="str">
         <v>Navigation</v>
       </c>
       <c r="C93" t="str">
-        <v>Navigation Automated Verification Case #13</v>
+        <v>Navigation Automated Verification Case #11</v>
       </c>
       <c r="D93" t="str">
-        <v>610ms</v>
+        <v>259ms</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>TC_WEB_NAV_014</v>
+        <v>TC_WEB_NAV_012</v>
       </c>
       <c r="B94" t="str">
         <v>Navigation</v>
       </c>
       <c r="C94" t="str">
-        <v>Navigation Automated Verification Case #14</v>
+        <v>Navigation Automated Verification Case #12</v>
       </c>
       <c r="D94" t="str">
-        <v>638ms</v>
+        <v>864ms</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>TC_WEB_NAV_015</v>
+        <v>TC_WEB_NAV_013</v>
       </c>
       <c r="B95" t="str">
         <v>Navigation</v>
       </c>
       <c r="C95" t="str">
-        <v>Navigation Automated Verification Case #15</v>
+        <v>Navigation Automated Verification Case #13</v>
       </c>
       <c r="D95" t="str">
-        <v>513ms</v>
+        <v>485ms</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>TC_WEB_NAV_016</v>
+        <v>TC_WEB_NAV_014</v>
       </c>
       <c r="B96" t="str">
         <v>Navigation</v>
       </c>
       <c r="C96" t="str">
-        <v>Navigation Automated Verification Case #16</v>
+        <v>Navigation Automated Verification Case #14</v>
       </c>
       <c r="D96" t="str">
-        <v>437ms</v>
+        <v>272ms</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>TC_WEB_NAV_017</v>
+        <v>TC_WEB_NAV_015</v>
       </c>
       <c r="B97" t="str">
         <v>Navigation</v>
       </c>
       <c r="C97" t="str">
-        <v>Navigation Automated Verification Case #17</v>
+        <v>Navigation Automated Verification Case #15</v>
       </c>
       <c r="D97" t="str">
-        <v>117ms</v>
+        <v>217ms</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>TC_WEB_NAV_018</v>
+        <v>TC_WEB_NAV_016</v>
       </c>
       <c r="B98" t="str">
         <v>Navigation</v>
       </c>
       <c r="C98" t="str">
-        <v>Navigation Automated Verification Case #18</v>
+        <v>Navigation Automated Verification Case #16</v>
       </c>
       <c r="D98" t="str">
-        <v>656ms</v>
+        <v>184ms</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>TC_WEB_NAV_019</v>
+        <v>TC_WEB_NAV_017</v>
       </c>
       <c r="B99" t="str">
         <v>Navigation</v>
       </c>
       <c r="C99" t="str">
-        <v>Navigation Automated Verification Case #19</v>
+        <v>Navigation Automated Verification Case #17</v>
       </c>
       <c r="D99" t="str">
-        <v>703ms</v>
+        <v>486ms</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>TC_WEB_NAV_020</v>
+        <v>TC_WEB_NAV_018</v>
       </c>
       <c r="B100" t="str">
         <v>Navigation</v>
       </c>
       <c r="C100" t="str">
-        <v>Navigation Automated Verification Case #20</v>
+        <v>Navigation Automated Verification Case #18</v>
       </c>
       <c r="D100" t="str">
-        <v>719ms</v>
+        <v>398ms</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>TC_WEB_NAV_021</v>
+        <v>TC_WEB_NAV_019</v>
       </c>
       <c r="B101" t="str">
         <v>Navigation</v>
       </c>
       <c r="C101" t="str">
-        <v>Navigation Automated Verification Case #21</v>
+        <v>Navigation Automated Verification Case #19</v>
       </c>
       <c r="D101" t="str">
-        <v>345ms</v>
+        <v>750ms</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>TC_WEB_NAV_022</v>
+        <v>TC_WEB_NAV_020</v>
       </c>
       <c r="B102" t="str">
         <v>Navigation</v>
       </c>
       <c r="C102" t="str">
-        <v>Navigation Automated Verification Case #22</v>
+        <v>Navigation Automated Verification Case #20</v>
       </c>
       <c r="D102" t="str">
-        <v>388ms</v>
+        <v>133ms</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>TC_WEB_NAV_023</v>
+        <v>TC_WEB_NAV_021</v>
       </c>
       <c r="B103" t="str">
         <v>Navigation</v>
       </c>
       <c r="C103" t="str">
-        <v>Navigation Automated Verification Case #23</v>
+        <v>Navigation Automated Verification Case #21</v>
       </c>
       <c r="D103" t="str">
-        <v>828ms</v>
+        <v>631ms</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>TC_WEB_NAV_024</v>
+        <v>TC_WEB_NAV_022</v>
       </c>
       <c r="B104" t="str">
         <v>Navigation</v>
       </c>
       <c r="C104" t="str">
-        <v>Navigation Automated Verification Case #24</v>
+        <v>Navigation Automated Verification Case #22</v>
       </c>
       <c r="D104" t="str">
-        <v>240ms</v>
+        <v>377ms</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>TC_WEB_NAV_025</v>
+        <v>TC_WEB_NAV_023</v>
       </c>
       <c r="B105" t="str">
         <v>Navigation</v>
       </c>
       <c r="C105" t="str">
-        <v>Navigation Automated Verification Case #25</v>
+        <v>Navigation Automated Verification Case #23</v>
       </c>
       <c r="D105" t="str">
-        <v>291ms</v>
+        <v>631ms</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>TC_WEB_NAV_026</v>
+        <v>TC_WEB_NAV_024</v>
       </c>
       <c r="B106" t="str">
         <v>Navigation</v>
       </c>
       <c r="C106" t="str">
-        <v>Navigation Automated Verification Case #26</v>
+        <v>Navigation Automated Verification Case #24</v>
       </c>
       <c r="D106" t="str">
-        <v>676ms</v>
+        <v>145ms</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>TC_WEB_NAV_027</v>
+        <v>TC_WEB_NAV_025</v>
       </c>
       <c r="B107" t="str">
         <v>Navigation</v>
       </c>
       <c r="C107" t="str">
-        <v>Navigation Automated Verification Case #27</v>
+        <v>Navigation Automated Verification Case #25</v>
       </c>
       <c r="D107" t="str">
-        <v>894ms</v>
+        <v>566ms</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>TC_WEB_NAV_028</v>
+        <v>TC_WEB_NAV_026</v>
       </c>
       <c r="B108" t="str">
         <v>Navigation</v>
       </c>
       <c r="C108" t="str">
-        <v>Navigation Automated Verification Case #28</v>
+        <v>Navigation Automated Verification Case #26</v>
       </c>
       <c r="D108" t="str">
-        <v>662ms</v>
+        <v>310ms</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>TC_WEB_NAV_029</v>
+        <v>TC_WEB_NAV_027</v>
       </c>
       <c r="B109" t="str">
         <v>Navigation</v>
       </c>
       <c r="C109" t="str">
-        <v>Navigation Automated Verification Case #29</v>
+        <v>Navigation Automated Verification Case #27</v>
       </c>
       <c r="D109" t="str">
-        <v>111ms</v>
+        <v>235ms</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>TC_WEB_NAV_030</v>
+        <v>TC_WEB_NAV_028</v>
       </c>
       <c r="B110" t="str">
         <v>Navigation</v>
       </c>
       <c r="C110" t="str">
-        <v>Navigation Automated Verification Case #30</v>
+        <v>Navigation Automated Verification Case #28</v>
       </c>
       <c r="D110" t="str">
-        <v>440ms</v>
+        <v>692ms</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>TC_WEB_UI_001</v>
+        <v>TC_WEB_NAV_029</v>
       </c>
       <c r="B111" t="str">
-        <v>UI Validation</v>
+        <v>Navigation</v>
       </c>
       <c r="C111" t="str">
-        <v>UI Validation Automated Verification Case #1</v>
+        <v>Navigation Automated Verification Case #29</v>
       </c>
       <c r="D111" t="str">
-        <v>195ms</v>
+        <v>887ms</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>TC_WEB_UI_002</v>
+        <v>TC_WEB_NAV_030</v>
       </c>
       <c r="B112" t="str">
-        <v>UI Validation</v>
+        <v>Navigation</v>
       </c>
       <c r="C112" t="str">
-        <v>UI Validation Automated Verification Case #2</v>
+        <v>Navigation Automated Verification Case #30</v>
       </c>
       <c r="D112" t="str">
-        <v>828ms</v>
+        <v>617ms</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>TC_WEB_UI_003</v>
+        <v>TC_WEB_UI_001</v>
       </c>
       <c r="B113" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C113" t="str">
-        <v>UI Validation Automated Verification Case #3</v>
+        <v>UI Validation Automated Verification Case #1</v>
       </c>
       <c r="D113" t="str">
-        <v>561ms</v>
+        <v>439ms</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>TC_WEB_UI_004</v>
+        <v>TC_WEB_UI_002</v>
       </c>
       <c r="B114" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C114" t="str">
-        <v>UI Validation Automated Verification Case #4</v>
+        <v>UI Validation Automated Verification Case #2</v>
       </c>
       <c r="D114" t="str">
-        <v>544ms</v>
+        <v>131ms</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>TC_WEB_UI_005</v>
+        <v>TC_WEB_UI_003</v>
       </c>
       <c r="B115" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C115" t="str">
-        <v>UI Validation Automated Verification Case #5</v>
+        <v>UI Validation Automated Verification Case #3</v>
       </c>
       <c r="D115" t="str">
-        <v>864ms</v>
+        <v>835ms</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>TC_WEB_UI_006</v>
+        <v>TC_WEB_UI_004</v>
       </c>
       <c r="B116" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C116" t="str">
-        <v>UI Validation Automated Verification Case #6</v>
+        <v>UI Validation Automated Verification Case #4</v>
       </c>
       <c r="D116" t="str">
-        <v>394ms</v>
+        <v>205ms</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>TC_WEB_UI_007</v>
+        <v>TC_WEB_UI_005</v>
       </c>
       <c r="B117" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C117" t="str">
-        <v>UI Validation Automated Verification Case #7</v>
+        <v>UI Validation Automated Verification Case #5</v>
       </c>
       <c r="D117" t="str">
-        <v>571ms</v>
+        <v>863ms</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>TC_WEB_UI_008</v>
+        <v>TC_WEB_UI_006</v>
       </c>
       <c r="B118" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C118" t="str">
-        <v>UI Validation Automated Verification Case #8</v>
+        <v>UI Validation Automated Verification Case #6</v>
       </c>
       <c r="D118" t="str">
-        <v>898ms</v>
+        <v>230ms</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>TC_WEB_UI_009</v>
+        <v>TC_WEB_UI_007</v>
       </c>
       <c r="B119" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C119" t="str">
-        <v>UI Validation Automated Verification Case #9</v>
+        <v>UI Validation Automated Verification Case #7</v>
       </c>
       <c r="D119" t="str">
-        <v>639ms</v>
+        <v>193ms</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>TC_WEB_UI_010</v>
+        <v>TC_WEB_UI_008</v>
       </c>
       <c r="B120" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C120" t="str">
-        <v>UI Validation Automated Verification Case #10</v>
+        <v>UI Validation Automated Verification Case #8</v>
       </c>
       <c r="D120" t="str">
-        <v>208ms</v>
+        <v>302ms</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>TC_WEB_UI_011</v>
+        <v>TC_WEB_UI_009</v>
       </c>
       <c r="B121" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C121" t="str">
-        <v>UI Validation Automated Verification Case #11</v>
+        <v>UI Validation Automated Verification Case #9</v>
       </c>
       <c r="D121" t="str">
-        <v>761ms</v>
+        <v>664ms</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>TC_WEB_UI_012</v>
+        <v>TC_WEB_UI_010</v>
       </c>
       <c r="B122" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C122" t="str">
-        <v>UI Validation Automated Verification Case #12</v>
+        <v>UI Validation Automated Verification Case #10</v>
       </c>
       <c r="D122" t="str">
-        <v>622ms</v>
+        <v>346ms</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>TC_WEB_UI_013</v>
+        <v>TC_WEB_UI_011</v>
       </c>
       <c r="B123" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C123" t="str">
-        <v>UI Validation Automated Verification Case #13</v>
+        <v>UI Validation Automated Verification Case #11</v>
       </c>
       <c r="D123" t="str">
-        <v>560ms</v>
+        <v>191ms</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>TC_WEB_UI_014</v>
+        <v>TC_WEB_UI_012</v>
       </c>
       <c r="B124" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C124" t="str">
-        <v>UI Validation Automated Verification Case #14</v>
+        <v>UI Validation Automated Verification Case #12</v>
       </c>
       <c r="D124" t="str">
-        <v>437ms</v>
+        <v>367ms</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>TC_WEB_UI_015</v>
+        <v>TC_WEB_UI_013</v>
       </c>
       <c r="B125" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C125" t="str">
-        <v>UI Validation Automated Verification Case #15</v>
+        <v>UI Validation Automated Verification Case #13</v>
       </c>
       <c r="D125" t="str">
-        <v>639ms</v>
+        <v>396ms</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>TC_WEB_UI_016</v>
+        <v>TC_WEB_UI_014</v>
       </c>
       <c r="B126" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C126" t="str">
-        <v>UI Validation Automated Verification Case #16</v>
+        <v>UI Validation Automated Verification Case #14</v>
       </c>
       <c r="D126" t="str">
-        <v>242ms</v>
+        <v>236ms</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>TC_WEB_UI_017</v>
+        <v>TC_WEB_UI_015</v>
       </c>
       <c r="B127" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C127" t="str">
-        <v>UI Validation Automated Verification Case #17</v>
+        <v>UI Validation Automated Verification Case #15</v>
       </c>
       <c r="D127" t="str">
-        <v>476ms</v>
+        <v>119ms</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>TC_WEB_UI_018</v>
+        <v>TC_WEB_UI_016</v>
       </c>
       <c r="B128" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C128" t="str">
-        <v>UI Validation Automated Verification Case #18</v>
+        <v>UI Validation Automated Verification Case #16</v>
       </c>
       <c r="D128" t="str">
-        <v>759ms</v>
+        <v>566ms</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>TC_WEB_UI_019</v>
+        <v>TC_WEB_UI_017</v>
       </c>
       <c r="B129" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C129" t="str">
-        <v>UI Validation Automated Verification Case #19</v>
+        <v>UI Validation Automated Verification Case #17</v>
       </c>
       <c r="D129" t="str">
-        <v>267ms</v>
+        <v>259ms</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>TC_WEB_UI_020</v>
+        <v>TC_WEB_UI_018</v>
       </c>
       <c r="B130" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C130" t="str">
-        <v>UI Validation Automated Verification Case #20</v>
+        <v>UI Validation Automated Verification Case #18</v>
       </c>
       <c r="D130" t="str">
-        <v>843ms</v>
+        <v>871ms</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>TC_WEB_UI_021</v>
+        <v>TC_WEB_UI_019</v>
       </c>
       <c r="B131" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C131" t="str">
-        <v>UI Validation Automated Verification Case #21</v>
+        <v>UI Validation Automated Verification Case #19</v>
       </c>
       <c r="D131" t="str">
-        <v>439ms</v>
+        <v>862ms</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>TC_WEB_UI_022</v>
+        <v>TC_WEB_UI_020</v>
       </c>
       <c r="B132" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C132" t="str">
-        <v>UI Validation Automated Verification Case #22</v>
+        <v>UI Validation Automated Verification Case #20</v>
       </c>
       <c r="D132" t="str">
-        <v>747ms</v>
+        <v>834ms</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>TC_WEB_UI_023</v>
+        <v>TC_WEB_UI_021</v>
       </c>
       <c r="B133" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C133" t="str">
-        <v>UI Validation Automated Verification Case #23</v>
+        <v>UI Validation Automated Verification Case #21</v>
       </c>
       <c r="D133" t="str">
-        <v>366ms</v>
+        <v>746ms</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>TC_WEB_UI_024</v>
+        <v>TC_WEB_UI_022</v>
       </c>
       <c r="B134" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C134" t="str">
-        <v>UI Validation Automated Verification Case #24</v>
+        <v>UI Validation Automated Verification Case #22</v>
       </c>
       <c r="D134" t="str">
-        <v>816ms</v>
+        <v>195ms</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>TC_WEB_UI_025</v>
+        <v>TC_WEB_UI_023</v>
       </c>
       <c r="B135" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C135" t="str">
-        <v>UI Validation Automated Verification Case #25</v>
+        <v>UI Validation Automated Verification Case #23</v>
       </c>
       <c r="D135" t="str">
-        <v>119ms</v>
+        <v>899ms</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>TC_WEB_UI_026</v>
+        <v>TC_WEB_UI_024</v>
       </c>
       <c r="B136" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C136" t="str">
-        <v>UI Validation Automated Verification Case #26</v>
+        <v>UI Validation Automated Verification Case #24</v>
       </c>
       <c r="D136" t="str">
-        <v>161ms</v>
+        <v>157ms</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>TC_WEB_UI_027</v>
+        <v>TC_WEB_UI_025</v>
       </c>
       <c r="B137" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C137" t="str">
-        <v>UI Validation Automated Verification Case #27</v>
+        <v>UI Validation Automated Verification Case #25</v>
       </c>
       <c r="D137" t="str">
-        <v>465ms</v>
+        <v>186ms</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>TC_WEB_UI_028</v>
+        <v>TC_WEB_UI_026</v>
       </c>
       <c r="B138" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C138" t="str">
-        <v>UI Validation Automated Verification Case #28</v>
+        <v>UI Validation Automated Verification Case #26</v>
       </c>
       <c r="D138" t="str">
-        <v>349ms</v>
+        <v>740ms</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>TC_WEB_UI_029</v>
+        <v>TC_WEB_UI_027</v>
       </c>
       <c r="B139" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C139" t="str">
-        <v>UI Validation Automated Verification Case #29</v>
+        <v>UI Validation Automated Verification Case #27</v>
       </c>
       <c r="D139" t="str">
-        <v>665ms</v>
+        <v>705ms</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>TC_WEB_UI_030</v>
+        <v>TC_WEB_UI_028</v>
       </c>
       <c r="B140" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C140" t="str">
-        <v>UI Validation Automated Verification Case #30</v>
+        <v>UI Validation Automated Verification Case #28</v>
       </c>
       <c r="D140" t="str">
-        <v>284ms</v>
+        <v>544ms</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>TC_WEB_UI_031</v>
+        <v>TC_WEB_UI_029</v>
       </c>
       <c r="B141" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C141" t="str">
-        <v>UI Validation Automated Verification Case #31</v>
+        <v>UI Validation Automated Verification Case #29</v>
       </c>
       <c r="D141" t="str">
-        <v>155ms</v>
+        <v>187ms</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>TC_WEB_UI_032</v>
+        <v>TC_WEB_UI_030</v>
       </c>
       <c r="B142" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C142" t="str">
-        <v>UI Validation Automated Verification Case #32</v>
+        <v>UI Validation Automated Verification Case #30</v>
       </c>
       <c r="D142" t="str">
-        <v>825ms</v>
+        <v>835ms</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>TC_WEB_UI_033</v>
+        <v>TC_WEB_UI_031</v>
       </c>
       <c r="B143" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C143" t="str">
-        <v>UI Validation Automated Verification Case #33</v>
+        <v>UI Validation Automated Verification Case #31</v>
       </c>
       <c r="D143" t="str">
-        <v>773ms</v>
+        <v>779ms</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>TC_WEB_UI_034</v>
+        <v>TC_WEB_UI_032</v>
       </c>
       <c r="B144" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C144" t="str">
-        <v>UI Validation Automated Verification Case #34</v>
+        <v>UI Validation Automated Verification Case #32</v>
       </c>
       <c r="D144" t="str">
-        <v>651ms</v>
+        <v>234ms</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>TC_WEB_UI_035</v>
+        <v>TC_WEB_UI_033</v>
       </c>
       <c r="B145" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C145" t="str">
-        <v>UI Validation Automated Verification Case #35</v>
+        <v>UI Validation Automated Verification Case #33</v>
       </c>
       <c r="D145" t="str">
-        <v>592ms</v>
+        <v>832ms</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>TC_WEB_UI_036</v>
+        <v>TC_WEB_UI_034</v>
       </c>
       <c r="B146" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C146" t="str">
-        <v>UI Validation Automated Verification Case #36</v>
+        <v>UI Validation Automated Verification Case #34</v>
       </c>
       <c r="D146" t="str">
-        <v>851ms</v>
+        <v>197ms</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>TC_WEB_UI_037</v>
+        <v>TC_WEB_UI_035</v>
       </c>
       <c r="B147" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C147" t="str">
-        <v>UI Validation Automated Verification Case #37</v>
+        <v>UI Validation Automated Verification Case #35</v>
       </c>
       <c r="D147" t="str">
-        <v>851ms</v>
+        <v>202ms</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>TC_WEB_UI_038</v>
+        <v>TC_WEB_UI_036</v>
       </c>
       <c r="B148" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C148" t="str">
-        <v>UI Validation Automated Verification Case #38</v>
+        <v>UI Validation Automated Verification Case #36</v>
       </c>
       <c r="D148" t="str">
-        <v>806ms</v>
+        <v>305ms</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>TC_WEB_UI_039</v>
+        <v>TC_WEB_UI_037</v>
       </c>
       <c r="B149" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C149" t="str">
-        <v>UI Validation Automated Verification Case #39</v>
+        <v>UI Validation Automated Verification Case #37</v>
       </c>
       <c r="D149" t="str">
-        <v>460ms</v>
+        <v>701ms</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>TC_WEB_UI_040</v>
+        <v>TC_WEB_UI_038</v>
       </c>
       <c r="B150" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C150" t="str">
-        <v>UI Validation Automated Verification Case #40</v>
+        <v>UI Validation Automated Verification Case #38</v>
       </c>
       <c r="D150" t="str">
-        <v>212ms</v>
+        <v>350ms</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>TC_WEB_UI_041</v>
+        <v>TC_WEB_UI_039</v>
       </c>
       <c r="B151" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C151" t="str">
-        <v>UI Validation Automated Verification Case #41</v>
+        <v>UI Validation Automated Verification Case #39</v>
       </c>
       <c r="D151" t="str">
-        <v>796ms</v>
+        <v>669ms</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>TC_WEB_UI_042</v>
+        <v>TC_WEB_UI_040</v>
       </c>
       <c r="B152" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C152" t="str">
-        <v>UI Validation Automated Verification Case #42</v>
+        <v>UI Validation Automated Verification Case #40</v>
       </c>
       <c r="D152" t="str">
-        <v>653ms</v>
+        <v>534ms</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>TC_WEB_UI_043</v>
+        <v>TC_WEB_UI_041</v>
       </c>
       <c r="B153" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C153" t="str">
-        <v>UI Validation Automated Verification Case #43</v>
+        <v>UI Validation Automated Verification Case #41</v>
       </c>
       <c r="D153" t="str">
-        <v>496ms</v>
+        <v>524ms</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>TC_WEB_UI_044</v>
+        <v>TC_WEB_UI_042</v>
       </c>
       <c r="B154" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C154" t="str">
-        <v>UI Validation Automated Verification Case #44</v>
+        <v>UI Validation Automated Verification Case #42</v>
       </c>
       <c r="D154" t="str">
-        <v>776ms</v>
+        <v>750ms</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>TC_WEB_UI_045</v>
+        <v>TC_WEB_UI_043</v>
       </c>
       <c r="B155" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C155" t="str">
-        <v>UI Validation Automated Verification Case #45</v>
+        <v>UI Validation Automated Verification Case #43</v>
       </c>
       <c r="D155" t="str">
-        <v>743ms</v>
+        <v>602ms</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>TC_WEB_UI_046</v>
+        <v>TC_WEB_UI_044</v>
       </c>
       <c r="B156" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C156" t="str">
-        <v>UI Validation Automated Verification Case #46</v>
+        <v>UI Validation Automated Verification Case #44</v>
       </c>
       <c r="D156" t="str">
-        <v>474ms</v>
+        <v>622ms</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>TC_WEB_UI_047</v>
+        <v>TC_WEB_UI_045</v>
       </c>
       <c r="B157" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C157" t="str">
-        <v>UI Validation Automated Verification Case #47</v>
+        <v>UI Validation Automated Verification Case #45</v>
       </c>
       <c r="D157" t="str">
-        <v>106ms</v>
+        <v>886ms</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>TC_WEB_UI_048</v>
+        <v>TC_WEB_UI_046</v>
       </c>
       <c r="B158" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C158" t="str">
-        <v>UI Validation Automated Verification Case #48</v>
+        <v>UI Validation Automated Verification Case #46</v>
       </c>
       <c r="D158" t="str">
-        <v>747ms</v>
+        <v>424ms</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>TC_WEB_UI_049</v>
+        <v>TC_WEB_UI_047</v>
       </c>
       <c r="B159" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C159" t="str">
-        <v>UI Validation Automated Verification Case #49</v>
+        <v>UI Validation Automated Verification Case #47</v>
       </c>
       <c r="D159" t="str">
-        <v>210ms</v>
+        <v>612ms</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>TC_WEB_UI_050</v>
+        <v>TC_WEB_UI_048</v>
       </c>
       <c r="B160" t="str">
         <v>UI Validation</v>
       </c>
       <c r="C160" t="str">
-        <v>UI Validation Automated Verification Case #50</v>
+        <v>UI Validation Automated Verification Case #48</v>
       </c>
       <c r="D160" t="str">
-        <v>292ms</v>
+        <v>214ms</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>TC_WEB_FORM_001</v>
+        <v>TC_WEB_UI_049</v>
       </c>
       <c r="B161" t="str">
-        <v>Forms</v>
+        <v>UI Validation</v>
       </c>
       <c r="C161" t="str">
-        <v>Forms Automated Verification Case #1</v>
+        <v>UI Validation Automated Verification Case #49</v>
       </c>
       <c r="D161" t="str">
-        <v>865ms</v>
+        <v>655ms</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>TC_WEB_FORM_002</v>
+        <v>TC_WEB_UI_050</v>
       </c>
       <c r="B162" t="str">
-        <v>Forms</v>
+        <v>UI Validation</v>
       </c>
       <c r="C162" t="str">
-        <v>Forms Automated Verification Case #2</v>
+        <v>UI Validation Automated Verification Case #50</v>
       </c>
       <c r="D162" t="str">
-        <v>260ms</v>
+        <v>421ms</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>TC_WEB_FORM_003</v>
+        <v>TC_WEB_FORM_001</v>
       </c>
       <c r="B163" t="str">
         <v>Forms</v>
       </c>
       <c r="C163" t="str">
-        <v>Forms Automated Verification Case #3</v>
+        <v>Forms Automated Verification Case #1</v>
       </c>
       <c r="D163" t="str">
-        <v>341ms</v>
+        <v>333ms</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>TC_WEB_FORM_004</v>
+        <v>TC_WEB_FORM_002</v>
       </c>
       <c r="B164" t="str">
         <v>Forms</v>
       </c>
       <c r="C164" t="str">
-        <v>Forms Automated Verification Case #4</v>
+        <v>Forms Automated Verification Case #2</v>
       </c>
       <c r="D164" t="str">
-        <v>714ms</v>
+        <v>423ms</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>TC_WEB_FORM_005</v>
+        <v>TC_WEB_FORM_003</v>
       </c>
       <c r="B165" t="str">
         <v>Forms</v>
       </c>
       <c r="C165" t="str">
-        <v>Forms Automated Verification Case #5</v>
+        <v>Forms Automated Verification Case #3</v>
       </c>
       <c r="D165" t="str">
-        <v>457ms</v>
+        <v>869ms</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>TC_WEB_FORM_006</v>
+        <v>TC_WEB_FORM_004</v>
       </c>
       <c r="B166" t="str">
         <v>Forms</v>
       </c>
       <c r="C166" t="str">
-        <v>Forms Automated Verification Case #6</v>
+        <v>Forms Automated Verification Case #4</v>
       </c>
       <c r="D166" t="str">
-        <v>571ms</v>
+        <v>335ms</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>TC_WEB_FORM_007</v>
+        <v>TC_WEB_FORM_005</v>
       </c>
       <c r="B167" t="str">
         <v>Forms</v>
       </c>
       <c r="C167" t="str">
-        <v>Forms Automated Verification Case #7</v>
+        <v>Forms Automated Verification Case #5</v>
       </c>
       <c r="D167" t="str">
-        <v>253ms</v>
+        <v>113ms</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>TC_WEB_FORM_008</v>
+        <v>TC_WEB_FORM_006</v>
       </c>
       <c r="B168" t="str">
         <v>Forms</v>
       </c>
       <c r="C168" t="str">
-        <v>Forms Automated Verification Case #8</v>
+        <v>Forms Automated Verification Case #6</v>
       </c>
       <c r="D168" t="str">
-        <v>353ms</v>
+        <v>671ms</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>TC_WEB_FORM_009</v>
+        <v>TC_WEB_FORM_007</v>
       </c>
       <c r="B169" t="str">
         <v>Forms</v>
       </c>
       <c r="C169" t="str">
-        <v>Forms Automated Verification Case #9</v>
+        <v>Forms Automated Verification Case #7</v>
       </c>
       <c r="D169" t="str">
-        <v>827ms</v>
+        <v>659ms</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>TC_WEB_FORM_010</v>
+        <v>TC_WEB_FORM_008</v>
       </c>
       <c r="B170" t="str">
         <v>Forms</v>
       </c>
       <c r="C170" t="str">
-        <v>Forms Automated Verification Case #10</v>
+        <v>Forms Automated Verification Case #8</v>
       </c>
       <c r="D170" t="str">
-        <v>680ms</v>
+        <v>426ms</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>TC_WEB_FORM_011</v>
+        <v>TC_WEB_FORM_009</v>
       </c>
       <c r="B171" t="str">
         <v>Forms</v>
       </c>
       <c r="C171" t="str">
-        <v>Forms Automated Verification Case #11</v>
+        <v>Forms Automated Verification Case #9</v>
       </c>
       <c r="D171" t="str">
-        <v>115ms</v>
+        <v>758ms</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>TC_WEB_FORM_012</v>
+        <v>TC_WEB_FORM_010</v>
       </c>
       <c r="B172" t="str">
         <v>Forms</v>
       </c>
       <c r="C172" t="str">
-        <v>Forms Automated Verification Case #12</v>
+        <v>Forms Automated Verification Case #10</v>
       </c>
       <c r="D172" t="str">
-        <v>149ms</v>
+        <v>876ms</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>TC_WEB_FORM_013</v>
+        <v>TC_WEB_FORM_011</v>
       </c>
       <c r="B173" t="str">
         <v>Forms</v>
       </c>
       <c r="C173" t="str">
-        <v>Forms Automated Verification Case #13</v>
+        <v>Forms Automated Verification Case #11</v>
       </c>
       <c r="D173" t="str">
-        <v>736ms</v>
+        <v>574ms</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>TC_WEB_FORM_014</v>
+        <v>TC_WEB_FORM_012</v>
       </c>
       <c r="B174" t="str">
         <v>Forms</v>
       </c>
       <c r="C174" t="str">
-        <v>Forms Automated Verification Case #14</v>
+        <v>Forms Automated Verification Case #12</v>
       </c>
       <c r="D174" t="str">
-        <v>608ms</v>
+        <v>600ms</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>TC_WEB_FORM_015</v>
+        <v>TC_WEB_FORM_013</v>
       </c>
       <c r="B175" t="str">
         <v>Forms</v>
       </c>
       <c r="C175" t="str">
-        <v>Forms Automated Verification Case #15</v>
+        <v>Forms Automated Verification Case #13</v>
       </c>
       <c r="D175" t="str">
-        <v>158ms</v>
+        <v>546ms</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>TC_WEB_FORM_016</v>
+        <v>TC_WEB_FORM_014</v>
       </c>
       <c r="B176" t="str">
         <v>Forms</v>
       </c>
       <c r="C176" t="str">
-        <v>Forms Automated Verification Case #16</v>
+        <v>Forms Automated Verification Case #14</v>
       </c>
       <c r="D176" t="str">
-        <v>181ms</v>
+        <v>660ms</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>TC_WEB_FORM_017</v>
+        <v>TC_WEB_FORM_015</v>
       </c>
       <c r="B177" t="str">
         <v>Forms</v>
       </c>
       <c r="C177" t="str">
-        <v>Forms Automated Verification Case #17</v>
+        <v>Forms Automated Verification Case #15</v>
       </c>
       <c r="D177" t="str">
-        <v>439ms</v>
+        <v>124ms</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>TC_WEB_FORM_018</v>
+        <v>TC_WEB_FORM_016</v>
       </c>
       <c r="B178" t="str">
         <v>Forms</v>
       </c>
       <c r="C178" t="str">
-        <v>Forms Automated Verification Case #18</v>
+        <v>Forms Automated Verification Case #16</v>
       </c>
       <c r="D178" t="str">
-        <v>571ms</v>
+        <v>811ms</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>TC_WEB_FORM_019</v>
+        <v>TC_WEB_FORM_017</v>
       </c>
       <c r="B179" t="str">
         <v>Forms</v>
       </c>
       <c r="C179" t="str">
-        <v>Forms Automated Verification Case #19</v>
+        <v>Forms Automated Verification Case #17</v>
       </c>
       <c r="D179" t="str">
-        <v>671ms</v>
+        <v>839ms</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>TC_WEB_FORM_020</v>
+        <v>TC_WEB_FORM_018</v>
       </c>
       <c r="B180" t="str">
         <v>Forms</v>
       </c>
       <c r="C180" t="str">
-        <v>Forms Automated Verification Case #20</v>
+        <v>Forms Automated Verification Case #18</v>
       </c>
       <c r="D180" t="str">
-        <v>120ms</v>
+        <v>647ms</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>TC_WEB_FORM_021</v>
+        <v>TC_WEB_FORM_019</v>
       </c>
       <c r="B181" t="str">
         <v>Forms</v>
       </c>
       <c r="C181" t="str">
-        <v>Forms Automated Verification Case #21</v>
+        <v>Forms Automated Verification Case #19</v>
       </c>
       <c r="D181" t="str">
-        <v>398ms</v>
+        <v>513ms</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>TC_WEB_FORM_022</v>
+        <v>TC_WEB_FORM_020</v>
       </c>
       <c r="B182" t="str">
         <v>Forms</v>
       </c>
       <c r="C182" t="str">
-        <v>Forms Automated Verification Case #22</v>
+        <v>Forms Automated Verification Case #20</v>
       </c>
       <c r="D182" t="str">
-        <v>681ms</v>
+        <v>261ms</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>TC_WEB_FORM_023</v>
+        <v>TC_WEB_FORM_021</v>
       </c>
       <c r="B183" t="str">
         <v>Forms</v>
       </c>
       <c r="C183" t="str">
-        <v>Forms Automated Verification Case #23</v>
+        <v>Forms Automated Verification Case #21</v>
       </c>
       <c r="D183" t="str">
-        <v>305ms</v>
+        <v>424ms</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>TC_WEB_FORM_024</v>
+        <v>TC_WEB_FORM_022</v>
       </c>
       <c r="B184" t="str">
         <v>Forms</v>
       </c>
       <c r="C184" t="str">
-        <v>Forms Automated Verification Case #24</v>
+        <v>Forms Automated Verification Case #22</v>
       </c>
       <c r="D184" t="str">
-        <v>198ms</v>
+        <v>322ms</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>TC_WEB_FORM_025</v>
+        <v>TC_WEB_FORM_023</v>
       </c>
       <c r="B185" t="str">
         <v>Forms</v>
       </c>
       <c r="C185" t="str">
-        <v>Forms Automated Verification Case #25</v>
+        <v>Forms Automated Verification Case #23</v>
       </c>
       <c r="D185" t="str">
-        <v>187ms</v>
+        <v>715ms</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>TC_WEB_FORM_026</v>
+        <v>TC_WEB_FORM_024</v>
       </c>
       <c r="B186" t="str">
         <v>Forms</v>
       </c>
       <c r="C186" t="str">
-        <v>Forms Automated Verification Case #26</v>
+        <v>Forms Automated Verification Case #24</v>
       </c>
       <c r="D186" t="str">
-        <v>703ms</v>
+        <v>213ms</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>TC_WEB_FORM_027</v>
+        <v>TC_WEB_FORM_025</v>
       </c>
       <c r="B187" t="str">
         <v>Forms</v>
       </c>
       <c r="C187" t="str">
-        <v>Forms Automated Verification Case #27</v>
+        <v>Forms Automated Verification Case #25</v>
       </c>
       <c r="D187" t="str">
-        <v>265ms</v>
+        <v>792ms</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>TC_WEB_FORM_028</v>
+        <v>TC_WEB_FORM_026</v>
       </c>
       <c r="B188" t="str">
         <v>Forms</v>
       </c>
       <c r="C188" t="str">
-        <v>Forms Automated Verification Case #28</v>
+        <v>Forms Automated Verification Case #26</v>
       </c>
       <c r="D188" t="str">
-        <v>145ms</v>
+        <v>190ms</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>TC_WEB_FORM_029</v>
+        <v>TC_WEB_FORM_027</v>
       </c>
       <c r="B189" t="str">
         <v>Forms</v>
       </c>
       <c r="C189" t="str">
-        <v>Forms Automated Verification Case #29</v>
+        <v>Forms Automated Verification Case #27</v>
       </c>
       <c r="D189" t="str">
-        <v>120ms</v>
+        <v>459ms</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>TC_WEB_FORM_030</v>
+        <v>TC_WEB_FORM_028</v>
       </c>
       <c r="B190" t="str">
         <v>Forms</v>
       </c>
       <c r="C190" t="str">
-        <v>Forms Automated Verification Case #30</v>
+        <v>Forms Automated Verification Case #28</v>
       </c>
       <c r="D190" t="str">
-        <v>203ms</v>
+        <v>734ms</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>TC_WEB_FORM_031</v>
+        <v>TC_WEB_FORM_029</v>
       </c>
       <c r="B191" t="str">
         <v>Forms</v>
       </c>
       <c r="C191" t="str">
-        <v>Forms Automated Verification Case #31</v>
+        <v>Forms Automated Verification Case #29</v>
       </c>
       <c r="D191" t="str">
-        <v>714ms</v>
+        <v>234ms</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>TC_WEB_FORM_032</v>
+        <v>TC_WEB_FORM_030</v>
       </c>
       <c r="B192" t="str">
         <v>Forms</v>
       </c>
       <c r="C192" t="str">
-        <v>Forms Automated Verification Case #32</v>
+        <v>Forms Automated Verification Case #30</v>
       </c>
       <c r="D192" t="str">
-        <v>392ms</v>
+        <v>776ms</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>TC_WEB_FORM_033</v>
+        <v>TC_WEB_FORM_031</v>
       </c>
       <c r="B193" t="str">
         <v>Forms</v>
       </c>
       <c r="C193" t="str">
-        <v>Forms Automated Verification Case #33</v>
+        <v>Forms Automated Verification Case #31</v>
       </c>
       <c r="D193" t="str">
-        <v>743ms</v>
+        <v>771ms</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>TC_WEB_FORM_034</v>
+        <v>TC_WEB_FORM_032</v>
       </c>
       <c r="B194" t="str">
         <v>Forms</v>
       </c>
       <c r="C194" t="str">
-        <v>Forms Automated Verification Case #34</v>
+        <v>Forms Automated Verification Case #32</v>
       </c>
       <c r="D194" t="str">
-        <v>185ms</v>
+        <v>801ms</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>TC_WEB_FORM_035</v>
+        <v>TC_WEB_FORM_033</v>
       </c>
       <c r="B195" t="str">
         <v>Forms</v>
       </c>
       <c r="C195" t="str">
-        <v>Forms Automated Verification Case #35</v>
+        <v>Forms Automated Verification Case #33</v>
       </c>
       <c r="D195" t="str">
-        <v>442ms</v>
+        <v>625ms</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>TC_WEB_FORM_036</v>
+        <v>TC_WEB_FORM_034</v>
       </c>
       <c r="B196" t="str">
         <v>Forms</v>
       </c>
       <c r="C196" t="str">
-        <v>Forms Automated Verification Case #36</v>
+        <v>Forms Automated Verification Case #34</v>
       </c>
       <c r="D196" t="str">
-        <v>799ms</v>
+        <v>458ms</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>TC_WEB_FORM_037</v>
+        <v>TC_WEB_FORM_035</v>
       </c>
       <c r="B197" t="str">
         <v>Forms</v>
       </c>
       <c r="C197" t="str">
-        <v>Forms Automated Verification Case #37</v>
+        <v>Forms Automated Verification Case #35</v>
       </c>
       <c r="D197" t="str">
-        <v>137ms</v>
+        <v>324ms</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>TC_WEB_FORM_038</v>
+        <v>TC_WEB_FORM_036</v>
       </c>
       <c r="B198" t="str">
         <v>Forms</v>
       </c>
       <c r="C198" t="str">
-        <v>Forms Automated Verification Case #38</v>
+        <v>Forms Automated Verification Case #36</v>
       </c>
       <c r="D198" t="str">
-        <v>251ms</v>
+        <v>742ms</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>TC_WEB_FORM_039</v>
+        <v>TC_WEB_FORM_037</v>
       </c>
       <c r="B199" t="str">
         <v>Forms</v>
       </c>
       <c r="C199" t="str">
-        <v>Forms Automated Verification Case #39</v>
+        <v>Forms Automated Verification Case #37</v>
       </c>
       <c r="D199" t="str">
-        <v>490ms</v>
+        <v>473ms</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>TC_WEB_FORM_040</v>
+        <v>TC_WEB_FORM_038</v>
       </c>
       <c r="B200" t="str">
         <v>Forms</v>
       </c>
       <c r="C200" t="str">
-        <v>Forms Automated Verification Case #40</v>
+        <v>Forms Automated Verification Case #38</v>
       </c>
       <c r="D200" t="str">
-        <v>468ms</v>
+        <v>166ms</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>TC_WEB_FORM_041</v>
+        <v>TC_WEB_FORM_039</v>
       </c>
       <c r="B201" t="str">
         <v>Forms</v>
       </c>
       <c r="C201" t="str">
-        <v>Forms Automated Verification Case #41</v>
+        <v>Forms Automated Verification Case #39</v>
       </c>
       <c r="D201" t="str">
-        <v>445ms</v>
+        <v>488ms</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>TC_WEB_FORM_042</v>
+        <v>TC_WEB_FORM_040</v>
       </c>
       <c r="B202" t="str">
         <v>Forms</v>
       </c>
       <c r="C202" t="str">
-        <v>Forms Automated Verification Case #42</v>
+        <v>Forms Automated Verification Case #40</v>
       </c>
       <c r="D202" t="str">
-        <v>170ms</v>
+        <v>208ms</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>TC_WEB_FORM_043</v>
+        <v>TC_WEB_FORM_041</v>
       </c>
       <c r="B203" t="str">
         <v>Forms</v>
       </c>
       <c r="C203" t="str">
-        <v>Forms Automated Verification Case #43</v>
+        <v>Forms Automated Verification Case #41</v>
       </c>
       <c r="D203" t="str">
-        <v>663ms</v>
+        <v>581ms</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>TC_WEB_FORM_044</v>
+        <v>TC_WEB_FORM_042</v>
       </c>
       <c r="B204" t="str">
         <v>Forms</v>
       </c>
       <c r="C204" t="str">
-        <v>Forms Automated Verification Case #44</v>
+        <v>Forms Automated Verification Case #42</v>
       </c>
       <c r="D204" t="str">
-        <v>823ms</v>
+        <v>746ms</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>TC_WEB_FORM_045</v>
+        <v>TC_WEB_FORM_043</v>
       </c>
       <c r="B205" t="str">
         <v>Forms</v>
       </c>
       <c r="C205" t="str">
-        <v>Forms Automated Verification Case #45</v>
+        <v>Forms Automated Verification Case #43</v>
       </c>
       <c r="D205" t="str">
-        <v>579ms</v>
+        <v>570ms</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>TC_WEB_FORM_046</v>
+        <v>TC_WEB_FORM_044</v>
       </c>
       <c r="B206" t="str">
         <v>Forms</v>
       </c>
       <c r="C206" t="str">
-        <v>Forms Automated Verification Case #46</v>
+        <v>Forms Automated Verification Case #44</v>
       </c>
       <c r="D206" t="str">
-        <v>841ms</v>
+        <v>278ms</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>TC_WEB_FORM_047</v>
+        <v>TC_WEB_FORM_045</v>
       </c>
       <c r="B207" t="str">
         <v>Forms</v>
       </c>
       <c r="C207" t="str">
-        <v>Forms Automated Verification Case #47</v>
+        <v>Forms Automated Verification Case #45</v>
       </c>
       <c r="D207" t="str">
-        <v>631ms</v>
+        <v>274ms</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>TC_WEB_FORM_048</v>
+        <v>TC_WEB_FORM_046</v>
       </c>
       <c r="B208" t="str">
         <v>Forms</v>
       </c>
       <c r="C208" t="str">
-        <v>Forms Automated Verification Case #48</v>
+        <v>Forms Automated Verification Case #46</v>
       </c>
       <c r="D208" t="str">
-        <v>262ms</v>
+        <v>477ms</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>TC_WEB_FORM_049</v>
+        <v>TC_WEB_FORM_047</v>
       </c>
       <c r="B209" t="str">
         <v>Forms</v>
       </c>
       <c r="C209" t="str">
-        <v>Forms Automated Verification Case #49</v>
+        <v>Forms Automated Verification Case #47</v>
       </c>
       <c r="D209" t="str">
-        <v>392ms</v>
+        <v>388ms</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>TC_WEB_FORM_050</v>
+        <v>TC_WEB_FORM_048</v>
       </c>
       <c r="B210" t="str">
         <v>Forms</v>
       </c>
       <c r="C210" t="str">
-        <v>Forms Automated Verification Case #50</v>
+        <v>Forms Automated Verification Case #48</v>
       </c>
       <c r="D210" t="str">
-        <v>720ms</v>
+        <v>430ms</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>TC_WEB_CRUD_002</v>
+        <v>TC_WEB_FORM_049</v>
       </c>
       <c r="B211" t="str">
-        <v>CRUD Operations</v>
+        <v>Forms</v>
       </c>
       <c r="C211" t="str">
-        <v>CRUD Operations Automated Verification Case #2</v>
+        <v>Forms Automated Verification Case #49</v>
       </c>
       <c r="D211" t="str">
-        <v>409ms</v>
+        <v>608ms</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>TC_WEB_CRUD_003</v>
+        <v>TC_WEB_FORM_050</v>
       </c>
       <c r="B212" t="str">
-        <v>CRUD Operations</v>
+        <v>Forms</v>
       </c>
       <c r="C212" t="str">
-        <v>CRUD Operations Automated Verification Case #3</v>
+        <v>Forms Automated Verification Case #50</v>
       </c>
       <c r="D212" t="str">
-        <v>346ms</v>
+        <v>386ms</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>TC_WEB_CRUD_004</v>
+        <v>TC_WEB_CRUD_002</v>
       </c>
       <c r="B213" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C213" t="str">
-        <v>CRUD Operations Automated Verification Case #4</v>
+        <v>CRUD Operations Automated Verification Case #2</v>
       </c>
       <c r="D213" t="str">
-        <v>476ms</v>
+        <v>262ms</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>TC_WEB_CRUD_005</v>
+        <v>TC_WEB_CRUD_003</v>
       </c>
       <c r="B214" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C214" t="str">
-        <v>CRUD Operations Automated Verification Case #5</v>
+        <v>CRUD Operations Automated Verification Case #3</v>
       </c>
       <c r="D214" t="str">
-        <v>720ms</v>
+        <v>393ms</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>TC_WEB_CRUD_006</v>
+        <v>TC_WEB_CRUD_004</v>
       </c>
       <c r="B215" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C215" t="str">
-        <v>CRUD Operations Automated Verification Case #6</v>
+        <v>CRUD Operations Automated Verification Case #4</v>
       </c>
       <c r="D215" t="str">
-        <v>766ms</v>
+        <v>483ms</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>TC_WEB_CRUD_007</v>
+        <v>TC_WEB_CRUD_005</v>
       </c>
       <c r="B216" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C216" t="str">
-        <v>CRUD Operations Automated Verification Case #7</v>
+        <v>CRUD Operations Automated Verification Case #5</v>
       </c>
       <c r="D216" t="str">
-        <v>832ms</v>
+        <v>819ms</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>TC_WEB_CRUD_008</v>
+        <v>TC_WEB_CRUD_006</v>
       </c>
       <c r="B217" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C217" t="str">
-        <v>CRUD Operations Automated Verification Case #8</v>
+        <v>CRUD Operations Automated Verification Case #6</v>
       </c>
       <c r="D217" t="str">
-        <v>421ms</v>
+        <v>872ms</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>TC_WEB_CRUD_009</v>
+        <v>TC_WEB_CRUD_007</v>
       </c>
       <c r="B218" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C218" t="str">
-        <v>CRUD Operations Automated Verification Case #9</v>
+        <v>CRUD Operations Automated Verification Case #7</v>
       </c>
       <c r="D218" t="str">
-        <v>198ms</v>
+        <v>751ms</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>TC_WEB_CRUD_010</v>
+        <v>TC_WEB_CRUD_008</v>
       </c>
       <c r="B219" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C219" t="str">
-        <v>CRUD Operations Automated Verification Case #10</v>
+        <v>CRUD Operations Automated Verification Case #8</v>
       </c>
       <c r="D219" t="str">
-        <v>616ms</v>
+        <v>686ms</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>TC_WEB_CRUD_011</v>
+        <v>TC_WEB_CRUD_009</v>
       </c>
       <c r="B220" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C220" t="str">
-        <v>CRUD Operations Automated Verification Case #11</v>
+        <v>CRUD Operations Automated Verification Case #9</v>
       </c>
       <c r="D220" t="str">
-        <v>470ms</v>
+        <v>743ms</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>TC_WEB_CRUD_012</v>
+        <v>TC_WEB_CRUD_010</v>
       </c>
       <c r="B221" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C221" t="str">
-        <v>CRUD Operations Automated Verification Case #12</v>
+        <v>CRUD Operations Automated Verification Case #10</v>
       </c>
       <c r="D221" t="str">
-        <v>832ms</v>
+        <v>155ms</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>TC_WEB_CRUD_013</v>
+        <v>TC_WEB_CRUD_011</v>
       </c>
       <c r="B222" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C222" t="str">
-        <v>CRUD Operations Automated Verification Case #13</v>
+        <v>CRUD Operations Automated Verification Case #11</v>
       </c>
       <c r="D222" t="str">
-        <v>777ms</v>
+        <v>438ms</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>TC_WEB_CRUD_014</v>
+        <v>TC_WEB_CRUD_012</v>
       </c>
       <c r="B223" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C223" t="str">
-        <v>CRUD Operations Automated Verification Case #14</v>
+        <v>CRUD Operations Automated Verification Case #12</v>
       </c>
       <c r="D223" t="str">
-        <v>641ms</v>
+        <v>300ms</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>TC_WEB_CRUD_015</v>
+        <v>TC_WEB_CRUD_013</v>
       </c>
       <c r="B224" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C224" t="str">
-        <v>CRUD Operations Automated Verification Case #15</v>
+        <v>CRUD Operations Automated Verification Case #13</v>
       </c>
       <c r="D224" t="str">
-        <v>382ms</v>
+        <v>882ms</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>TC_WEB_CRUD_016</v>
+        <v>TC_WEB_CRUD_014</v>
       </c>
       <c r="B225" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C225" t="str">
-        <v>CRUD Operations Automated Verification Case #16</v>
+        <v>CRUD Operations Automated Verification Case #14</v>
       </c>
       <c r="D225" t="str">
-        <v>377ms</v>
+        <v>412ms</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>TC_WEB_CRUD_017</v>
+        <v>TC_WEB_CRUD_015</v>
       </c>
       <c r="B226" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C226" t="str">
-        <v>CRUD Operations Automated Verification Case #17</v>
+        <v>CRUD Operations Automated Verification Case #15</v>
       </c>
       <c r="D226" t="str">
-        <v>271ms</v>
+        <v>557ms</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>TC_WEB_CRUD_018</v>
+        <v>TC_WEB_CRUD_016</v>
       </c>
       <c r="B227" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C227" t="str">
-        <v>CRUD Operations Automated Verification Case #18</v>
+        <v>CRUD Operations Automated Verification Case #16</v>
       </c>
       <c r="D227" t="str">
-        <v>494ms</v>
+        <v>472ms</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>TC_WEB_CRUD_019</v>
+        <v>TC_WEB_CRUD_017</v>
       </c>
       <c r="B228" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C228" t="str">
-        <v>CRUD Operations Automated Verification Case #19</v>
+        <v>CRUD Operations Automated Verification Case #17</v>
       </c>
       <c r="D228" t="str">
-        <v>407ms</v>
+        <v>245ms</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>TC_WEB_CRUD_020</v>
+        <v>TC_WEB_CRUD_018</v>
       </c>
       <c r="B229" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C229" t="str">
-        <v>CRUD Operations Automated Verification Case #20</v>
+        <v>CRUD Operations Automated Verification Case #18</v>
       </c>
       <c r="D229" t="str">
-        <v>409ms</v>
+        <v>498ms</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>TC_WEB_CRUD_021</v>
+        <v>TC_WEB_CRUD_019</v>
       </c>
       <c r="B230" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C230" t="str">
-        <v>CRUD Operations Automated Verification Case #21</v>
+        <v>CRUD Operations Automated Verification Case #19</v>
       </c>
       <c r="D230" t="str">
-        <v>760ms</v>
+        <v>734ms</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>TC_WEB_CRUD_022</v>
+        <v>TC_WEB_CRUD_020</v>
       </c>
       <c r="B231" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C231" t="str">
-        <v>CRUD Operations Automated Verification Case #22</v>
+        <v>CRUD Operations Automated Verification Case #20</v>
       </c>
       <c r="D231" t="str">
-        <v>335ms</v>
+        <v>251ms</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>TC_WEB_CRUD_023</v>
+        <v>TC_WEB_CRUD_021</v>
       </c>
       <c r="B232" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C232" t="str">
-        <v>CRUD Operations Automated Verification Case #23</v>
+        <v>CRUD Operations Automated Verification Case #21</v>
       </c>
       <c r="D232" t="str">
-        <v>231ms</v>
+        <v>254ms</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>TC_WEB_CRUD_024</v>
+        <v>TC_WEB_CRUD_022</v>
       </c>
       <c r="B233" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C233" t="str">
-        <v>CRUD Operations Automated Verification Case #24</v>
+        <v>CRUD Operations Automated Verification Case #22</v>
       </c>
       <c r="D233" t="str">
-        <v>666ms</v>
+        <v>733ms</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>TC_WEB_CRUD_025</v>
+        <v>TC_WEB_CRUD_023</v>
       </c>
       <c r="B234" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C234" t="str">
-        <v>CRUD Operations Automated Verification Case #25</v>
+        <v>CRUD Operations Automated Verification Case #23</v>
       </c>
       <c r="D234" t="str">
-        <v>898ms</v>
+        <v>413ms</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>TC_WEB_CRUD_026</v>
+        <v>TC_WEB_CRUD_024</v>
       </c>
       <c r="B235" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C235" t="str">
-        <v>CRUD Operations Automated Verification Case #26</v>
+        <v>CRUD Operations Automated Verification Case #24</v>
       </c>
       <c r="D235" t="str">
-        <v>189ms</v>
+        <v>858ms</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>TC_WEB_CRUD_027</v>
+        <v>TC_WEB_CRUD_025</v>
       </c>
       <c r="B236" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C236" t="str">
-        <v>CRUD Operations Automated Verification Case #27</v>
+        <v>CRUD Operations Automated Verification Case #25</v>
       </c>
       <c r="D236" t="str">
-        <v>285ms</v>
+        <v>828ms</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>TC_WEB_CRUD_028</v>
+        <v>TC_WEB_CRUD_026</v>
       </c>
       <c r="B237" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C237" t="str">
-        <v>CRUD Operations Automated Verification Case #28</v>
+        <v>CRUD Operations Automated Verification Case #26</v>
       </c>
       <c r="D237" t="str">
-        <v>330ms</v>
+        <v>193ms</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>TC_WEB_CRUD_029</v>
+        <v>TC_WEB_CRUD_027</v>
       </c>
       <c r="B238" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C238" t="str">
-        <v>CRUD Operations Automated Verification Case #29</v>
+        <v>CRUD Operations Automated Verification Case #27</v>
       </c>
       <c r="D238" t="str">
-        <v>301ms</v>
+        <v>259ms</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>TC_WEB_CRUD_030</v>
+        <v>TC_WEB_CRUD_028</v>
       </c>
       <c r="B239" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C239" t="str">
-        <v>CRUD Operations Automated Verification Case #30</v>
+        <v>CRUD Operations Automated Verification Case #28</v>
       </c>
       <c r="D239" t="str">
-        <v>146ms</v>
+        <v>364ms</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>TC_WEB_CRUD_031</v>
+        <v>TC_WEB_CRUD_029</v>
       </c>
       <c r="B240" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C240" t="str">
-        <v>CRUD Operations Automated Verification Case #31</v>
+        <v>CRUD Operations Automated Verification Case #29</v>
       </c>
       <c r="D240" t="str">
-        <v>220ms</v>
+        <v>892ms</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>TC_WEB_CRUD_032</v>
+        <v>TC_WEB_CRUD_030</v>
       </c>
       <c r="B241" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C241" t="str">
-        <v>CRUD Operations Automated Verification Case #32</v>
+        <v>CRUD Operations Automated Verification Case #30</v>
       </c>
       <c r="D241" t="str">
-        <v>388ms</v>
+        <v>758ms</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>TC_WEB_CRUD_033</v>
+        <v>TC_WEB_CRUD_031</v>
       </c>
       <c r="B242" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C242" t="str">
-        <v>CRUD Operations Automated Verification Case #33</v>
+        <v>CRUD Operations Automated Verification Case #31</v>
       </c>
       <c r="D242" t="str">
-        <v>180ms</v>
+        <v>842ms</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>TC_WEB_CRUD_034</v>
+        <v>TC_WEB_CRUD_032</v>
       </c>
       <c r="B243" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C243" t="str">
-        <v>CRUD Operations Automated Verification Case #34</v>
+        <v>CRUD Operations Automated Verification Case #32</v>
       </c>
       <c r="D243" t="str">
-        <v>655ms</v>
+        <v>660ms</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>TC_WEB_CRUD_035</v>
+        <v>TC_WEB_CRUD_033</v>
       </c>
       <c r="B244" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C244" t="str">
-        <v>CRUD Operations Automated Verification Case #35</v>
+        <v>CRUD Operations Automated Verification Case #33</v>
       </c>
       <c r="D244" t="str">
-        <v>812ms</v>
+        <v>395ms</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>TC_WEB_CRUD_036</v>
+        <v>TC_WEB_CRUD_034</v>
       </c>
       <c r="B245" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C245" t="str">
-        <v>CRUD Operations Automated Verification Case #36</v>
+        <v>CRUD Operations Automated Verification Case #34</v>
       </c>
       <c r="D245" t="str">
-        <v>385ms</v>
+        <v>205ms</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>TC_WEB_CRUD_037</v>
+        <v>TC_WEB_CRUD_035</v>
       </c>
       <c r="B246" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C246" t="str">
-        <v>CRUD Operations Automated Verification Case #37</v>
+        <v>CRUD Operations Automated Verification Case #35</v>
       </c>
       <c r="D246" t="str">
-        <v>589ms</v>
+        <v>278ms</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>TC_WEB_CRUD_038</v>
+        <v>TC_WEB_CRUD_036</v>
       </c>
       <c r="B247" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C247" t="str">
-        <v>CRUD Operations Automated Verification Case #38</v>
+        <v>CRUD Operations Automated Verification Case #36</v>
       </c>
       <c r="D247" t="str">
-        <v>209ms</v>
+        <v>773ms</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>TC_WEB_CRUD_039</v>
+        <v>TC_WEB_CRUD_037</v>
       </c>
       <c r="B248" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C248" t="str">
-        <v>CRUD Operations Automated Verification Case #39</v>
+        <v>CRUD Operations Automated Verification Case #37</v>
       </c>
       <c r="D248" t="str">
-        <v>881ms</v>
+        <v>283ms</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>TC_WEB_CRUD_040</v>
+        <v>TC_WEB_CRUD_038</v>
       </c>
       <c r="B249" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C249" t="str">
-        <v>CRUD Operations Automated Verification Case #40</v>
+        <v>CRUD Operations Automated Verification Case #38</v>
       </c>
       <c r="D249" t="str">
-        <v>450ms</v>
+        <v>419ms</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>TC_WEB_CRUD_041</v>
+        <v>TC_WEB_CRUD_039</v>
       </c>
       <c r="B250" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C250" t="str">
-        <v>CRUD Operations Automated Verification Case #41</v>
+        <v>CRUD Operations Automated Verification Case #39</v>
       </c>
       <c r="D250" t="str">
-        <v>422ms</v>
+        <v>644ms</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>TC_WEB_CRUD_042</v>
+        <v>TC_WEB_CRUD_040</v>
       </c>
       <c r="B251" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C251" t="str">
-        <v>CRUD Operations Automated Verification Case #42</v>
+        <v>CRUD Operations Automated Verification Case #40</v>
       </c>
       <c r="D251" t="str">
-        <v>700ms</v>
+        <v>149ms</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>TC_WEB_CRUD_043</v>
+        <v>TC_WEB_CRUD_041</v>
       </c>
       <c r="B252" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C252" t="str">
-        <v>CRUD Operations Automated Verification Case #43</v>
+        <v>CRUD Operations Automated Verification Case #41</v>
       </c>
       <c r="D252" t="str">
-        <v>491ms</v>
+        <v>307ms</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>TC_WEB_CRUD_044</v>
+        <v>TC_WEB_CRUD_042</v>
       </c>
       <c r="B253" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C253" t="str">
-        <v>CRUD Operations Automated Verification Case #44</v>
+        <v>CRUD Operations Automated Verification Case #42</v>
       </c>
       <c r="D253" t="str">
-        <v>403ms</v>
+        <v>770ms</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>TC_WEB_CRUD_045</v>
+        <v>TC_WEB_CRUD_043</v>
       </c>
       <c r="B254" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C254" t="str">
-        <v>CRUD Operations Automated Verification Case #45</v>
+        <v>CRUD Operations Automated Verification Case #43</v>
       </c>
       <c r="D254" t="str">
-        <v>587ms</v>
+        <v>300ms</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>TC_WEB_CRUD_046</v>
+        <v>TC_WEB_CRUD_044</v>
       </c>
       <c r="B255" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C255" t="str">
-        <v>CRUD Operations Automated Verification Case #46</v>
+        <v>CRUD Operations Automated Verification Case #44</v>
       </c>
       <c r="D255" t="str">
-        <v>681ms</v>
+        <v>816ms</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>TC_WEB_CRUD_047</v>
+        <v>TC_WEB_CRUD_045</v>
       </c>
       <c r="B256" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C256" t="str">
-        <v>CRUD Operations Automated Verification Case #47</v>
+        <v>CRUD Operations Automated Verification Case #45</v>
       </c>
       <c r="D256" t="str">
-        <v>838ms</v>
+        <v>707ms</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>TC_WEB_CRUD_048</v>
+        <v>TC_WEB_CRUD_046</v>
       </c>
       <c r="B257" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C257" t="str">
-        <v>CRUD Operations Automated Verification Case #48</v>
+        <v>CRUD Operations Automated Verification Case #46</v>
       </c>
       <c r="D257" t="str">
-        <v>637ms</v>
+        <v>312ms</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>TC_WEB_CRUD_049</v>
+        <v>TC_WEB_CRUD_047</v>
       </c>
       <c r="B258" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C258" t="str">
-        <v>CRUD Operations Automated Verification Case #49</v>
+        <v>CRUD Operations Automated Verification Case #47</v>
       </c>
       <c r="D258" t="str">
-        <v>235ms</v>
+        <v>216ms</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>TC_WEB_CRUD_050</v>
+        <v>TC_WEB_CRUD_048</v>
       </c>
       <c r="B259" t="str">
         <v>CRUD Operations</v>
       </c>
       <c r="C259" t="str">
-        <v>CRUD Operations Automated Verification Case #50</v>
+        <v>CRUD Operations Automated Verification Case #48</v>
       </c>
       <c r="D259" t="str">
-        <v>180ms</v>
+        <v>166ms</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>TC_WEB_VAL_001</v>
+        <v>TC_WEB_CRUD_049</v>
       </c>
       <c r="B260" t="str">
-        <v>Input Validation</v>
+        <v>CRUD Operations</v>
       </c>
       <c r="C260" t="str">
-        <v>Input Validation Automated Verification Case #1</v>
+        <v>CRUD Operations Automated Verification Case #49</v>
       </c>
       <c r="D260" t="str">
-        <v>440ms</v>
+        <v>215ms</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>TC_WEB_VAL_002</v>
+        <v>TC_WEB_CRUD_050</v>
       </c>
       <c r="B261" t="str">
-        <v>Input Validation</v>
+        <v>CRUD Operations</v>
       </c>
       <c r="C261" t="str">
-        <v>Input Validation Automated Verification Case #2</v>
+        <v>CRUD Operations Automated Verification Case #50</v>
       </c>
       <c r="D261" t="str">
-        <v>649ms</v>
+        <v>868ms</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>TC_WEB_VAL_003</v>
+        <v>TC_WEB_VAL_001</v>
       </c>
       <c r="B262" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C262" t="str">
-        <v>Input Validation Automated Verification Case #3</v>
+        <v>Input Validation Automated Verification Case #1</v>
       </c>
       <c r="D262" t="str">
-        <v>842ms</v>
+        <v>316ms</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>TC_WEB_VAL_004</v>
+        <v>TC_WEB_VAL_002</v>
       </c>
       <c r="B263" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C263" t="str">
-        <v>Input Validation Automated Verification Case #4</v>
+        <v>Input Validation Automated Verification Case #2</v>
       </c>
       <c r="D263" t="str">
-        <v>835ms</v>
+        <v>130ms</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>TC_WEB_VAL_005</v>
+        <v>TC_WEB_VAL_003</v>
       </c>
       <c r="B264" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C264" t="str">
-        <v>Input Validation Automated Verification Case #5</v>
+        <v>Input Validation Automated Verification Case #3</v>
       </c>
       <c r="D264" t="str">
-        <v>643ms</v>
+        <v>673ms</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>TC_WEB_VAL_006</v>
+        <v>TC_WEB_VAL_004</v>
       </c>
       <c r="B265" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C265" t="str">
-        <v>Input Validation Automated Verification Case #6</v>
+        <v>Input Validation Automated Verification Case #4</v>
       </c>
       <c r="D265" t="str">
-        <v>403ms</v>
+        <v>289ms</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>TC_WEB_VAL_007</v>
+        <v>TC_WEB_VAL_005</v>
       </c>
       <c r="B266" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C266" t="str">
-        <v>Input Validation Automated Verification Case #7</v>
+        <v>Input Validation Automated Verification Case #5</v>
       </c>
       <c r="D266" t="str">
-        <v>347ms</v>
+        <v>151ms</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>TC_WEB_VAL_008</v>
+        <v>TC_WEB_VAL_006</v>
       </c>
       <c r="B267" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C267" t="str">
-        <v>Input Validation Automated Verification Case #8</v>
+        <v>Input Validation Automated Verification Case #6</v>
       </c>
       <c r="D267" t="str">
-        <v>270ms</v>
+        <v>289ms</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>TC_WEB_VAL_009</v>
+        <v>TC_WEB_VAL_007</v>
       </c>
       <c r="B268" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C268" t="str">
-        <v>Input Validation Automated Verification Case #9</v>
+        <v>Input Validation Automated Verification Case #7</v>
       </c>
       <c r="D268" t="str">
-        <v>435ms</v>
+        <v>324ms</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>TC_WEB_VAL_010</v>
+        <v>TC_WEB_VAL_008</v>
       </c>
       <c r="B269" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C269" t="str">
-        <v>Input Validation Automated Verification Case #10</v>
+        <v>Input Validation Automated Verification Case #8</v>
       </c>
       <c r="D269" t="str">
-        <v>201ms</v>
+        <v>645ms</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>TC_WEB_VAL_011</v>
+        <v>TC_WEB_VAL_009</v>
       </c>
       <c r="B270" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C270" t="str">
-        <v>Input Validation Automated Verification Case #11</v>
+        <v>Input Validation Automated Verification Case #9</v>
       </c>
       <c r="D270" t="str">
-        <v>652ms</v>
+        <v>641ms</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>TC_WEB_VAL_012</v>
+        <v>TC_WEB_VAL_010</v>
       </c>
       <c r="B271" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C271" t="str">
-        <v>Input Validation Automated Verification Case #12</v>
+        <v>Input Validation Automated Verification Case #10</v>
       </c>
       <c r="D271" t="str">
-        <v>401ms</v>
+        <v>294ms</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>TC_WEB_VAL_013</v>
+        <v>TC_WEB_VAL_011</v>
       </c>
       <c r="B272" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C272" t="str">
-        <v>Input Validation Automated Verification Case #13</v>
+        <v>Input Validation Automated Verification Case #11</v>
       </c>
       <c r="D272" t="str">
-        <v>527ms</v>
+        <v>266ms</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>TC_WEB_VAL_014</v>
+        <v>TC_WEB_VAL_012</v>
       </c>
       <c r="B273" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C273" t="str">
-        <v>Input Validation Automated Verification Case #14</v>
+        <v>Input Validation Automated Verification Case #12</v>
       </c>
       <c r="D273" t="str">
-        <v>145ms</v>
+        <v>267ms</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>TC_WEB_VAL_015</v>
+        <v>TC_WEB_VAL_013</v>
       </c>
       <c r="B274" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C274" t="str">
-        <v>Input Validation Automated Verification Case #15</v>
+        <v>Input Validation Automated Verification Case #13</v>
       </c>
       <c r="D274" t="str">
-        <v>250ms</v>
+        <v>105ms</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>TC_WEB_VAL_016</v>
+        <v>TC_WEB_VAL_014</v>
       </c>
       <c r="B275" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C275" t="str">
-        <v>Input Validation Automated Verification Case #16</v>
+        <v>Input Validation Automated Verification Case #14</v>
       </c>
       <c r="D275" t="str">
-        <v>491ms</v>
+        <v>591ms</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>TC_WEB_VAL_017</v>
+        <v>TC_WEB_VAL_015</v>
       </c>
       <c r="B276" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C276" t="str">
-        <v>Input Validation Automated Verification Case #17</v>
+        <v>Input Validation Automated Verification Case #15</v>
       </c>
       <c r="D276" t="str">
-        <v>503ms</v>
+        <v>468ms</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>TC_WEB_VAL_018</v>
+        <v>TC_WEB_VAL_016</v>
       </c>
       <c r="B277" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C277" t="str">
-        <v>Input Validation Automated Verification Case #18</v>
+        <v>Input Validation Automated Verification Case #16</v>
       </c>
       <c r="D277" t="str">
-        <v>322ms</v>
+        <v>270ms</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>TC_WEB_VAL_019</v>
+        <v>TC_WEB_VAL_017</v>
       </c>
       <c r="B278" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C278" t="str">
-        <v>Input Validation Automated Verification Case #19</v>
+        <v>Input Validation Automated Verification Case #17</v>
       </c>
       <c r="D278" t="str">
-        <v>801ms</v>
+        <v>347ms</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>TC_WEB_VAL_020</v>
+        <v>TC_WEB_VAL_018</v>
       </c>
       <c r="B279" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C279" t="str">
-        <v>Input Validation Automated Verification Case #20</v>
+        <v>Input Validation Automated Verification Case #18</v>
       </c>
       <c r="D279" t="str">
-        <v>507ms</v>
+        <v>785ms</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>TC_WEB_VAL_021</v>
+        <v>TC_WEB_VAL_019</v>
       </c>
       <c r="B280" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C280" t="str">
-        <v>Input Validation Automated Verification Case #21</v>
+        <v>Input Validation Automated Verification Case #19</v>
       </c>
       <c r="D280" t="str">
-        <v>257ms</v>
+        <v>783ms</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>TC_WEB_VAL_022</v>
+        <v>TC_WEB_VAL_020</v>
       </c>
       <c r="B281" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C281" t="str">
-        <v>Input Validation Automated Verification Case #22</v>
+        <v>Input Validation Automated Verification Case #20</v>
       </c>
       <c r="D281" t="str">
-        <v>322ms</v>
+        <v>779ms</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>TC_WEB_VAL_023</v>
+        <v>TC_WEB_VAL_021</v>
       </c>
       <c r="B282" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C282" t="str">
-        <v>Input Validation Automated Verification Case #23</v>
+        <v>Input Validation Automated Verification Case #21</v>
       </c>
       <c r="D282" t="str">
-        <v>789ms</v>
+        <v>770ms</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>TC_WEB_VAL_024</v>
+        <v>TC_WEB_VAL_022</v>
       </c>
       <c r="B283" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C283" t="str">
-        <v>Input Validation Automated Verification Case #24</v>
+        <v>Input Validation Automated Verification Case #22</v>
       </c>
       <c r="D283" t="str">
-        <v>364ms</v>
+        <v>270ms</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>TC_WEB_VAL_025</v>
+        <v>TC_WEB_VAL_023</v>
       </c>
       <c r="B284" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C284" t="str">
-        <v>Input Validation Automated Verification Case #25</v>
+        <v>Input Validation Automated Verification Case #23</v>
       </c>
       <c r="D284" t="str">
-        <v>589ms</v>
+        <v>531ms</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>TC_WEB_VAL_026</v>
+        <v>TC_WEB_VAL_024</v>
       </c>
       <c r="B285" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C285" t="str">
-        <v>Input Validation Automated Verification Case #26</v>
+        <v>Input Validation Automated Verification Case #24</v>
       </c>
       <c r="D285" t="str">
-        <v>719ms</v>
+        <v>619ms</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>TC_WEB_VAL_027</v>
+        <v>TC_WEB_VAL_025</v>
       </c>
       <c r="B286" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C286" t="str">
-        <v>Input Validation Automated Verification Case #27</v>
+        <v>Input Validation Automated Verification Case #25</v>
       </c>
       <c r="D286" t="str">
-        <v>692ms</v>
+        <v>857ms</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>TC_WEB_VAL_028</v>
+        <v>TC_WEB_VAL_026</v>
       </c>
       <c r="B287" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C287" t="str">
-        <v>Input Validation Automated Verification Case #28</v>
+        <v>Input Validation Automated Verification Case #26</v>
       </c>
       <c r="D287" t="str">
-        <v>265ms</v>
+        <v>166ms</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>TC_WEB_VAL_029</v>
+        <v>TC_WEB_VAL_027</v>
       </c>
       <c r="B288" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C288" t="str">
-        <v>Input Validation Automated Verification Case #29</v>
+        <v>Input Validation Automated Verification Case #27</v>
       </c>
       <c r="D288" t="str">
-        <v>478ms</v>
+        <v>330ms</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>TC_WEB_VAL_030</v>
+        <v>TC_WEB_VAL_028</v>
       </c>
       <c r="B289" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C289" t="str">
-        <v>Input Validation Automated Verification Case #30</v>
+        <v>Input Validation Automated Verification Case #28</v>
       </c>
       <c r="D289" t="str">
-        <v>619ms</v>
+        <v>404ms</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>TC_WEB_VAL_031</v>
+        <v>TC_WEB_VAL_029</v>
       </c>
       <c r="B290" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C290" t="str">
-        <v>Input Validation Automated Verification Case #31</v>
+        <v>Input Validation Automated Verification Case #29</v>
       </c>
       <c r="D290" t="str">
-        <v>286ms</v>
+        <v>290ms</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>TC_WEB_VAL_032</v>
+        <v>TC_WEB_VAL_030</v>
       </c>
       <c r="B291" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C291" t="str">
-        <v>Input Validation Automated Verification Case #32</v>
+        <v>Input Validation Automated Verification Case #30</v>
       </c>
       <c r="D291" t="str">
-        <v>405ms</v>
+        <v>420ms</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>TC_WEB_VAL_033</v>
+        <v>TC_WEB_VAL_031</v>
       </c>
       <c r="B292" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C292" t="str">
-        <v>Input Validation Automated Verification Case #33</v>
+        <v>Input Validation Automated Verification Case #31</v>
       </c>
       <c r="D292" t="str">
-        <v>792ms</v>
+        <v>771ms</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>TC_WEB_VAL_034</v>
+        <v>TC_WEB_VAL_032</v>
       </c>
       <c r="B293" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C293" t="str">
-        <v>Input Validation Automated Verification Case #34</v>
+        <v>Input Validation Automated Verification Case #32</v>
       </c>
       <c r="D293" t="str">
-        <v>608ms</v>
+        <v>642ms</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>TC_WEB_VAL_035</v>
+        <v>TC_WEB_VAL_033</v>
       </c>
       <c r="B294" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C294" t="str">
-        <v>Input Validation Automated Verification Case #35</v>
+        <v>Input Validation Automated Verification Case #33</v>
       </c>
       <c r="D294" t="str">
-        <v>670ms</v>
+        <v>788ms</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>TC_WEB_VAL_036</v>
+        <v>TC_WEB_VAL_034</v>
       </c>
       <c r="B295" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C295" t="str">
-        <v>Input Validation Automated Verification Case #36</v>
+        <v>Input Validation Automated Verification Case #34</v>
       </c>
       <c r="D295" t="str">
-        <v>845ms</v>
+        <v>830ms</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>TC_WEB_VAL_037</v>
+        <v>TC_WEB_VAL_035</v>
       </c>
       <c r="B296" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C296" t="str">
-        <v>Input Validation Automated Verification Case #37</v>
+        <v>Input Validation Automated Verification Case #35</v>
       </c>
       <c r="D296" t="str">
-        <v>752ms</v>
+        <v>348ms</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>TC_WEB_VAL_038</v>
+        <v>TC_WEB_VAL_036</v>
       </c>
       <c r="B297" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C297" t="str">
-        <v>Input Validation Automated Verification Case #38</v>
+        <v>Input Validation Automated Verification Case #36</v>
       </c>
       <c r="D297" t="str">
-        <v>234ms</v>
+        <v>868ms</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>TC_WEB_VAL_039</v>
+        <v>TC_WEB_VAL_037</v>
       </c>
       <c r="B298" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C298" t="str">
-        <v>Input Validation Automated Verification Case #39</v>
+        <v>Input Validation Automated Verification Case #37</v>
       </c>
       <c r="D298" t="str">
-        <v>508ms</v>
+        <v>577ms</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>TC_WEB_VAL_040</v>
+        <v>TC_WEB_VAL_038</v>
       </c>
       <c r="B299" t="str">
         <v>Input Validation</v>
       </c>
       <c r="C299" t="str">
-        <v>Input Validation Automated Verification Case #40</v>
+        <v>Input Validation Automated Verification Case #38</v>
       </c>
       <c r="D299" t="str">
-        <v>245ms</v>
+        <v>417ms</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>TC_WEB_ERR_001</v>
+        <v>TC_WEB_VAL_039</v>
       </c>
       <c r="B300" t="str">
-        <v>Error Handling</v>
+        <v>Input Validation</v>
       </c>
       <c r="C300" t="str">
-        <v>Error Handling Automated Verification Case #1</v>
+        <v>Input Validation Automated Verification Case #39</v>
       </c>
       <c r="D300" t="str">
-        <v>866ms</v>
+        <v>180ms</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>TC_WEB_ERR_002</v>
+        <v>TC_WEB_VAL_040</v>
       </c>
       <c r="B301" t="str">
-        <v>Error Handling</v>
+        <v>Input Validation</v>
       </c>
       <c r="C301" t="str">
-        <v>Error Handling Automated Verification Case #2</v>
+        <v>Input Validation Automated Verification Case #40</v>
       </c>
       <c r="D301" t="str">
-        <v>782ms</v>
+        <v>505ms</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>TC_WEB_ERR_003</v>
+        <v>TC_WEB_ERR_001</v>
       </c>
       <c r="B302" t="str">
         <v>Error Handling</v>
       </c>
       <c r="C302" t="str">
-        <v>Error Handling Automated Verification Case #3</v>
+        <v>Error Handling Automated Verification Case #1</v>
       </c>
       <c r="D302" t="str">
-        <v>427ms</v>
+        <v>297ms</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>TC_WEB_ERR_004</v>
+        <v>TC_WEB_ERR_002</v>
       </c>
       <c r="B303" t="str">
         <v>Error Handling</v>
       </c>
       <c r="C303" t="str">
-        <v>Error Handling Automated Verification Case #4</v>
+        <v>Error Handling Automated Verification Case #2</v>
       </c>
       <c r="D303" t="str">
-        <v>459ms</v>
+        <v>687ms</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>TC_WEB_ERR_005</v>
+        <v>TC_WEB_ERR_003</v>
       </c>
       <c r="B304" t="str">
         <v>Error Handling</v>
       </c>
       <c r="C304" t="str">
-        <v>Error Handling Automated Verification Case #5</v>
+        <v>Error Handling Automated Verification Case #3</v>
       </c>
       <c r="D304" t="str">
-        <v>178ms</v>
+        <v>645ms</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>TC_WEB_ERR_006</v>
+        <v>TC_WEB_ERR_004</v>
       </c>
       <c r="B305" t="str">
         <v>Error Handling</v>
       </c>
       <c r="C305" t="str">
-        <v>Error Handling Automated Verification Case #6</v>
+        <v>Error Handling Automated Verification Case #4</v>
       </c>
       <c r="D305" t="str">
-        <v>876ms</v>
+        <v>438ms</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>TC_WEB_ERR_007</v>
+        <v>TC_WEB_ERR_005</v>
       </c>
       <c r="B306" t="str">
         <v>Error Handling</v>
       </c>
       <c r="C306" t="str">
-        <v>Error Handling Automated Verification Case #7</v>
+        <v>Error Handling Automated Verification Case #5</v>
       </c>
       <c r="D306" t="str">
-        <v>225ms</v>
+        <v>309ms</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>TC_WEB_ERR_008</v>
+        <v>TC_WEB_ERR_006</v>
       </c>
       <c r="B307" t="str">
         <v>Error Handling</v>
       </c>
       <c r="C307" t="str">
-        <v>Error Handling Automated Verification Case #8</v>
+        <v>Error Handling Automated Verification Case #6</v>
       </c>
       <c r="D307" t="str">
-        <v>894ms</v>
+        <v>573ms</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>TC_WEB_ERR_009</v>
+        <v>TC_WEB_ERR_007</v>
       </c>
       <c r="B308" t="str">
         <v>Error Handling</v>
       </c>
       <c r="C308" t="str">
-        <v>Error Handling Automated Verification Case #9</v>
+        <v>Error Handling Automated Verification Case #7</v>
       </c>
       <c r="D308" t="str">
-        <v>438ms</v>
+        <v>396ms</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>TC_WEB_ERR_010</v>
+        <v>TC_WEB_ERR_008</v>
       </c>
       <c r="B309" t="str">
         <v>Error Handling</v>
       </c>
       <c r="C309" t="str">
-        <v>Error Handling Automated Verification Case #10</v>
+        <v>Error Handling Automated Verification Case #8</v>
       </c>
       <c r="D309" t="str">
-        <v>723ms</v>
+        <v>261ms</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>TC_WEB_ERR_011</v>
+        <v>TC_WEB_ERR_009</v>
       </c>
       <c r="B310" t="str">
         <v>Error Handling</v>
       </c>
       <c r="C310" t="str">
-        <v>Error Handling Automated Verification Case #11</v>
+        <v>Error Handling Automated Verification Case #9</v>
       </c>
       <c r="D310" t="str">
-        <v>654ms</v>
+        <v>475ms</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>TC_WEB_ERR_012</v>
+        <v>TC_WEB_ERR_010</v>
       </c>
       <c r="B311" t="str">
         <v>Error Handling</v>
       </c>
       <c r="C311" t="str">
-        <v>Error Handling Automated Verification Case #12</v>
+        <v>Error Handling Automated Verification Case #10</v>
       </c>
       <c r="D311" t="str">
-        <v>875ms</v>
+        <v>206ms</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>TC_WEB_ERR_013</v>
+        <v>TC_WEB_ERR_011</v>
       </c>
       <c r="B312" t="str">
         <v>Error Handling</v>
       </c>
       <c r="C312" t="str">
-        <v>Error Handling Automated Verification Case #13</v>
+        <v>Error Handling Automated Verification Case #11</v>
       </c>
       <c r="D312" t="str">
-        <v>164ms</v>
+        <v>684ms</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>TC_WEB_ERR_014</v>
+        <v>TC_WEB_ERR_012</v>
       </c>
       <c r="B313" t="str">
         <v>Error Handling</v>
       </c>
       <c r="C313" t="str">
-        <v>Error Handling Automated Verification Case #14</v>
+        <v>Error Handling Automated Verification Case #12</v>
       </c>
       <c r="D313" t="str">
-        <v>445ms</v>
+        <v>509ms</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>TC_WEB_ERR_015</v>
+        <v>TC_WEB_ERR_013</v>
       </c>
       <c r="B314" t="str">
         <v>Error Handling</v>
       </c>
       <c r="C314" t="str">
-        <v>Error Handling Automated Verification Case #15</v>
+        <v>Error Handling Automated Verification Case #13</v>
       </c>
       <c r="D314" t="str">
-        <v>682ms</v>
+        <v>467ms</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>TC_WEB_ERR_016</v>
+        <v>TC_WEB_ERR_014</v>
       </c>
       <c r="B315" t="str">
         <v>Error Handling</v>
       </c>
       <c r="C315" t="str">
-        <v>Error Handling Automated Verification Case #16</v>
+        <v>Error Handling Automated Verification Case #14</v>
       </c>
       <c r="D315" t="str">
-        <v>565ms</v>
+        <v>582ms</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>TC_WEB_ERR_017</v>
+        <v>TC_WEB_ERR_015</v>
       </c>
       <c r="B316" t="str">
         <v>Error Handling</v>
       </c>
       <c r="C316" t="str">
-        <v>Error Handling Automated Verification Case #17</v>
+        <v>Error Handling Automated Verification Case #15</v>
       </c>
       <c r="D316" t="str">
-        <v>599ms</v>
+        <v>791ms</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>TC_WEB_ERR_018</v>
+        <v>TC_WEB_ERR_016</v>
       </c>
       <c r="B317" t="str">
         <v>Error Handling</v>
       </c>
       <c r="C317" t="str">
-        <v>Error Handling Automated Verification Case #18</v>
+        <v>Error Handling Automated Verification Case #16</v>
       </c>
       <c r="D317" t="str">
-        <v>301ms</v>
+        <v>232ms</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>TC_WEB_ERR_019</v>
+        <v>TC_WEB_ERR_017</v>
       </c>
       <c r="B318" t="str">
         <v>Error Handling</v>
       </c>
       <c r="C318" t="str">
-        <v>Error Handling Automated Verification Case #19</v>
+        <v>Error Handling Automated Verification Case #17</v>
       </c>
       <c r="D318" t="str">
-        <v>548ms</v>
+        <v>568ms</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>TC_WEB_ERR_020</v>
+        <v>TC_WEB_ERR_018</v>
       </c>
       <c r="B319" t="str">
         <v>Error Handling</v>
       </c>
       <c r="C319" t="str">
-        <v>Error Handling Automated Verification Case #20</v>
+        <v>Error Handling Automated Verification Case #18</v>
       </c>
       <c r="D319" t="str">
-        <v>555ms</v>
+        <v>583ms</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>TC_WEB_SESS_001</v>
+        <v>TC_WEB_ERR_019</v>
       </c>
       <c r="B320" t="str">
-        <v>Session Management</v>
+        <v>Error Handling</v>
       </c>
       <c r="C320" t="str">
-        <v>Session Management Automated Verification Case #1</v>
+        <v>Error Handling Automated Verification Case #19</v>
       </c>
       <c r="D320" t="str">
-        <v>735ms</v>
+        <v>805ms</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>TC_WEB_SESS_002</v>
+        <v>TC_WEB_ERR_020</v>
       </c>
       <c r="B321" t="str">
-        <v>Session Management</v>
+        <v>Error Handling</v>
       </c>
       <c r="C321" t="str">
-        <v>Session Management Automated Verification Case #2</v>
+        <v>Error Handling Automated Verification Case #20</v>
       </c>
       <c r="D321" t="str">
-        <v>620ms</v>
+        <v>188ms</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>TC_WEB_SESS_003</v>
+        <v>TC_WEB_SESS_001</v>
       </c>
       <c r="B322" t="str">
         <v>Session Management</v>
       </c>
       <c r="C322" t="str">
-        <v>Session Management Automated Verification Case #3</v>
+        <v>Session Management Automated Verification Case #1</v>
       </c>
       <c r="D322" t="str">
-        <v>526ms</v>
+        <v>427ms</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>TC_WEB_SESS_004</v>
+        <v>TC_WEB_SESS_002</v>
       </c>
       <c r="B323" t="str">
         <v>Session Management</v>
       </c>
       <c r="C323" t="str">
-        <v>Session Management Automated Verification Case #4</v>
+        <v>Session Management Automated Verification Case #2</v>
       </c>
       <c r="D323" t="str">
-        <v>136ms</v>
+        <v>261ms</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>TC_WEB_SESS_005</v>
+        <v>TC_WEB_SESS_003</v>
       </c>
       <c r="B324" t="str">
         <v>Session Management</v>
       </c>
       <c r="C324" t="str">
-        <v>Session Management Automated Verification Case #5</v>
+        <v>Session Management Automated Verification Case #3</v>
       </c>
       <c r="D324" t="str">
-        <v>545ms</v>
+        <v>653ms</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>TC_WEB_SESS_006</v>
+        <v>TC_WEB_SESS_004</v>
       </c>
       <c r="B325" t="str">
         <v>Session Management</v>
       </c>
       <c r="C325" t="str">
-        <v>Session Management Automated Verification Case #6</v>
+        <v>Session Management Automated Verification Case #4</v>
       </c>
       <c r="D325" t="str">
-        <v>548ms</v>
+        <v>658ms</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>TC_WEB_SESS_007</v>
+        <v>TC_WEB_SESS_005</v>
       </c>
       <c r="B326" t="str">
         <v>Session Management</v>
       </c>
       <c r="C326" t="str">
-        <v>Session Management Automated Verification Case #7</v>
+        <v>Session Management Automated Verification Case #5</v>
       </c>
       <c r="D326" t="str">
-        <v>812ms</v>
+        <v>620ms</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>TC_WEB_SESS_008</v>
+        <v>TC_WEB_SESS_006</v>
       </c>
       <c r="B327" t="str">
         <v>Session Management</v>
       </c>
       <c r="C327" t="str">
-        <v>Session Management Automated Verification Case #8</v>
+        <v>Session Management Automated Verification Case #6</v>
       </c>
       <c r="D327" t="str">
-        <v>358ms</v>
+        <v>276ms</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>TC_WEB_SESS_009</v>
+        <v>TC_WEB_SESS_007</v>
       </c>
       <c r="B328" t="str">
         <v>Session Management</v>
       </c>
       <c r="C328" t="str">
-        <v>Session Management Automated Verification Case #9</v>
+        <v>Session Management Automated Verification Case #7</v>
       </c>
       <c r="D328" t="str">
-        <v>645ms</v>
+        <v>436ms</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>TC_WEB_SESS_010</v>
+        <v>TC_WEB_SESS_008</v>
       </c>
       <c r="B329" t="str">
         <v>Session Management</v>
       </c>
       <c r="C329" t="str">
-        <v>Session Management Automated Verification Case #10</v>
+        <v>Session Management Automated Verification Case #8</v>
       </c>
       <c r="D329" t="str">
-        <v>547ms</v>
+        <v>196ms</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>TC_WEB_SESS_011</v>
+        <v>TC_WEB_SESS_009</v>
       </c>
       <c r="B330" t="str">
         <v>Session Management</v>
       </c>
       <c r="C330" t="str">
-        <v>Session Management Automated Verification Case #11</v>
+        <v>Session Management Automated Verification Case #9</v>
       </c>
       <c r="D330" t="str">
-        <v>186ms</v>
+        <v>762ms</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>TC_WEB_SESS_012</v>
+        <v>TC_WEB_SESS_010</v>
       </c>
       <c r="B331" t="str">
         <v>Session Management</v>
       </c>
       <c r="C331" t="str">
-        <v>Session Management Automated Verification Case #12</v>
+        <v>Session Management Automated Verification Case #10</v>
       </c>
       <c r="D331" t="str">
-        <v>765ms</v>
+        <v>849ms</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>TC_WEB_SESS_013</v>
+        <v>TC_WEB_SESS_011</v>
       </c>
       <c r="B332" t="str">
         <v>Session Management</v>
       </c>
       <c r="C332" t="str">
-        <v>Session Management Automated Verification Case #13</v>
+        <v>Session Management Automated Verification Case #11</v>
       </c>
       <c r="D332" t="str">
-        <v>302ms</v>
+        <v>395ms</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>TC_WEB_SESS_014</v>
+        <v>TC_WEB_SESS_012</v>
       </c>
       <c r="B333" t="str">
         <v>Session Management</v>
       </c>
       <c r="C333" t="str">
-        <v>Session Management Automated Verification Case #14</v>
+        <v>Session Management Automated Verification Case #12</v>
       </c>
       <c r="D333" t="str">
-        <v>104ms</v>
+        <v>321ms</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>TC_WEB_SESS_015</v>
+        <v>TC_WEB_SESS_013</v>
       </c>
       <c r="B334" t="str">
         <v>Session Management</v>
       </c>
       <c r="C334" t="str">
-        <v>Session Management Automated Verification Case #15</v>
+        <v>Session Management Automated Verification Case #13</v>
       </c>
       <c r="D334" t="str">
-        <v>310ms</v>
+        <v>293ms</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>TC_WEB_SESS_016</v>
+        <v>TC_WEB_SESS_014</v>
       </c>
       <c r="B335" t="str">
         <v>Session Management</v>
       </c>
       <c r="C335" t="str">
-        <v>Session Management Automated Verification Case #16</v>
+        <v>Session Management Automated Verification Case #14</v>
       </c>
       <c r="D335" t="str">
-        <v>898ms</v>
+        <v>539ms</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>TC_WEB_SESS_017</v>
+        <v>TC_WEB_SESS_015</v>
       </c>
       <c r="B336" t="str">
         <v>Session Management</v>
       </c>
       <c r="C336" t="str">
-        <v>Session Management Automated Verification Case #17</v>
+        <v>Session Management Automated Verification Case #15</v>
       </c>
       <c r="D336" t="str">
-        <v>392ms</v>
+        <v>440ms</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>TC_WEB_SESS_018</v>
+        <v>TC_WEB_SESS_016</v>
       </c>
       <c r="B337" t="str">
         <v>Session Management</v>
       </c>
       <c r="C337" t="str">
-        <v>Session Management Automated Verification Case #18</v>
+        <v>Session Management Automated Verification Case #16</v>
       </c>
       <c r="D337" t="str">
-        <v>302ms</v>
+        <v>640ms</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>TC_WEB_SESS_019</v>
+        <v>TC_WEB_SESS_017</v>
       </c>
       <c r="B338" t="str">
         <v>Session Management</v>
       </c>
       <c r="C338" t="str">
-        <v>Session Management Automated Verification Case #19</v>
+        <v>Session Management Automated Verification Case #17</v>
       </c>
       <c r="D338" t="str">
-        <v>895ms</v>
+        <v>544ms</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>TC_WEB_SESS_020</v>
+        <v>TC_WEB_SESS_018</v>
       </c>
       <c r="B339" t="str">
         <v>Session Management</v>
       </c>
       <c r="C339" t="str">
-        <v>Session Management Automated Verification Case #20</v>
+        <v>Session Management Automated Verification Case #18</v>
       </c>
       <c r="D339" t="str">
-        <v>666ms</v>
+        <v>566ms</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>TC_WEB_FILE_001</v>
+        <v>TC_WEB_SESS_019</v>
       </c>
       <c r="B340" t="str">
-        <v>File Upload</v>
+        <v>Session Management</v>
       </c>
       <c r="C340" t="str">
-        <v>File Upload Automated Verification Case #1</v>
+        <v>Session Management Automated Verification Case #19</v>
       </c>
       <c r="D340" t="str">
-        <v>574ms</v>
+        <v>746ms</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>TC_WEB_FILE_002</v>
+        <v>TC_WEB_SESS_020</v>
       </c>
       <c r="B341" t="str">
-        <v>File Upload</v>
+        <v>Session Management</v>
       </c>
       <c r="C341" t="str">
-        <v>File Upload Automated Verification Case #2</v>
+        <v>Session Management Automated Verification Case #20</v>
       </c>
       <c r="D341" t="str">
-        <v>240ms</v>
+        <v>791ms</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>TC_WEB_FILE_003</v>
+        <v>TC_WEB_FILE_001</v>
       </c>
       <c r="B342" t="str">
         <v>File Upload</v>
       </c>
       <c r="C342" t="str">
-        <v>File Upload Automated Verification Case #3</v>
+        <v>File Upload Automated Verification Case #1</v>
       </c>
       <c r="D342" t="str">
-        <v>625ms</v>
+        <v>537ms</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>TC_WEB_FILE_004</v>
+        <v>TC_WEB_FILE_002</v>
       </c>
       <c r="B343" t="str">
         <v>File Upload</v>
       </c>
       <c r="C343" t="str">
-        <v>File Upload Automated Verification Case #4</v>
+        <v>File Upload Automated Verification Case #2</v>
       </c>
       <c r="D343" t="str">
-        <v>478ms</v>
+        <v>118ms</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>TC_WEB_FILE_005</v>
+        <v>TC_WEB_FILE_003</v>
       </c>
       <c r="B344" t="str">
         <v>File Upload</v>
       </c>
       <c r="C344" t="str">
-        <v>File Upload Automated Verification Case #5</v>
+        <v>File Upload Automated Verification Case #3</v>
       </c>
       <c r="D344" t="str">
-        <v>261ms</v>
+        <v>256ms</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>TC_WEB_FILE_006</v>
+        <v>TC_WEB_FILE_004</v>
       </c>
       <c r="B345" t="str">
         <v>File Upload</v>
       </c>
       <c r="C345" t="str">
-        <v>File Upload Automated Verification Case #6</v>
+        <v>File Upload Automated Verification Case #4</v>
       </c>
       <c r="D345" t="str">
-        <v>516ms</v>
+        <v>587ms</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>TC_WEB_FILE_007</v>
+        <v>TC_WEB_FILE_005</v>
       </c>
       <c r="B346" t="str">
         <v>File Upload</v>
       </c>
       <c r="C346" t="str">
-        <v>File Upload Automated Verification Case #7</v>
+        <v>File Upload Automated Verification Case #5</v>
       </c>
       <c r="D346" t="str">
-        <v>805ms</v>
+        <v>822ms</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>TC_WEB_FILE_008</v>
+        <v>TC_WEB_FILE_006</v>
       </c>
       <c r="B347" t="str">
         <v>File Upload</v>
       </c>
       <c r="C347" t="str">
-        <v>File Upload Automated Verification Case #8</v>
+        <v>File Upload Automated Verification Case #6</v>
       </c>
       <c r="D347" t="str">
-        <v>666ms</v>
+        <v>611ms</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>TC_WEB_FILE_009</v>
+        <v>TC_WEB_FILE_007</v>
       </c>
       <c r="B348" t="str">
         <v>File Upload</v>
       </c>
       <c r="C348" t="str">
-        <v>File Upload Automated Verification Case #9</v>
+        <v>File Upload Automated Verification Case #7</v>
       </c>
       <c r="D348" t="str">
-        <v>657ms</v>
+        <v>577ms</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>TC_WEB_FILE_010</v>
+        <v>TC_WEB_FILE_008</v>
       </c>
       <c r="B349" t="str">
         <v>File Upload</v>
       </c>
       <c r="C349" t="str">
-        <v>File Upload Automated Verification Case #10</v>
+        <v>File Upload Automated Verification Case #8</v>
       </c>
       <c r="D349" t="str">
-        <v>227ms</v>
+        <v>523ms</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>TC_WEB_FILE_011</v>
+        <v>TC_WEB_FILE_009</v>
       </c>
       <c r="B350" t="str">
         <v>File Upload</v>
       </c>
       <c r="C350" t="str">
-        <v>File Upload Automated Verification Case #11</v>
+        <v>File Upload Automated Verification Case #9</v>
       </c>
       <c r="D350" t="str">
-        <v>110ms</v>
+        <v>533ms</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>TC_WEB_FILE_012</v>
+        <v>TC_WEB_FILE_010</v>
       </c>
       <c r="B351" t="str">
         <v>File Upload</v>
       </c>
       <c r="C351" t="str">
-        <v>File Upload Automated Verification Case #12</v>
+        <v>File Upload Automated Verification Case #10</v>
       </c>
       <c r="D351" t="str">
-        <v>669ms</v>
+        <v>284ms</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>TC_WEB_FILE_013</v>
+        <v>TC_WEB_FILE_011</v>
       </c>
       <c r="B352" t="str">
         <v>File Upload</v>
       </c>
       <c r="C352" t="str">
-        <v>File Upload Automated Verification Case #13</v>
+        <v>File Upload Automated Verification Case #11</v>
       </c>
       <c r="D352" t="str">
-        <v>230ms</v>
+        <v>194ms</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>TC_WEB_FILE_014</v>
+        <v>TC_WEB_FILE_012</v>
       </c>
       <c r="B353" t="str">
         <v>File Upload</v>
       </c>
       <c r="C353" t="str">
-        <v>File Upload Automated Verification Case #14</v>
+        <v>File Upload Automated Verification Case #12</v>
       </c>
       <c r="D353" t="str">
-        <v>879ms</v>
+        <v>313ms</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>TC_WEB_FILE_015</v>
+        <v>TC_WEB_FILE_013</v>
       </c>
       <c r="B354" t="str">
         <v>File Upload</v>
       </c>
       <c r="C354" t="str">
-        <v>File Upload Automated Verification Case #15</v>
+        <v>File Upload Automated Verification Case #13</v>
       </c>
       <c r="D354" t="str">
-        <v>235ms</v>
+        <v>602ms</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>TC_WEB_FILE_016</v>
+        <v>TC_WEB_FILE_014</v>
       </c>
       <c r="B355" t="str">
         <v>File Upload</v>
       </c>
       <c r="C355" t="str">
-        <v>File Upload Automated Verification Case #16</v>
+        <v>File Upload Automated Verification Case #14</v>
       </c>
       <c r="D355" t="str">
-        <v>477ms</v>
+        <v>535ms</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>TC_WEB_FILE_017</v>
+        <v>TC_WEB_FILE_015</v>
       </c>
       <c r="B356" t="str">
         <v>File Upload</v>
       </c>
       <c r="C356" t="str">
-        <v>File Upload Automated Verification Case #17</v>
+        <v>File Upload Automated Verification Case #15</v>
       </c>
       <c r="D356" t="str">
-        <v>166ms</v>
+        <v>479ms</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>TC_WEB_FILE_018</v>
+        <v>TC_WEB_FILE_016</v>
       </c>
       <c r="B357" t="str">
         <v>File Upload</v>
       </c>
       <c r="C357" t="str">
-        <v>File Upload Automated Verification Case #18</v>
+        <v>File Upload Automated Verification Case #16</v>
       </c>
       <c r="D357" t="str">
-        <v>621ms</v>
+        <v>150ms</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>TC_WEB_FILE_019</v>
+        <v>TC_WEB_FILE_017</v>
       </c>
       <c r="B358" t="str">
         <v>File Upload</v>
       </c>
       <c r="C358" t="str">
-        <v>File Upload Automated Verification Case #19</v>
+        <v>File Upload Automated Verification Case #17</v>
       </c>
       <c r="D358" t="str">
-        <v>300ms</v>
+        <v>817ms</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>TC_WEB_FILE_020</v>
+        <v>TC_WEB_FILE_018</v>
       </c>
       <c r="B359" t="str">
         <v>File Upload</v>
       </c>
       <c r="C359" t="str">
-        <v>File Upload Automated Verification Case #20</v>
+        <v>File Upload Automated Verification Case #18</v>
       </c>
       <c r="D359" t="str">
-        <v>532ms</v>
+        <v>503ms</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>TC_WEB_ACC_001</v>
+        <v>TC_WEB_FILE_019</v>
       </c>
       <c r="B360" t="str">
-        <v>Accessibility</v>
+        <v>File Upload</v>
       </c>
       <c r="C360" t="str">
-        <v>Accessibility Automated Verification Case #1</v>
+        <v>File Upload Automated Verification Case #19</v>
       </c>
       <c r="D360" t="str">
-        <v>207ms</v>
+        <v>126ms</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>TC_WEB_ACC_002</v>
+        <v>TC_WEB_FILE_020</v>
       </c>
       <c r="B361" t="str">
-        <v>Accessibility</v>
+        <v>File Upload</v>
       </c>
       <c r="C361" t="str">
-        <v>Accessibility Automated Verification Case #2</v>
+        <v>File Upload Automated Verification Case #20</v>
       </c>
       <c r="D361" t="str">
-        <v>761ms</v>
+        <v>293ms</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>TC_WEB_ACC_003</v>
+        <v>TC_WEB_ACC_001</v>
       </c>
       <c r="B362" t="str">
         <v>Accessibility</v>
       </c>
       <c r="C362" t="str">
-        <v>Accessibility Automated Verification Case #3</v>
+        <v>Accessibility Automated Verification Case #1</v>
       </c>
       <c r="D362" t="str">
-        <v>292ms</v>
+        <v>449ms</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>TC_WEB_ACC_004</v>
+        <v>TC_WEB_ACC_002</v>
       </c>
       <c r="B363" t="str">
         <v>Accessibility</v>
       </c>
       <c r="C363" t="str">
-        <v>Accessibility Automated Verification Case #4</v>
+        <v>Accessibility Automated Verification Case #2</v>
       </c>
       <c r="D363" t="str">
-        <v>817ms</v>
+        <v>396ms</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>TC_WEB_ACC_005</v>
+        <v>TC_WEB_ACC_003</v>
       </c>
       <c r="B364" t="str">
         <v>Accessibility</v>
       </c>
       <c r="C364" t="str">
-        <v>Accessibility Automated Verification Case #5</v>
+        <v>Accessibility Automated Verification Case #3</v>
       </c>
       <c r="D364" t="str">
-        <v>849ms</v>
+        <v>438ms</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>TC_WEB_ACC_006</v>
+        <v>TC_WEB_ACC_004</v>
       </c>
       <c r="B365" t="str">
         <v>Accessibility</v>
       </c>
       <c r="C365" t="str">
-        <v>Accessibility Automated Verification Case #6</v>
+        <v>Accessibility Automated Verification Case #4</v>
       </c>
       <c r="D365" t="str">
-        <v>595ms</v>
+        <v>715ms</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>TC_WEB_ACC_007</v>
+        <v>TC_WEB_ACC_005</v>
       </c>
       <c r="B366" t="str">
         <v>Accessibility</v>
       </c>
       <c r="C366" t="str">
-        <v>Accessibility Automated Verification Case #7</v>
+        <v>Accessibility Automated Verification Case #5</v>
       </c>
       <c r="D366" t="str">
-        <v>411ms</v>
+        <v>452ms</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>TC_WEB_ACC_008</v>
+        <v>TC_WEB_ACC_006</v>
       </c>
       <c r="B367" t="str">
         <v>Accessibility</v>
       </c>
       <c r="C367" t="str">
-        <v>Accessibility Automated Verification Case #8</v>
+        <v>Accessibility Automated Verification Case #6</v>
       </c>
       <c r="D367" t="str">
-        <v>775ms</v>
+        <v>385ms</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>TC_WEB_ACC_009</v>
+        <v>TC_WEB_ACC_007</v>
       </c>
       <c r="B368" t="str">
         <v>Accessibility</v>
       </c>
       <c r="C368" t="str">
-        <v>Accessibility Automated Verification Case #9</v>
+        <v>Accessibility Automated Verification Case #7</v>
       </c>
       <c r="D368" t="str">
-        <v>128ms</v>
+        <v>575ms</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>TC_WEB_ACC_010</v>
+        <v>TC_WEB_ACC_008</v>
       </c>
       <c r="B369" t="str">
         <v>Accessibility</v>
       </c>
       <c r="C369" t="str">
-        <v>Accessibility Automated Verification Case #10</v>
+        <v>Accessibility Automated Verification Case #8</v>
       </c>
       <c r="D369" t="str">
-        <v>356ms</v>
+        <v>582ms</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>TC_WEB_ACC_011</v>
+        <v>TC_WEB_ACC_009</v>
       </c>
       <c r="B370" t="str">
         <v>Accessibility</v>
       </c>
       <c r="C370" t="str">
-        <v>Accessibility Automated Verification Case #11</v>
+        <v>Accessibility Automated Verification Case #9</v>
       </c>
       <c r="D370" t="str">
-        <v>149ms</v>
+        <v>462ms</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>TC_WEB_ACC_012</v>
+        <v>TC_WEB_ACC_010</v>
       </c>
       <c r="B371" t="str">
         <v>Accessibility</v>
       </c>
       <c r="C371" t="str">
-        <v>Accessibility Automated Verification Case #12</v>
+        <v>Accessibility Automated Verification Case #10</v>
       </c>
       <c r="D371" t="str">
-        <v>371ms</v>
+        <v>669ms</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>TC_WEB_ACC_013</v>
+        <v>TC_WEB_ACC_011</v>
       </c>
       <c r="B372" t="str">
         <v>Accessibility</v>
       </c>
       <c r="C372" t="str">
-        <v>Accessibility Automated Verification Case #13</v>
+        <v>Accessibility Automated Verification Case #11</v>
       </c>
       <c r="D372" t="str">
-        <v>242ms</v>
+        <v>157ms</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>TC_WEB_ACC_014</v>
+        <v>TC_WEB_ACC_012</v>
       </c>
       <c r="B373" t="str">
         <v>Accessibility</v>
       </c>
       <c r="C373" t="str">
-        <v>Accessibility Automated Verification Case #14</v>
+        <v>Accessibility Automated Verification Case #12</v>
       </c>
       <c r="D373" t="str">
-        <v>372ms</v>
+        <v>455ms</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>TC_WEB_ACC_015</v>
+        <v>TC_WEB_ACC_013</v>
       </c>
       <c r="B374" t="str">
         <v>Accessibility</v>
       </c>
       <c r="C374" t="str">
-        <v>Accessibility Automated Verification Case #15</v>
+        <v>Accessibility Automated Verification Case #13</v>
       </c>
       <c r="D374" t="str">
-        <v>837ms</v>
+        <v>415ms</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>TC_WEB_ACC_016</v>
+        <v>TC_WEB_ACC_014</v>
       </c>
       <c r="B375" t="str">
         <v>Accessibility</v>
       </c>
       <c r="C375" t="str">
-        <v>Accessibility Automated Verification Case #16</v>
+        <v>Accessibility Automated Verification Case #14</v>
       </c>
       <c r="D375" t="str">
-        <v>811ms</v>
+        <v>850ms</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>TC_WEB_ACC_017</v>
+        <v>TC_WEB_ACC_015</v>
       </c>
       <c r="B376" t="str">
         <v>Accessibility</v>
       </c>
       <c r="C376" t="str">
-        <v>Accessibility Automated Verification Case #17</v>
+        <v>Accessibility Automated Verification Case #15</v>
       </c>
       <c r="D376" t="str">
-        <v>570ms</v>
+        <v>681ms</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>TC_WEB_ACC_018</v>
+        <v>TC_WEB_ACC_016</v>
       </c>
       <c r="B377" t="str">
         <v>Accessibility</v>
       </c>
       <c r="C377" t="str">
-        <v>Accessibility Automated Verification Case #18</v>
+        <v>Accessibility Automated Verification Case #16</v>
       </c>
       <c r="D377" t="str">
-        <v>332ms</v>
+        <v>471ms</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>TC_WEB_ACC_019</v>
+        <v>TC_WEB_ACC_017</v>
       </c>
       <c r="B378" t="str">
         <v>Accessibility</v>
       </c>
       <c r="C378" t="str">
-        <v>Accessibility Automated Verification Case #19</v>
+        <v>Accessibility Automated Verification Case #17</v>
       </c>
       <c r="D378" t="str">
-        <v>487ms</v>
+        <v>340ms</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>TC_WEB_ACC_020</v>
+        <v>TC_WEB_ACC_018</v>
       </c>
       <c r="B379" t="str">
         <v>Accessibility</v>
       </c>
       <c r="C379" t="str">
-        <v>Accessibility Automated Verification Case #20</v>
+        <v>Accessibility Automated Verification Case #18</v>
       </c>
       <c r="D379" t="str">
-        <v>155ms</v>
+        <v>453ms</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>TC_WEB_RESP_001</v>
+        <v>TC_WEB_ACC_019</v>
       </c>
       <c r="B380" t="str">
-        <v>Responsive Design</v>
+        <v>Accessibility</v>
       </c>
       <c r="C380" t="str">
-        <v>Responsive Design Automated Verification Case #1</v>
+        <v>Accessibility Automated Verification Case #19</v>
       </c>
       <c r="D380" t="str">
-        <v>318ms</v>
+        <v>337ms</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>TC_WEB_RESP_002</v>
+        <v>TC_WEB_ACC_020</v>
       </c>
       <c r="B381" t="str">
-        <v>Responsive Design</v>
+        <v>Accessibility</v>
       </c>
       <c r="C381" t="str">
-        <v>Responsive Design Automated Verification Case #2</v>
+        <v>Accessibility Automated Verification Case #20</v>
       </c>
       <c r="D381" t="str">
-        <v>205ms</v>
+        <v>580ms</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>TC_WEB_RESP_003</v>
+        <v>TC_WEB_RESP_001</v>
       </c>
       <c r="B382" t="str">
         <v>Responsive Design</v>
       </c>
       <c r="C382" t="str">
-        <v>Responsive Design Automated Verification Case #3</v>
+        <v>Responsive Design Automated Verification Case #1</v>
       </c>
       <c r="D382" t="str">
-        <v>653ms</v>
+        <v>677ms</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>TC_WEB_RESP_004</v>
+        <v>TC_WEB_RESP_002</v>
       </c>
       <c r="B383" t="str">
         <v>Responsive Design</v>
       </c>
       <c r="C383" t="str">
-        <v>Responsive Design Automated Verification Case #4</v>
+        <v>Responsive Design Automated Verification Case #2</v>
       </c>
       <c r="D383" t="str">
-        <v>118ms</v>
+        <v>835ms</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>TC_WEB_RESP_005</v>
+        <v>TC_WEB_RESP_003</v>
       </c>
       <c r="B384" t="str">
         <v>Responsive Design</v>
       </c>
       <c r="C384" t="str">
-        <v>Responsive Design Automated Verification Case #5</v>
+        <v>Responsive Design Automated Verification Case #3</v>
       </c>
       <c r="D384" t="str">
-        <v>728ms</v>
+        <v>812ms</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>TC_WEB_RESP_006</v>
+        <v>TC_WEB_RESP_004</v>
       </c>
       <c r="B385" t="str">
         <v>Responsive Design</v>
       </c>
       <c r="C385" t="str">
-        <v>Responsive Design Automated Verification Case #6</v>
+        <v>Responsive Design Automated Verification Case #4</v>
       </c>
       <c r="D385" t="str">
-        <v>501ms</v>
+        <v>691ms</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>TC_WEB_RESP_007</v>
+        <v>TC_WEB_RESP_005</v>
       </c>
       <c r="B386" t="str">
         <v>Responsive Design</v>
       </c>
       <c r="C386" t="str">
-        <v>Responsive Design Automated Verification Case #7</v>
+        <v>Responsive Design Automated Verification Case #5</v>
       </c>
       <c r="D386" t="str">
-        <v>246ms</v>
+        <v>604ms</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>TC_WEB_RESP_008</v>
+        <v>TC_WEB_RESP_006</v>
       </c>
       <c r="B387" t="str">
         <v>Responsive Design</v>
       </c>
       <c r="C387" t="str">
-        <v>Responsive Design Automated Verification Case #8</v>
+        <v>Responsive Design Automated Verification Case #6</v>
       </c>
       <c r="D387" t="str">
-        <v>441ms</v>
+        <v>445ms</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>TC_WEB_RESP_009</v>
+        <v>TC_WEB_RESP_007</v>
       </c>
       <c r="B388" t="str">
         <v>Responsive Design</v>
       </c>
       <c r="C388" t="str">
-        <v>Responsive Design Automated Verification Case #9</v>
+        <v>Responsive Design Automated Verification Case #7</v>
       </c>
       <c r="D388" t="str">
-        <v>169ms</v>
+        <v>146ms</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>TC_WEB_RESP_010</v>
+        <v>TC_WEB_RESP_008</v>
       </c>
       <c r="B389" t="str">
         <v>Responsive Design</v>
       </c>
       <c r="C389" t="str">
-        <v>Responsive Design Automated Verification Case #10</v>
+        <v>Responsive Design Automated Verification Case #8</v>
       </c>
       <c r="D389" t="str">
-        <v>717ms</v>
+        <v>281ms</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>TC_WEB_RESP_011</v>
+        <v>TC_WEB_RESP_009</v>
       </c>
       <c r="B390" t="str">
         <v>Responsive Design</v>
       </c>
       <c r="C390" t="str">
-        <v>Responsive Design Automated Verification Case #11</v>
+        <v>Responsive Design Automated Verification Case #9</v>
       </c>
       <c r="D390" t="str">
-        <v>312ms</v>
+        <v>768ms</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>TC_WEB_RESP_012</v>
+        <v>TC_WEB_RESP_010</v>
       </c>
       <c r="B391" t="str">
         <v>Responsive Design</v>
       </c>
       <c r="C391" t="str">
-        <v>Responsive Design Automated Verification Case #12</v>
+        <v>Responsive Design Automated Verification Case #10</v>
       </c>
       <c r="D391" t="str">
-        <v>423ms</v>
+        <v>296ms</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>TC_WEB_RESP_013</v>
+        <v>TC_WEB_RESP_011</v>
       </c>
       <c r="B392" t="str">
         <v>Responsive Design</v>
       </c>
       <c r="C392" t="str">
-        <v>Responsive Design Automated Verification Case #13</v>
+        <v>Responsive Design Automated Verification Case #11</v>
       </c>
       <c r="D392" t="str">
-        <v>658ms</v>
+        <v>109ms</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>TC_WEB_RESP_014</v>
+        <v>TC_WEB_RESP_012</v>
       </c>
       <c r="B393" t="str">
         <v>Responsive Design</v>
       </c>
       <c r="C393" t="str">
-        <v>Responsive Design Automated Verification Case #14</v>
+        <v>Responsive Design Automated Verification Case #12</v>
       </c>
       <c r="D393" t="str">
-        <v>768ms</v>
+        <v>420ms</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>TC_WEB_RESP_015</v>
+        <v>TC_WEB_RESP_013</v>
       </c>
       <c r="B394" t="str">
         <v>Responsive Design</v>
       </c>
       <c r="C394" t="str">
-        <v>Responsive Design Automated Verification Case #15</v>
+        <v>Responsive Design Automated Verification Case #13</v>
       </c>
       <c r="D394" t="str">
-        <v>469ms</v>
+        <v>347ms</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>TC_WEB_RESP_016</v>
+        <v>TC_WEB_RESP_014</v>
       </c>
       <c r="B395" t="str">
         <v>Responsive Design</v>
       </c>
       <c r="C395" t="str">
-        <v>Responsive Design Automated Verification Case #16</v>
+        <v>Responsive Design Automated Verification Case #14</v>
       </c>
       <c r="D395" t="str">
-        <v>500ms</v>
+        <v>821ms</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>TC_WEB_RESP_017</v>
+        <v>TC_WEB_RESP_015</v>
       </c>
       <c r="B396" t="str">
         <v>Responsive Design</v>
       </c>
       <c r="C396" t="str">
-        <v>Responsive Design Automated Verification Case #17</v>
+        <v>Responsive Design Automated Verification Case #15</v>
       </c>
       <c r="D396" t="str">
-        <v>245ms</v>
+        <v>318ms</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>TC_WEB_RESP_018</v>
+        <v>TC_WEB_RESP_016</v>
       </c>
       <c r="B397" t="str">
         <v>Responsive Design</v>
       </c>
       <c r="C397" t="str">
-        <v>Responsive Design Automated Verification Case #18</v>
+        <v>Responsive Design Automated Verification Case #16</v>
       </c>
       <c r="D397" t="str">
-        <v>791ms</v>
+        <v>534ms</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>TC_WEB_RESP_019</v>
+        <v>TC_WEB_RESP_017</v>
       </c>
       <c r="B398" t="str">
         <v>Responsive Design</v>
       </c>
       <c r="C398" t="str">
-        <v>Responsive Design Automated Verification Case #19</v>
+        <v>Responsive Design Automated Verification Case #17</v>
       </c>
       <c r="D398" t="str">
-        <v>892ms</v>
+        <v>209ms</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>TC_WEB_RESP_020</v>
+        <v>TC_WEB_RESP_018</v>
       </c>
       <c r="B399" t="str">
         <v>Responsive Design</v>
       </c>
       <c r="C399" t="str">
-        <v>Responsive Design Automated Verification Case #20</v>
+        <v>Responsive Design Automated Verification Case #18</v>
       </c>
       <c r="D399" t="str">
-        <v>351ms</v>
+        <v>261ms</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>TC_WEB_PERF_001</v>
+        <v>TC_WEB_RESP_019</v>
       </c>
       <c r="B400" t="str">
-        <v>Performance Smoke Tests</v>
+        <v>Responsive Design</v>
       </c>
       <c r="C400" t="str">
-        <v>Performance Smoke Tests Automated Verification Case #1</v>
+        <v>Responsive Design Automated Verification Case #19</v>
       </c>
       <c r="D400" t="str">
-        <v>334ms</v>
+        <v>263ms</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>TC_WEB_PERF_002</v>
+        <v>TC_WEB_RESP_020</v>
       </c>
       <c r="B401" t="str">
-        <v>Performance Smoke Tests</v>
+        <v>Responsive Design</v>
       </c>
       <c r="C401" t="str">
-        <v>Performance Smoke Tests Automated Verification Case #2</v>
+        <v>Responsive Design Automated Verification Case #20</v>
       </c>
       <c r="D401" t="str">
-        <v>566ms</v>
+        <v>702ms</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>TC_WEB_PERF_003</v>
+        <v>TC_WEB_PERF_001</v>
       </c>
       <c r="B402" t="str">
         <v>Performance Smoke Tests</v>
       </c>
       <c r="C402" t="str">
-        <v>Performance Smoke Tests Automated Verification Case #3</v>
+        <v>Performance Smoke Tests Automated Verification Case #1</v>
       </c>
       <c r="D402" t="str">
-        <v>897ms</v>
+        <v>763ms</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>TC_WEB_PERF_004</v>
+        <v>TC_WEB_PERF_002</v>
       </c>
       <c r="B403" t="str">
         <v>Performance Smoke Tests</v>
       </c>
       <c r="C403" t="str">
-        <v>Performance Smoke Tests Automated Verification Case #4</v>
+        <v>Performance Smoke Tests Automated Verification Case #2</v>
       </c>
       <c r="D403" t="str">
-        <v>263ms</v>
+        <v>496ms</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>TC_WEB_PERF_005</v>
+        <v>TC_WEB_PERF_003</v>
       </c>
       <c r="B404" t="str">
         <v>Performance Smoke Tests</v>
       </c>
       <c r="C404" t="str">
-        <v>Performance Smoke Tests Automated Verification Case #5</v>
+        <v>Performance Smoke Tests Automated Verification Case #3</v>
       </c>
       <c r="D404" t="str">
-        <v>825ms</v>
+        <v>622ms</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>TC_WEB_PERF_006</v>
+        <v>TC_WEB_PERF_004</v>
       </c>
       <c r="B405" t="str">
         <v>Performance Smoke Tests</v>
       </c>
       <c r="C405" t="str">
-        <v>Performance Smoke Tests Automated Verification Case #6</v>
+        <v>Performance Smoke Tests Automated Verification Case #4</v>
       </c>
       <c r="D405" t="str">
-        <v>713ms</v>
+        <v>683ms</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>TC_WEB_PERF_007</v>
+        <v>TC_WEB_PERF_005</v>
       </c>
       <c r="B406" t="str">
         <v>Performance Smoke Tests</v>
       </c>
       <c r="C406" t="str">
-        <v>Performance Smoke Tests Automated Verification Case #7</v>
+        <v>Performance Smoke Tests Automated Verification Case #5</v>
       </c>
       <c r="D406" t="str">
-        <v>262ms</v>
+        <v>109ms</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>TC_WEB_PERF_008</v>
+        <v>TC_WEB_PERF_006</v>
       </c>
       <c r="B407" t="str">
         <v>Performance Smoke Tests</v>
       </c>
       <c r="C407" t="str">
-        <v>Performance Smoke Tests Automated Verification Case #8</v>
+        <v>Performance Smoke Tests Automated Verification Case #6</v>
       </c>
       <c r="D407" t="str">
-        <v>118ms</v>
+        <v>107ms</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>TC_WEB_PERF_009</v>
+        <v>TC_WEB_PERF_007</v>
       </c>
       <c r="B408" t="str">
         <v>Performance Smoke Tests</v>
       </c>
       <c r="C408" t="str">
-        <v>Performance Smoke Tests Automated Verification Case #9</v>
+        <v>Performance Smoke Tests Automated Verification Case #7</v>
       </c>
       <c r="D408" t="str">
-        <v>431ms</v>
+        <v>775ms</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>TC_WEB_PERF_010</v>
+        <v>TC_WEB_PERF_008</v>
       </c>
       <c r="B409" t="str">
         <v>Performance Smoke Tests</v>
       </c>
       <c r="C409" t="str">
-        <v>Performance Smoke Tests Automated Verification Case #10</v>
+        <v>Performance Smoke Tests Automated Verification Case #8</v>
       </c>
       <c r="D409" t="str">
-        <v>184ms</v>
+        <v>517ms</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>TC_WEB_PERF_011</v>
+        <v>TC_WEB_PERF_009</v>
       </c>
       <c r="B410" t="str">
         <v>Performance Smoke Tests</v>
       </c>
       <c r="C410" t="str">
-        <v>Performance Smoke Tests Automated Verification Case #11</v>
+        <v>Performance Smoke Tests Automated Verification Case #9</v>
       </c>
       <c r="D410" t="str">
-        <v>887ms</v>
+        <v>777ms</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>TC_WEB_PERF_012</v>
+        <v>TC_WEB_PERF_010</v>
       </c>
       <c r="B411" t="str">
         <v>Performance Smoke Tests</v>
       </c>
       <c r="C411" t="str">
-        <v>Performance Smoke Tests Automated Verification Case #12</v>
+        <v>Performance Smoke Tests Automated Verification Case #10</v>
       </c>
       <c r="D411" t="str">
-        <v>443ms</v>
+        <v>129ms</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>TC_WEB_PERF_013</v>
+        <v>TC_WEB_PERF_011</v>
       </c>
       <c r="B412" t="str">
         <v>Performance Smoke Tests</v>
       </c>
       <c r="C412" t="str">
-        <v>Performance Smoke Tests Automated Verification Case #13</v>
+        <v>Performance Smoke Tests Automated Verification Case #11</v>
       </c>
       <c r="D412" t="str">
-        <v>808ms</v>
+        <v>676ms</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>TC_WEB_PERF_014</v>
+        <v>TC_WEB_PERF_012</v>
       </c>
       <c r="B413" t="str">
         <v>Performance Smoke Tests</v>
       </c>
       <c r="C413" t="str">
-        <v>Performance Smoke Tests Automated Verification Case #14</v>
+        <v>Performance Smoke Tests Automated Verification Case #12</v>
       </c>
       <c r="D413" t="str">
-        <v>465ms</v>
+        <v>120ms</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>TC_WEB_PERF_015</v>
+        <v>TC_WEB_PERF_013</v>
       </c>
       <c r="B414" t="str">
         <v>Performance Smoke Tests</v>
       </c>
       <c r="C414" t="str">
-        <v>Performance Smoke Tests Automated Verification Case #15</v>
+        <v>Performance Smoke Tests Automated Verification Case #13</v>
       </c>
       <c r="D414" t="str">
-        <v>696ms</v>
+        <v>214ms</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>TC_WEB_PERF_016</v>
+        <v>TC_WEB_PERF_014</v>
       </c>
       <c r="B415" t="str">
         <v>Performance Smoke Tests</v>
       </c>
       <c r="C415" t="str">
-        <v>Performance Smoke Tests Automated Verification Case #16</v>
+        <v>Performance Smoke Tests Automated Verification Case #14</v>
       </c>
       <c r="D415" t="str">
-        <v>866ms</v>
+        <v>737ms</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>TC_WEB_PERF_017</v>
+        <v>TC_WEB_PERF_015</v>
       </c>
       <c r="B416" t="str">
         <v>Performance Smoke Tests</v>
       </c>
       <c r="C416" t="str">
-        <v>Performance Smoke Tests Automated Verification Case #17</v>
+        <v>Performance Smoke Tests Automated Verification Case #15</v>
       </c>
       <c r="D416" t="str">
-        <v>117ms</v>
+        <v>779ms</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>TC_WEB_PERF_018</v>
+        <v>TC_WEB_PERF_016</v>
       </c>
       <c r="B417" t="str">
         <v>Performance Smoke Tests</v>
       </c>
       <c r="C417" t="str">
-        <v>Performance Smoke Tests Automated Verification Case #18</v>
+        <v>Performance Smoke Tests Automated Verification Case #16</v>
       </c>
       <c r="D417" t="str">
-        <v>691ms</v>
+        <v>115ms</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>TC_WEB_PERF_019</v>
+        <v>TC_WEB_PERF_017</v>
       </c>
       <c r="B418" t="str">
         <v>Performance Smoke Tests</v>
       </c>
       <c r="C418" t="str">
-        <v>Performance Smoke Tests Automated Verification Case #19</v>
+        <v>Performance Smoke Tests Automated Verification Case #17</v>
       </c>
       <c r="D418" t="str">
-        <v>894ms</v>
+        <v>244ms</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>TC_WEB_PERF_020</v>
+        <v>TC_WEB_PERF_018</v>
       </c>
       <c r="B419" t="str">
         <v>Performance Smoke Tests</v>
       </c>
       <c r="C419" t="str">
-        <v>Performance Smoke Tests Automated Verification Case #20</v>
+        <v>Performance Smoke Tests Automated Verification Case #18</v>
       </c>
       <c r="D419" t="str">
-        <v>747ms</v>
+        <v>456ms</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>TC_WEB_REGRESS_001</v>
+        <v>TC_WEB_PERF_019</v>
       </c>
       <c r="B420" t="str">
-        <v>Regression</v>
+        <v>Performance Smoke Tests</v>
       </c>
       <c r="C420" t="str">
-        <v>Regression Automated Verification Case #1</v>
+        <v>Performance Smoke Tests Automated Verification Case #19</v>
       </c>
       <c r="D420" t="str">
-        <v>483ms</v>
+        <v>434ms</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>TC_WEB_REGRESS_002</v>
+        <v>TC_WEB_PERF_020</v>
       </c>
       <c r="B421" t="str">
-        <v>Regression</v>
+        <v>Performance Smoke Tests</v>
       </c>
       <c r="C421" t="str">
-        <v>Regression Automated Verification Case #2</v>
+        <v>Performance Smoke Tests Automated Verification Case #20</v>
       </c>
       <c r="D421" t="str">
-        <v>345ms</v>
+        <v>417ms</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>TC_WEB_REGRESS_003</v>
+        <v>TC_WEB_REGRESS_001</v>
       </c>
       <c r="B422" t="str">
         <v>Regression</v>
       </c>
       <c r="C422" t="str">
-        <v>Regression Automated Verification Case #3</v>
+        <v>Regression Automated Verification Case #1</v>
       </c>
       <c r="D422" t="str">
-        <v>541ms</v>
+        <v>852ms</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>TC_WEB_REGRESS_004</v>
+        <v>TC_WEB_REGRESS_002</v>
       </c>
       <c r="B423" t="str">
         <v>Regression</v>
       </c>
       <c r="C423" t="str">
-        <v>Regression Automated Verification Case #4</v>
+        <v>Regression Automated Verification Case #2</v>
       </c>
       <c r="D423" t="str">
-        <v>510ms</v>
+        <v>462ms</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>TC_WEB_REGRESS_005</v>
+        <v>TC_WEB_REGRESS_003</v>
       </c>
       <c r="B424" t="str">
         <v>Regression</v>
       </c>
       <c r="C424" t="str">
-        <v>Regression Automated Verification Case #5</v>
+        <v>Regression Automated Verification Case #3</v>
       </c>
       <c r="D424" t="str">
-        <v>213ms</v>
+        <v>105ms</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>TC_WEB_REGRESS_006</v>
+        <v>TC_WEB_REGRESS_004</v>
       </c>
       <c r="B425" t="str">
         <v>Regression</v>
       </c>
       <c r="C425" t="str">
-        <v>Regression Automated Verification Case #6</v>
+        <v>Regression Automated Verification Case #4</v>
       </c>
       <c r="D425" t="str">
-        <v>443ms</v>
+        <v>303ms</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>TC_WEB_REGRESS_007</v>
+        <v>TC_WEB_REGRESS_005</v>
       </c>
       <c r="B426" t="str">
         <v>Regression</v>
       </c>
       <c r="C426" t="str">
-        <v>Regression Automated Verification Case #7</v>
+        <v>Regression Automated Verification Case #5</v>
       </c>
       <c r="D426" t="str">
-        <v>718ms</v>
+        <v>736ms</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>TC_WEB_REGRESS_008</v>
+        <v>TC_WEB_REGRESS_006</v>
       </c>
       <c r="B427" t="str">
         <v>Regression</v>
       </c>
       <c r="C427" t="str">
-        <v>Regression Automated Verification Case #8</v>
+        <v>Regression Automated Verification Case #6</v>
       </c>
       <c r="D427" t="str">
-        <v>674ms</v>
+        <v>462ms</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>TC_WEB_REGRESS_009</v>
+        <v>TC_WEB_REGRESS_007</v>
       </c>
       <c r="B428" t="str">
         <v>Regression</v>
       </c>
       <c r="C428" t="str">
-        <v>Regression Automated Verification Case #9</v>
+        <v>Regression Automated Verification Case #7</v>
       </c>
       <c r="D428" t="str">
-        <v>542ms</v>
+        <v>320ms</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>TC_WEB_REGRESS_010</v>
+        <v>TC_WEB_REGRESS_008</v>
       </c>
       <c r="B429" t="str">
         <v>Regression</v>
       </c>
       <c r="C429" t="str">
-        <v>Regression Automated Verification Case #10</v>
+        <v>Regression Automated Verification Case #8</v>
       </c>
       <c r="D429" t="str">
         <v>143ms</v>
@@ -6407,567 +6407,595 @@
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>TC_WEB_REGRESS_011</v>
+        <v>TC_WEB_REGRESS_009</v>
       </c>
       <c r="B430" t="str">
         <v>Regression</v>
       </c>
       <c r="C430" t="str">
-        <v>Regression Automated Verification Case #11</v>
+        <v>Regression Automated Verification Case #9</v>
       </c>
       <c r="D430" t="str">
-        <v>285ms</v>
+        <v>793ms</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>TC_WEB_REGRESS_012</v>
+        <v>TC_WEB_REGRESS_010</v>
       </c>
       <c r="B431" t="str">
         <v>Regression</v>
       </c>
       <c r="C431" t="str">
-        <v>Regression Automated Verification Case #12</v>
+        <v>Regression Automated Verification Case #10</v>
       </c>
       <c r="D431" t="str">
-        <v>654ms</v>
+        <v>493ms</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>TC_WEB_REGRESS_013</v>
+        <v>TC_WEB_REGRESS_011</v>
       </c>
       <c r="B432" t="str">
         <v>Regression</v>
       </c>
       <c r="C432" t="str">
-        <v>Regression Automated Verification Case #13</v>
+        <v>Regression Automated Verification Case #11</v>
       </c>
       <c r="D432" t="str">
-        <v>452ms</v>
+        <v>275ms</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>TC_WEB_REGRESS_014</v>
+        <v>TC_WEB_REGRESS_012</v>
       </c>
       <c r="B433" t="str">
         <v>Regression</v>
       </c>
       <c r="C433" t="str">
-        <v>Regression Automated Verification Case #14</v>
+        <v>Regression Automated Verification Case #12</v>
       </c>
       <c r="D433" t="str">
-        <v>112ms</v>
+        <v>133ms</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>TC_WEB_REGRESS_015</v>
+        <v>TC_WEB_REGRESS_013</v>
       </c>
       <c r="B434" t="str">
         <v>Regression</v>
       </c>
       <c r="C434" t="str">
-        <v>Regression Automated Verification Case #15</v>
+        <v>Regression Automated Verification Case #13</v>
       </c>
       <c r="D434" t="str">
-        <v>852ms</v>
+        <v>844ms</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>TC_WEB_REGRESS_016</v>
+        <v>TC_WEB_REGRESS_014</v>
       </c>
       <c r="B435" t="str">
         <v>Regression</v>
       </c>
       <c r="C435" t="str">
-        <v>Regression Automated Verification Case #16</v>
+        <v>Regression Automated Verification Case #14</v>
       </c>
       <c r="D435" t="str">
-        <v>591ms</v>
+        <v>503ms</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>TC_WEB_REGRESS_017</v>
+        <v>TC_WEB_REGRESS_015</v>
       </c>
       <c r="B436" t="str">
         <v>Regression</v>
       </c>
       <c r="C436" t="str">
-        <v>Regression Automated Verification Case #17</v>
+        <v>Regression Automated Verification Case #15</v>
       </c>
       <c r="D436" t="str">
-        <v>440ms</v>
+        <v>444ms</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>TC_WEB_REGRESS_018</v>
+        <v>TC_WEB_REGRESS_016</v>
       </c>
       <c r="B437" t="str">
         <v>Regression</v>
       </c>
       <c r="C437" t="str">
-        <v>Regression Automated Verification Case #18</v>
+        <v>Regression Automated Verification Case #16</v>
       </c>
       <c r="D437" t="str">
-        <v>898ms</v>
+        <v>357ms</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>TC_WEB_REGRESS_019</v>
+        <v>TC_WEB_REGRESS_017</v>
       </c>
       <c r="B438" t="str">
         <v>Regression</v>
       </c>
       <c r="C438" t="str">
-        <v>Regression Automated Verification Case #19</v>
+        <v>Regression Automated Verification Case #17</v>
       </c>
       <c r="D438" t="str">
-        <v>298ms</v>
+        <v>154ms</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>TC_WEB_REGRESS_020</v>
+        <v>TC_WEB_REGRESS_018</v>
       </c>
       <c r="B439" t="str">
         <v>Regression</v>
       </c>
       <c r="C439" t="str">
-        <v>Regression Automated Verification Case #20</v>
+        <v>Regression Automated Verification Case #18</v>
       </c>
       <c r="D439" t="str">
-        <v>490ms</v>
+        <v>226ms</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>TC_WEB_REGRESS_021</v>
+        <v>TC_WEB_REGRESS_019</v>
       </c>
       <c r="B440" t="str">
         <v>Regression</v>
       </c>
       <c r="C440" t="str">
-        <v>Regression Automated Verification Case #21</v>
+        <v>Regression Automated Verification Case #19</v>
       </c>
       <c r="D440" t="str">
-        <v>147ms</v>
+        <v>256ms</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>TC_WEB_REGRESS_022</v>
+        <v>TC_WEB_REGRESS_020</v>
       </c>
       <c r="B441" t="str">
         <v>Regression</v>
       </c>
       <c r="C441" t="str">
-        <v>Regression Automated Verification Case #22</v>
+        <v>Regression Automated Verification Case #20</v>
       </c>
       <c r="D441" t="str">
-        <v>819ms</v>
+        <v>487ms</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>TC_WEB_REGRESS_023</v>
+        <v>TC_WEB_REGRESS_021</v>
       </c>
       <c r="B442" t="str">
         <v>Regression</v>
       </c>
       <c r="C442" t="str">
-        <v>Regression Automated Verification Case #23</v>
+        <v>Regression Automated Verification Case #21</v>
       </c>
       <c r="D442" t="str">
-        <v>113ms</v>
+        <v>191ms</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>TC_WEB_REGRESS_024</v>
+        <v>TC_WEB_REGRESS_022</v>
       </c>
       <c r="B443" t="str">
         <v>Regression</v>
       </c>
       <c r="C443" t="str">
-        <v>Regression Automated Verification Case #24</v>
+        <v>Regression Automated Verification Case #22</v>
       </c>
       <c r="D443" t="str">
-        <v>345ms</v>
+        <v>754ms</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>TC_WEB_REGRESS_025</v>
+        <v>TC_WEB_REGRESS_023</v>
       </c>
       <c r="B444" t="str">
         <v>Regression</v>
       </c>
       <c r="C444" t="str">
-        <v>Regression Automated Verification Case #25</v>
+        <v>Regression Automated Verification Case #23</v>
       </c>
       <c r="D444" t="str">
-        <v>660ms</v>
+        <v>856ms</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>TC_WEB_REGRESS_026</v>
+        <v>TC_WEB_REGRESS_024</v>
       </c>
       <c r="B445" t="str">
         <v>Regression</v>
       </c>
       <c r="C445" t="str">
-        <v>Regression Automated Verification Case #26</v>
+        <v>Regression Automated Verification Case #24</v>
       </c>
       <c r="D445" t="str">
-        <v>165ms</v>
+        <v>259ms</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>TC_WEB_REGRESS_027</v>
+        <v>TC_WEB_REGRESS_025</v>
       </c>
       <c r="B446" t="str">
         <v>Regression</v>
       </c>
       <c r="C446" t="str">
-        <v>Regression Automated Verification Case #27</v>
+        <v>Regression Automated Verification Case #25</v>
       </c>
       <c r="D446" t="str">
-        <v>269ms</v>
+        <v>596ms</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>TC_WEB_REGRESS_028</v>
+        <v>TC_WEB_REGRESS_026</v>
       </c>
       <c r="B447" t="str">
         <v>Regression</v>
       </c>
       <c r="C447" t="str">
-        <v>Regression Automated Verification Case #28</v>
+        <v>Regression Automated Verification Case #26</v>
       </c>
       <c r="D447" t="str">
-        <v>759ms</v>
+        <v>499ms</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>TC_WEB_REGRESS_029</v>
+        <v>TC_WEB_REGRESS_027</v>
       </c>
       <c r="B448" t="str">
         <v>Regression</v>
       </c>
       <c r="C448" t="str">
-        <v>Regression Automated Verification Case #29</v>
+        <v>Regression Automated Verification Case #27</v>
       </c>
       <c r="D448" t="str">
-        <v>492ms</v>
+        <v>878ms</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>TC_WEB_REGRESS_030</v>
+        <v>TC_WEB_REGRESS_028</v>
       </c>
       <c r="B449" t="str">
         <v>Regression</v>
       </c>
       <c r="C449" t="str">
-        <v>Regression Automated Verification Case #30</v>
+        <v>Regression Automated Verification Case #28</v>
       </c>
       <c r="D449" t="str">
-        <v>345ms</v>
+        <v>834ms</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>TC_WEB_REGRESS_031</v>
+        <v>TC_WEB_REGRESS_029</v>
       </c>
       <c r="B450" t="str">
         <v>Regression</v>
       </c>
       <c r="C450" t="str">
-        <v>Regression Automated Verification Case #31</v>
+        <v>Regression Automated Verification Case #29</v>
       </c>
       <c r="D450" t="str">
-        <v>526ms</v>
+        <v>705ms</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>TC_WEB_REGRESS_032</v>
+        <v>TC_WEB_REGRESS_030</v>
       </c>
       <c r="B451" t="str">
         <v>Regression</v>
       </c>
       <c r="C451" t="str">
-        <v>Regression Automated Verification Case #32</v>
+        <v>Regression Automated Verification Case #30</v>
       </c>
       <c r="D451" t="str">
-        <v>207ms</v>
+        <v>691ms</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>TC_WEB_REGRESS_033</v>
+        <v>TC_WEB_REGRESS_031</v>
       </c>
       <c r="B452" t="str">
         <v>Regression</v>
       </c>
       <c r="C452" t="str">
-        <v>Regression Automated Verification Case #33</v>
+        <v>Regression Automated Verification Case #31</v>
       </c>
       <c r="D452" t="str">
-        <v>480ms</v>
+        <v>318ms</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>TC_WEB_REGRESS_034</v>
+        <v>TC_WEB_REGRESS_032</v>
       </c>
       <c r="B453" t="str">
         <v>Regression</v>
       </c>
       <c r="C453" t="str">
-        <v>Regression Automated Verification Case #34</v>
+        <v>Regression Automated Verification Case #32</v>
       </c>
       <c r="D453" t="str">
-        <v>589ms</v>
+        <v>514ms</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>TC_WEB_REGRESS_035</v>
+        <v>TC_WEB_REGRESS_033</v>
       </c>
       <c r="B454" t="str">
         <v>Regression</v>
       </c>
       <c r="C454" t="str">
-        <v>Regression Automated Verification Case #35</v>
+        <v>Regression Automated Verification Case #33</v>
       </c>
       <c r="D454" t="str">
-        <v>640ms</v>
+        <v>849ms</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>TC_WEB_REGRESS_036</v>
+        <v>TC_WEB_REGRESS_034</v>
       </c>
       <c r="B455" t="str">
         <v>Regression</v>
       </c>
       <c r="C455" t="str">
-        <v>Regression Automated Verification Case #36</v>
+        <v>Regression Automated Verification Case #34</v>
       </c>
       <c r="D455" t="str">
-        <v>311ms</v>
+        <v>755ms</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>TC_WEB_REGRESS_037</v>
+        <v>TC_WEB_REGRESS_035</v>
       </c>
       <c r="B456" t="str">
         <v>Regression</v>
       </c>
       <c r="C456" t="str">
-        <v>Regression Automated Verification Case #37</v>
+        <v>Regression Automated Verification Case #35</v>
       </c>
       <c r="D456" t="str">
-        <v>258ms</v>
+        <v>127ms</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>TC_WEB_REGRESS_038</v>
+        <v>TC_WEB_REGRESS_036</v>
       </c>
       <c r="B457" t="str">
         <v>Regression</v>
       </c>
       <c r="C457" t="str">
-        <v>Regression Automated Verification Case #38</v>
+        <v>Regression Automated Verification Case #36</v>
       </c>
       <c r="D457" t="str">
-        <v>648ms</v>
+        <v>871ms</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>TC_WEB_REGRESS_039</v>
+        <v>TC_WEB_REGRESS_037</v>
       </c>
       <c r="B458" t="str">
         <v>Regression</v>
       </c>
       <c r="C458" t="str">
-        <v>Regression Automated Verification Case #39</v>
+        <v>Regression Automated Verification Case #37</v>
       </c>
       <c r="D458" t="str">
-        <v>477ms</v>
+        <v>731ms</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>TC_WEB_REGRESS_040</v>
+        <v>TC_WEB_REGRESS_038</v>
       </c>
       <c r="B459" t="str">
         <v>Regression</v>
       </c>
       <c r="C459" t="str">
-        <v>Regression Automated Verification Case #40</v>
+        <v>Regression Automated Verification Case #38</v>
       </c>
       <c r="D459" t="str">
-        <v>112ms</v>
+        <v>829ms</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>TC_WEB_REGRESS_041</v>
+        <v>TC_WEB_REGRESS_039</v>
       </c>
       <c r="B460" t="str">
         <v>Regression</v>
       </c>
       <c r="C460" t="str">
-        <v>Regression Automated Verification Case #41</v>
+        <v>Regression Automated Verification Case #39</v>
       </c>
       <c r="D460" t="str">
-        <v>726ms</v>
+        <v>197ms</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>TC_WEB_REGRESS_042</v>
+        <v>TC_WEB_REGRESS_040</v>
       </c>
       <c r="B461" t="str">
         <v>Regression</v>
       </c>
       <c r="C461" t="str">
-        <v>Regression Automated Verification Case #42</v>
+        <v>Regression Automated Verification Case #40</v>
       </c>
       <c r="D461" t="str">
-        <v>163ms</v>
+        <v>535ms</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>TC_WEB_REGRESS_043</v>
+        <v>TC_WEB_REGRESS_041</v>
       </c>
       <c r="B462" t="str">
         <v>Regression</v>
       </c>
       <c r="C462" t="str">
-        <v>Regression Automated Verification Case #43</v>
+        <v>Regression Automated Verification Case #41</v>
       </c>
       <c r="D462" t="str">
-        <v>610ms</v>
+        <v>184ms</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>TC_WEB_REGRESS_044</v>
+        <v>TC_WEB_REGRESS_042</v>
       </c>
       <c r="B463" t="str">
         <v>Regression</v>
       </c>
       <c r="C463" t="str">
-        <v>Regression Automated Verification Case #44</v>
+        <v>Regression Automated Verification Case #42</v>
       </c>
       <c r="D463" t="str">
-        <v>898ms</v>
+        <v>763ms</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>TC_WEB_REGRESS_045</v>
+        <v>TC_WEB_REGRESS_043</v>
       </c>
       <c r="B464" t="str">
         <v>Regression</v>
       </c>
       <c r="C464" t="str">
-        <v>Regression Automated Verification Case #45</v>
+        <v>Regression Automated Verification Case #43</v>
       </c>
       <c r="D464" t="str">
-        <v>705ms</v>
+        <v>474ms</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>TC_WEB_REGRESS_046</v>
+        <v>TC_WEB_REGRESS_044</v>
       </c>
       <c r="B465" t="str">
         <v>Regression</v>
       </c>
       <c r="C465" t="str">
-        <v>Regression Automated Verification Case #46</v>
+        <v>Regression Automated Verification Case #44</v>
       </c>
       <c r="D465" t="str">
-        <v>344ms</v>
+        <v>267ms</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>TC_WEB_REGRESS_047</v>
+        <v>TC_WEB_REGRESS_045</v>
       </c>
       <c r="B466" t="str">
         <v>Regression</v>
       </c>
       <c r="C466" t="str">
-        <v>Regression Automated Verification Case #47</v>
+        <v>Regression Automated Verification Case #45</v>
       </c>
       <c r="D466" t="str">
-        <v>281ms</v>
+        <v>588ms</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>TC_WEB_REGRESS_048</v>
+        <v>TC_WEB_REGRESS_046</v>
       </c>
       <c r="B467" t="str">
         <v>Regression</v>
       </c>
       <c r="C467" t="str">
-        <v>Regression Automated Verification Case #48</v>
+        <v>Regression Automated Verification Case #46</v>
       </c>
       <c r="D467" t="str">
-        <v>609ms</v>
+        <v>532ms</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>TC_WEB_REGRESS_049</v>
+        <v>TC_WEB_REGRESS_047</v>
       </c>
       <c r="B468" t="str">
         <v>Regression</v>
       </c>
       <c r="C468" t="str">
-        <v>Regression Automated Verification Case #49</v>
+        <v>Regression Automated Verification Case #47</v>
       </c>
       <c r="D468" t="str">
-        <v>608ms</v>
+        <v>186ms</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>TC_WEB_REGRESS_050</v>
+        <v>TC_WEB_REGRESS_048</v>
       </c>
       <c r="B469" t="str">
         <v>Regression</v>
       </c>
       <c r="C469" t="str">
+        <v>Regression Automated Verification Case #48</v>
+      </c>
+      <c r="D469" t="str">
+        <v>789ms</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="str">
+        <v>TC_WEB_REGRESS_049</v>
+      </c>
+      <c r="B470" t="str">
+        <v>Regression</v>
+      </c>
+      <c r="C470" t="str">
+        <v>Regression Automated Verification Case #49</v>
+      </c>
+      <c r="D470" t="str">
+        <v>498ms</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="str">
+        <v>TC_WEB_REGRESS_050</v>
+      </c>
+      <c r="B471" t="str">
+        <v>Regression</v>
+      </c>
+      <c r="C471" t="str">
         <v>Regression Automated Verification Case #50</v>
       </c>
-      <c r="D469" t="str">
-        <v>385ms</v>
+      <c r="D471" t="str">
+        <v>642ms</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D469"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D471"/>
   </ignoredErrors>
 </worksheet>
 </file>